--- a/research/traditional_assets/database/data/thailand/thailand_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ26"/>
+  <dimension ref="A1:AQ29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08650000000000001</v>
+        <v>0.0851</v>
       </c>
       <c r="E2">
+        <v>0.1105</v>
+      </c>
+      <c r="F2">
         <v>0.12</v>
       </c>
-      <c r="F2">
-        <v>0.262</v>
-      </c>
       <c r="G2">
-        <v>0.03904699964600021</v>
+        <v>0.05025350190126426</v>
       </c>
       <c r="H2">
-        <v>0.03904699964600021</v>
+        <v>0.05025350190126426</v>
       </c>
       <c r="I2">
-        <v>0.03404591845999588</v>
+        <v>0.04715695858329336</v>
       </c>
       <c r="J2">
-        <v>0.02838755424672402</v>
+        <v>0.0395179092224999</v>
       </c>
       <c r="K2">
-        <v>904.217</v>
+        <v>850.102</v>
       </c>
       <c r="L2">
-        <v>0.3722007261111888</v>
+        <v>0.3453565276739575</v>
       </c>
       <c r="M2">
-        <v>331.495</v>
+        <v>340.057</v>
       </c>
       <c r="N2">
-        <v>0.01543416519228978</v>
+        <v>0.01751379752911438</v>
       </c>
       <c r="O2">
-        <v>0.3666100062263815</v>
+        <v>0.400019056536745</v>
       </c>
       <c r="P2">
-        <v>331.495</v>
+        <v>340.057</v>
       </c>
       <c r="Q2">
-        <v>0.01543416519228978</v>
+        <v>0.01751379752911438</v>
       </c>
       <c r="R2">
-        <v>0.3666100062263815</v>
+        <v>0.400019056536745</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>617.551</v>
+        <v>621.24</v>
       </c>
       <c r="V2">
-        <v>0.02875272371729212</v>
+        <v>0.03199543481530161</v>
       </c>
       <c r="W2">
-        <v>0.1169462717332514</v>
+        <v>0.1080305927342256</v>
       </c>
       <c r="X2">
-        <v>0.03166187640883158</v>
+        <v>0.06047766712063649</v>
       </c>
       <c r="Y2">
-        <v>0.08528439532441978</v>
+        <v>0.04755292561358915</v>
       </c>
       <c r="Z2">
-        <v>0.159157592427928</v>
+        <v>0.1537544000608181</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0319749767374036</v>
+        <v>0.05959778929253862</v>
       </c>
       <c r="AC2">
-        <v>-0.03122481156220767</v>
+        <v>-0.05852052255000606</v>
       </c>
       <c r="AD2">
-        <v>10947.7</v>
+        <v>12663.8</v>
       </c>
       <c r="AE2">
-        <v>0.5726330582760877</v>
+        <v>0.5910165402585904</v>
       </c>
       <c r="AF2">
-        <v>10948.27263305828</v>
+        <v>12664.39101654026</v>
       </c>
       <c r="AG2">
-        <v>10330.72163305828</v>
+        <v>12043.15101654026</v>
       </c>
       <c r="AH2">
-        <v>0.3376358657361259</v>
+        <v>0.3947640704470879</v>
       </c>
       <c r="AI2">
-        <v>0.662868700250438</v>
+        <v>0.6722724983596186</v>
       </c>
       <c r="AJ2">
-        <v>0.3247763853018767</v>
+        <v>0.382812363492563</v>
       </c>
       <c r="AK2">
-        <v>0.6497737631692568</v>
+        <v>0.6610962293617548</v>
       </c>
       <c r="AL2">
-        <v>22.023</v>
+        <v>32.79</v>
       </c>
       <c r="AM2">
-        <v>20.662</v>
+        <v>31.73</v>
       </c>
       <c r="AN2">
-        <v>125.7416872451617</v>
+        <v>103.830575734221</v>
       </c>
       <c r="AO2">
-        <v>3.742905144621532</v>
+        <v>3.528514791094846</v>
       </c>
       <c r="AP2">
-        <v>118.6552763229573</v>
+        <v>98.74187082088663</v>
       </c>
       <c r="AQ2">
-        <v>3.989449230471397</v>
+        <v>3.646391427670974</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JMT Network Services Public Company Limited (SET:JMT)</t>
+          <t>SG Capital Public Company Limited (SET:SGC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,47 +724,41 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.286</v>
-      </c>
-      <c r="E3">
-        <v>0.6990000000000001</v>
-      </c>
       <c r="G3">
-        <v>0.5783836416747808</v>
+        <v>0.5837742504409171</v>
       </c>
       <c r="H3">
-        <v>0.5783836416747808</v>
+        <v>0.5837742504409171</v>
       </c>
       <c r="I3">
-        <v>0.5676728334956183</v>
+        <v>0.5784832451499118</v>
       </c>
       <c r="J3">
-        <v>0.4881186828860211</v>
+        <v>0.4744174761811446</v>
       </c>
       <c r="K3">
-        <v>37.3</v>
+        <v>15.5</v>
       </c>
       <c r="L3">
-        <v>0.3631937682570593</v>
+        <v>0.27336860670194</v>
       </c>
       <c r="M3">
-        <v>26.4</v>
+        <v>11.7</v>
       </c>
       <c r="N3">
-        <v>0.009400705052878966</v>
+        <v>0.02493606138107417</v>
       </c>
       <c r="O3">
-        <v>0.707774798927614</v>
+        <v>0.7548387096774193</v>
       </c>
       <c r="P3">
-        <v>26.4</v>
+        <v>11.7</v>
       </c>
       <c r="Q3">
-        <v>0.009400705052878966</v>
+        <v>0.02493606138107417</v>
       </c>
       <c r="R3">
-        <v>0.707774798927614</v>
+        <v>0.7548387096774193</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -773,73 +767,58 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>43.6</v>
+        <v>9.25</v>
       </c>
       <c r="V3">
-        <v>0.01552540682975466</v>
-      </c>
-      <c r="W3">
-        <v>0.2345911949685534</v>
+        <v>0.01971440750213129</v>
       </c>
       <c r="X3">
-        <v>0.02694960537904759</v>
-      </c>
-      <c r="Y3">
-        <v>0.2076415895895058</v>
-      </c>
-      <c r="Z3">
-        <v>0.3224186104919474</v>
-      </c>
-      <c r="AA3">
-        <v>0.1573785474912704</v>
+        <v>0.05981370990339367</v>
       </c>
       <c r="AB3">
-        <v>0.02754597235272503</v>
-      </c>
-      <c r="AC3">
-        <v>0.1298325751385454</v>
+        <v>0.06096492252624325</v>
       </c>
       <c r="AD3">
-        <v>294.1</v>
+        <v>313.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>294.1</v>
+        <v>313.8</v>
       </c>
       <c r="AG3">
-        <v>250.5</v>
+        <v>304.55</v>
       </c>
       <c r="AH3">
-        <v>0.09479757607013925</v>
+        <v>0.4007662835249042</v>
       </c>
       <c r="AI3">
-        <v>0.5382503660322108</v>
+        <v>0.8292811839323468</v>
       </c>
       <c r="AJ3">
-        <v>0.08189486072969793</v>
+        <v>0.3936025848142165</v>
       </c>
       <c r="AK3">
-        <v>0.4982100238663484</v>
+        <v>0.8250033861573887</v>
       </c>
       <c r="AL3">
-        <v>9.970000000000001</v>
+        <v>13.8</v>
       </c>
       <c r="AM3">
-        <v>9.970000000000001</v>
+        <v>13.8</v>
       </c>
       <c r="AN3">
-        <v>5.018771331058021</v>
+        <v>9.423423423423424</v>
       </c>
       <c r="AO3">
-        <v>5.847542627883651</v>
+        <v>2.376811594202898</v>
       </c>
       <c r="AP3">
-        <v>4.274744027303755</v>
+        <v>9.145645645645647</v>
       </c>
       <c r="AQ3">
-        <v>5.847542627883651</v>
+        <v>2.376811594202898</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amanah Leasing Public Company Limited (SET:AMANAH)</t>
+          <t>Knight Club Capital Asset Management Public Company Limited (SET:KCC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -858,47 +837,41 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.203</v>
-      </c>
-      <c r="E4">
-        <v>0.867</v>
-      </c>
       <c r="G4">
-        <v>0.5887445887445887</v>
+        <v>0.5071574642126789</v>
       </c>
       <c r="H4">
-        <v>0.5887445887445887</v>
+        <v>0.5071574642126789</v>
       </c>
       <c r="I4">
-        <v>0.5411255411255411</v>
+        <v>0.6871165644171779</v>
       </c>
       <c r="J4">
-        <v>0.4832993803582039</v>
+        <v>0.5507544354170121</v>
       </c>
       <c r="K4">
-        <v>9.15</v>
+        <v>2.07</v>
       </c>
       <c r="L4">
-        <v>0.3961038961038961</v>
+        <v>0.4233128834355828</v>
       </c>
       <c r="M4">
-        <v>3.99</v>
+        <v>0.623</v>
       </c>
       <c r="N4">
-        <v>0.02356763142350856</v>
+        <v>0.004792307692307692</v>
       </c>
       <c r="O4">
-        <v>0.4360655737704918</v>
+        <v>0.3009661835748793</v>
       </c>
       <c r="P4">
-        <v>3.99</v>
+        <v>0.623</v>
       </c>
       <c r="Q4">
-        <v>0.02356763142350856</v>
+        <v>0.004792307692307692</v>
       </c>
       <c r="R4">
-        <v>0.4360655737704918</v>
+        <v>0.3009661835748793</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -907,73 +880,58 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>0.02622563496751329</v>
-      </c>
-      <c r="W4">
-        <v>0.1963519313304721</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>0.02901981894004209</v>
-      </c>
-      <c r="Y4">
-        <v>0.16733211239043</v>
-      </c>
-      <c r="Z4">
-        <v>0.2105167228652146</v>
-      </c>
-      <c r="AA4">
-        <v>0.101742601715798</v>
+        <v>0.05388779307908484</v>
       </c>
       <c r="AB4">
-        <v>0.03009405348541173</v>
-      </c>
-      <c r="AC4">
-        <v>0.07164854823038623</v>
+        <v>0.05488406998577119</v>
       </c>
       <c r="AD4">
-        <v>57.8</v>
+        <v>16.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>57.8</v>
+        <v>16.6</v>
       </c>
       <c r="AG4">
-        <v>53.36</v>
+        <v>16.6</v>
       </c>
       <c r="AH4">
-        <v>0.2545134302069573</v>
+        <v>0.1132332878581173</v>
       </c>
       <c r="AI4">
-        <v>0.5406922357343311</v>
+        <v>0.3656387665198238</v>
       </c>
       <c r="AJ4">
-        <v>0.2396478936495104</v>
+        <v>0.1132332878581173</v>
       </c>
       <c r="AK4">
-        <v>0.5207886004294359</v>
+        <v>0.3656387665198238</v>
       </c>
       <c r="AL4">
-        <v>2.3</v>
+        <v>0.775</v>
       </c>
       <c r="AM4">
-        <v>2.3</v>
+        <v>0.775</v>
       </c>
       <c r="AN4">
-        <v>4.551181102362205</v>
+        <v>4.882352941176471</v>
       </c>
       <c r="AO4">
-        <v>5.434782608695652</v>
+        <v>4.335483870967741</v>
       </c>
       <c r="AP4">
-        <v>4.201574803149606</v>
+        <v>4.882352941176471</v>
       </c>
       <c r="AQ4">
-        <v>5.434782608695652</v>
+        <v>4.335483870967741</v>
       </c>
     </row>
     <row r="5">
@@ -984,7 +942,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IFS Capital (Thailand) Public Company Limited (SET:IFS)</t>
+          <t>JMT Network Services Public Company Limited (SET:JMT)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -993,46 +951,49 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.00482</v>
+        <v>0.273</v>
       </c>
       <c r="E5">
-        <v>0.0139</v>
+        <v>0.274</v>
+      </c>
+      <c r="F5">
+        <v>0.229</v>
       </c>
       <c r="G5">
-        <v>0.7245454545454545</v>
+        <v>0.5297202797202797</v>
       </c>
       <c r="H5">
-        <v>0.7245454545454545</v>
+        <v>0.5297202797202797</v>
       </c>
       <c r="I5">
-        <v>0.6554545454545454</v>
+        <v>0.4956293706293706</v>
       </c>
       <c r="J5">
-        <v>0.5170808080808081</v>
+        <v>0.436193338533976</v>
       </c>
       <c r="K5">
-        <v>4.27</v>
+        <v>45.9</v>
       </c>
       <c r="L5">
-        <v>0.3881818181818181</v>
+        <v>0.4012237762237762</v>
       </c>
       <c r="M5">
-        <v>2.05</v>
+        <v>34.9</v>
       </c>
       <c r="N5">
-        <v>0.0435244161358811</v>
+        <v>0.01198283261802575</v>
       </c>
       <c r="O5">
-        <v>0.4800936768149883</v>
+        <v>0.7603485838779956</v>
       </c>
       <c r="P5">
-        <v>2.05</v>
+        <v>34.9</v>
       </c>
       <c r="Q5">
-        <v>0.0435244161358811</v>
+        <v>0.01198283261802575</v>
       </c>
       <c r="R5">
-        <v>0.4800936768149883</v>
+        <v>0.7603485838779956</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1041,73 +1002,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>13.4</v>
+        <v>34.2</v>
       </c>
       <c r="V5">
-        <v>0.2845010615711253</v>
+        <v>0.01174248927038627</v>
       </c>
       <c r="W5">
-        <v>0.09027484143763213</v>
+        <v>0.1822875297855441</v>
       </c>
       <c r="X5">
-        <v>0.03654468724030398</v>
+        <v>0.05302369140842133</v>
       </c>
       <c r="Y5">
-        <v>0.05373015419732815</v>
+        <v>0.1292638383771227</v>
       </c>
       <c r="Z5">
-        <v>0.1344743276283619</v>
+        <v>0.2315039663266958</v>
       </c>
       <c r="AA5">
-        <v>0.0695340939961967</v>
+        <v>0.1009804879558986</v>
       </c>
       <c r="AB5">
-        <v>0.03272493028049351</v>
+        <v>0.05304520910182675</v>
       </c>
       <c r="AC5">
-        <v>0.03680916371570319</v>
+        <v>0.04793527885407185</v>
       </c>
       <c r="AD5">
-        <v>56.6</v>
+        <v>142.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>56.6</v>
+        <v>142.1</v>
       </c>
       <c r="AG5">
-        <v>43.2</v>
+        <v>107.9</v>
       </c>
       <c r="AH5">
-        <v>0.5458052073288332</v>
+        <v>0.04652000261900085</v>
       </c>
       <c r="AI5">
-        <v>0.5484496124031008</v>
+        <v>0.1918196544276458</v>
       </c>
       <c r="AJ5">
-        <v>0.4784053156146179</v>
+        <v>0.03572374519931135</v>
       </c>
       <c r="AK5">
-        <v>0.4810690423162583</v>
+        <v>0.1527030851967167</v>
       </c>
       <c r="AL5">
-        <v>0.973</v>
+        <v>7.64</v>
       </c>
       <c r="AM5">
-        <v>0.973</v>
+        <v>7.64</v>
       </c>
       <c r="AN5">
-        <v>7.546666666666667</v>
+        <v>2.424914675767918</v>
       </c>
       <c r="AO5">
-        <v>7.410071942446043</v>
+        <v>7.421465968586388</v>
       </c>
       <c r="AP5">
-        <v>5.760000000000001</v>
+        <v>1.841296928327645</v>
       </c>
       <c r="AQ5">
-        <v>7.410071942446043</v>
+        <v>7.421465968586388</v>
       </c>
     </row>
     <row r="6">
@@ -1118,7 +1079,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AIRA Factoring Public Company Limited (SET:AF)</t>
+          <t>Amanah Leasing Public Company Limited (SET:AMANAH)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1127,46 +1088,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.00801</v>
+        <v>0.132</v>
       </c>
       <c r="E6">
-        <v>0.006540000000000001</v>
+        <v>0.506</v>
       </c>
       <c r="G6">
-        <v>0.5834767641996558</v>
+        <v>0.5517241379310345</v>
       </c>
       <c r="H6">
-        <v>0.5834767641996558</v>
+        <v>0.5517241379310345</v>
       </c>
       <c r="I6">
-        <v>0.5421686746987951</v>
+        <v>0.4741379310344828</v>
       </c>
       <c r="J6">
-        <v>0.4343086632243258</v>
+        <v>0.3996525572533343</v>
       </c>
       <c r="K6">
-        <v>1.52</v>
+        <v>7.78</v>
       </c>
       <c r="L6">
-        <v>0.2616179001721171</v>
+        <v>0.3353448275862069</v>
       </c>
       <c r="M6">
-        <v>0.999</v>
+        <v>4.39</v>
       </c>
       <c r="N6">
-        <v>0.01809782608695652</v>
+        <v>0.03874669020300088</v>
       </c>
       <c r="O6">
-        <v>0.6572368421052631</v>
+        <v>0.5642673521850899</v>
       </c>
       <c r="P6">
-        <v>0.999</v>
+        <v>4.39</v>
       </c>
       <c r="Q6">
-        <v>0.01809782608695652</v>
+        <v>0.03874669020300088</v>
       </c>
       <c r="R6">
-        <v>0.6572368421052631</v>
+        <v>0.5642673521850899</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1175,73 +1136,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>3.62</v>
+        <v>1.56</v>
       </c>
       <c r="V6">
-        <v>0.06557971014492754</v>
+        <v>0.01376875551632833</v>
       </c>
       <c r="W6">
-        <v>0.08888888888888888</v>
+        <v>0.1584521384928717</v>
       </c>
       <c r="X6">
-        <v>0.03192821654567073</v>
+        <v>0.05814393930492617</v>
       </c>
       <c r="Y6">
-        <v>0.05696067234321815</v>
+        <v>0.1003081991879455</v>
       </c>
       <c r="Z6">
-        <v>0.1024691358024691</v>
+        <v>0.2264298262736678</v>
       </c>
       <c r="AA6">
-        <v>0.04450323339212228</v>
+        <v>0.09049325910869954</v>
       </c>
       <c r="AB6">
-        <v>0.03343784340879304</v>
+        <v>0.05865549055516051</v>
       </c>
       <c r="AC6">
-        <v>0.01106538998332924</v>
+        <v>0.03183776855353903</v>
       </c>
       <c r="AD6">
-        <v>37.2</v>
+        <v>58.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>37.2</v>
+        <v>58.5</v>
       </c>
       <c r="AG6">
-        <v>33.58000000000001</v>
+        <v>56.94</v>
       </c>
       <c r="AH6">
-        <v>0.4025974025974026</v>
+        <v>0.3405122235157159</v>
       </c>
       <c r="AI6">
-        <v>0.6914498141263941</v>
+        <v>0.5545023696682464</v>
       </c>
       <c r="AJ6">
-        <v>0.378238341968912</v>
+        <v>0.334468984962406</v>
       </c>
       <c r="AK6">
-        <v>0.6691909127142288</v>
+        <v>0.5478160477198384</v>
       </c>
       <c r="AL6">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="AM6">
-        <v>1.029</v>
+        <v>1.96</v>
       </c>
       <c r="AN6">
-        <v>11.96141479099679</v>
+        <v>5.27027027027027</v>
       </c>
       <c r="AO6">
-        <v>3.058252427184466</v>
+        <v>5.612244897959184</v>
       </c>
       <c r="AP6">
-        <v>10.79742765273312</v>
+        <v>5.129729729729729</v>
       </c>
       <c r="AQ6">
-        <v>3.061224489795918</v>
+        <v>5.612244897959184</v>
       </c>
     </row>
     <row r="7">
@@ -1252,7 +1213,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Srisawad Finance Public Company Limited (SET:BFIT)</t>
+          <t>IFS Capital (Thailand) Public Company Limited (SET:IFS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1261,46 +1222,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.5539999999999999</v>
+        <v>0.0104</v>
       </c>
       <c r="E7">
-        <v>0.53</v>
+        <v>0.0159</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.6486486486486487</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.6486486486486487</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>0.6144144144144145</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>0.4897343412882718</v>
       </c>
       <c r="K7">
-        <v>29.8</v>
+        <v>4.35</v>
       </c>
       <c r="L7">
-        <v>0.4641744548286604</v>
+        <v>0.3918918918918919</v>
       </c>
       <c r="M7">
-        <v>23</v>
+        <v>2.07</v>
       </c>
       <c r="N7">
-        <v>0.04756980351602896</v>
+        <v>0.04870588235294118</v>
       </c>
       <c r="O7">
-        <v>0.7718120805369127</v>
+        <v>0.4758620689655172</v>
       </c>
       <c r="P7">
-        <v>23</v>
+        <v>2.07</v>
       </c>
       <c r="Q7">
-        <v>0.04756980351602896</v>
+        <v>0.04870588235294118</v>
       </c>
       <c r="R7">
-        <v>0.7718120805369127</v>
+        <v>0.4758620689655172</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1309,61 +1270,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>17.2</v>
+        <v>13</v>
       </c>
       <c r="V7">
-        <v>0.03557394002068252</v>
+        <v>0.3058823529411765</v>
       </c>
       <c r="W7">
-        <v>0.1007096992227104</v>
+        <v>0.09334763948497853</v>
       </c>
       <c r="X7">
-        <v>0.02621811250225947</v>
+        <v>0.06586308153276384</v>
       </c>
       <c r="Y7">
-        <v>0.07449158672045092</v>
+        <v>0.02748455795221469</v>
       </c>
       <c r="Z7">
-        <v>0.1980259099321407</v>
+        <v>0.1236080178173719</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>0.06053509118373961</v>
       </c>
       <c r="AB7">
-        <v>0.02636319845491849</v>
+        <v>0.05905844009490442</v>
       </c>
       <c r="AC7">
-        <v>-0.02636319845491849</v>
+        <v>0.001476651088835185</v>
       </c>
       <c r="AD7">
-        <v>10.2</v>
+        <v>51.9</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>10.2</v>
+        <v>51.9</v>
       </c>
       <c r="AG7">
-        <v>-7</v>
+        <v>38.9</v>
       </c>
       <c r="AH7">
-        <v>0.02066032003240834</v>
+        <v>0.5497881355932203</v>
       </c>
       <c r="AI7">
-        <v>0.03455284552845529</v>
+        <v>0.542319749216301</v>
       </c>
       <c r="AJ7">
-        <v>-0.01469045120671563</v>
+        <v>0.4778869778869778</v>
       </c>
       <c r="AK7">
-        <v>-0.02517985611510791</v>
+        <v>0.4703748488512697</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.995</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>0.995</v>
+      </c>
+      <c r="AN7">
+        <v>7.330508474576271</v>
+      </c>
+      <c r="AO7">
+        <v>6.85427135678392</v>
+      </c>
+      <c r="AP7">
+        <v>5.494350282485875</v>
+      </c>
+      <c r="AQ7">
+        <v>6.85427135678392</v>
       </c>
     </row>
     <row r="8">
@@ -1374,7 +1347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Thitikorn Public Company Limited (SET:TK)</t>
+          <t>AIRA Factoring Public Company Limited (SET:AF)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1383,46 +1356,46 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.112</v>
+        <v>0.0116</v>
       </c>
       <c r="E8">
-        <v>0.00223</v>
+        <v>0.0733</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.5118243243243243</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.5118243243243243</v>
       </c>
       <c r="I8">
-        <v>0.006237253936826445</v>
+        <v>0.4831081081081081</v>
       </c>
       <c r="J8">
-        <v>0.004719065203851657</v>
+        <v>0.3705628114147667</v>
       </c>
       <c r="K8">
-        <v>13.7</v>
+        <v>1.37</v>
       </c>
       <c r="L8">
-        <v>0.3261904761904762</v>
+        <v>0.2314189189189189</v>
       </c>
       <c r="M8">
-        <v>6.25</v>
+        <v>1.06</v>
       </c>
       <c r="N8">
-        <v>0.04555393586005831</v>
+        <v>0.01992481203007519</v>
       </c>
       <c r="O8">
-        <v>0.4562043795620438</v>
+        <v>0.7737226277372262</v>
       </c>
       <c r="P8">
-        <v>6.25</v>
+        <v>1.06</v>
       </c>
       <c r="Q8">
-        <v>0.04555393586005831</v>
+        <v>0.01992481203007519</v>
       </c>
       <c r="R8">
-        <v>0.4562043795620438</v>
+        <v>0.7737226277372262</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1431,67 +1404,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>30.2</v>
+        <v>4.49</v>
       </c>
       <c r="V8">
-        <v>0.2201166180758018</v>
+        <v>0.0843984962406015</v>
       </c>
       <c r="W8">
-        <v>0.0822328931572629</v>
+        <v>0.0825301204819277</v>
       </c>
       <c r="X8">
-        <v>0.02777659693858684</v>
+        <v>0.06027069792984464</v>
       </c>
       <c r="Y8">
-        <v>0.05445629621867606</v>
+        <v>0.02225942255208306</v>
       </c>
       <c r="Z8">
-        <v>0.2428585468566396</v>
+        <v>0.1179752889597449</v>
       </c>
       <c r="AA8">
-        <v>0.001146065317929145</v>
+        <v>0.04371725475439256</v>
       </c>
       <c r="AB8">
-        <v>0.02807065251339808</v>
+        <v>0.06001130710309337</v>
       </c>
       <c r="AC8">
-        <v>-0.02692458719546894</v>
+        <v>-0.01629405234870081</v>
       </c>
       <c r="AD8">
-        <v>26.8</v>
+        <v>37.8</v>
       </c>
       <c r="AE8">
-        <v>0.5401766732664464</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>27.34017667326645</v>
+        <v>37.8</v>
       </c>
       <c r="AG8">
-        <v>-2.859823326733551</v>
+        <v>33.31</v>
       </c>
       <c r="AH8">
-        <v>0.1661610995322854</v>
+        <v>0.4153846153846154</v>
       </c>
       <c r="AI8">
-        <v>0.142071043302386</v>
+        <v>0.7145557655954631</v>
       </c>
       <c r="AJ8">
-        <v>-0.02128792292486729</v>
+        <v>0.385042191654144</v>
       </c>
       <c r="AK8">
-        <v>-0.01762709697051745</v>
+        <v>0.6880809750051642</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AN8">
-        <v>72.43243243243244</v>
+        <v>13.125</v>
+      </c>
+      <c r="AO8">
+        <v>2.672897196261682</v>
       </c>
       <c r="AP8">
-        <v>-7.729252234415003</v>
+        <v>11.56597222222222</v>
+      </c>
+      <c r="AQ8">
+        <v>2.672897196261682</v>
       </c>
     </row>
     <row r="9">
@@ -1502,7 +1481,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Saksiam Leasing Public Company Limited (SET:SAK)</t>
+          <t>Thitikorn Public Company Limited (SET:TK)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1510,8 +1489,11 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="F9">
-        <v>0.319</v>
+      <c r="D9">
+        <v>-0.0867</v>
+      </c>
+      <c r="E9">
+        <v>-0.00886</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1520,34 +1502,34 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>0.01002105902314486</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>0.007496523000006442</v>
       </c>
       <c r="K9">
-        <v>17.1</v>
+        <v>11.6</v>
       </c>
       <c r="L9">
-        <v>0.3607594936708861</v>
+        <v>0.3143631436314363</v>
       </c>
       <c r="M9">
-        <v>6.73</v>
+        <v>6.62</v>
       </c>
       <c r="N9">
-        <v>0.01060343469355601</v>
+        <v>0.05448559670781893</v>
       </c>
       <c r="O9">
-        <v>0.3935672514619883</v>
+        <v>0.5706896551724138</v>
       </c>
       <c r="P9">
-        <v>6.73</v>
+        <v>6.62</v>
       </c>
       <c r="Q9">
-        <v>0.01060343469355601</v>
+        <v>0.05448559670781893</v>
       </c>
       <c r="R9">
-        <v>0.3935672514619883</v>
+        <v>0.5706896551724138</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1556,61 +1538,67 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>8.73</v>
+        <v>18</v>
       </c>
       <c r="V9">
-        <v>0.01375452969907043</v>
+        <v>0.1481481481481481</v>
       </c>
       <c r="W9">
-        <v>0.2255936675461742</v>
+        <v>0.07051671732522796</v>
       </c>
       <c r="X9">
-        <v>0.02772728526591921</v>
+        <v>0.05382122773781757</v>
       </c>
       <c r="Y9">
-        <v>0.1978663822802549</v>
+        <v>0.01669548958741039</v>
       </c>
       <c r="Z9">
-        <v>0.2330727245906476</v>
+        <v>0.2282340844778392</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>0.001710962063673534</v>
       </c>
       <c r="AB9">
-        <v>0.02862166370780776</v>
+        <v>0.05378490560674654</v>
       </c>
       <c r="AC9">
-        <v>-0.02862166370780776</v>
+        <v>-0.052073943543073</v>
       </c>
       <c r="AD9">
-        <v>122.9</v>
+        <v>14.2</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>0.5761146102297738</v>
       </c>
       <c r="AF9">
-        <v>122.9</v>
+        <v>14.77611461022977</v>
       </c>
       <c r="AG9">
-        <v>114.17</v>
+        <v>-3.223885389770228</v>
       </c>
       <c r="AH9">
-        <v>0.1622228088701162</v>
+        <v>0.1084277655882081</v>
       </c>
       <c r="AI9">
-        <v>0.4676560121765601</v>
+        <v>0.08791323290936212</v>
       </c>
       <c r="AJ9">
-        <v>0.1524563675938414</v>
+        <v>-0.02725728183069172</v>
       </c>
       <c r="AK9">
-        <v>0.4493643484079191</v>
+        <v>-0.02148166880614642</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
         <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>29.27835051546392</v>
+      </c>
+      <c r="AP9">
+        <v>-6.647186370660264</v>
       </c>
     </row>
     <row r="10">
@@ -1621,7 +1609,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Micro Leasing Public Company Limited (SET:MICRO)</t>
+          <t>Krungthai Card Public Company Limited (SET:KTC)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1629,6 +1617,15 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D10">
+        <v>0.08259999999999999</v>
+      </c>
+      <c r="E10">
+        <v>0.173</v>
+      </c>
+      <c r="F10">
+        <v>0.117</v>
+      </c>
       <c r="G10">
         <v>0</v>
       </c>
@@ -1642,28 +1639,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>5.42</v>
+        <v>176.5</v>
       </c>
       <c r="L10">
-        <v>0.4442622950819672</v>
+        <v>0.4189413719439829</v>
       </c>
       <c r="M10">
-        <v>1.53</v>
+        <v>68.3</v>
       </c>
       <c r="N10">
-        <v>0.006695842450765864</v>
+        <v>0.01552061082579648</v>
       </c>
       <c r="O10">
-        <v>0.2822878228782288</v>
+        <v>0.3869688385269122</v>
       </c>
       <c r="P10">
-        <v>1.53</v>
+        <v>68.3</v>
       </c>
       <c r="Q10">
-        <v>0.006695842450765864</v>
+        <v>0.01552061082579648</v>
       </c>
       <c r="R10">
-        <v>0.2822878228782288</v>
+        <v>0.3869688385269122</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1672,55 +1669,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>3.68</v>
+        <v>42.9</v>
       </c>
       <c r="V10">
-        <v>0.01610503282275711</v>
+        <v>0.009748670635822387</v>
       </c>
       <c r="W10">
-        <v>0.09609929078014184</v>
+        <v>0.2323285507437146</v>
       </c>
       <c r="X10">
-        <v>0.02781741250982117</v>
+        <v>0.05628230314351224</v>
       </c>
       <c r="Y10">
-        <v>0.06828187827032067</v>
+        <v>0.1760462476002024</v>
       </c>
       <c r="Z10">
-        <v>0.1713483146067415</v>
+        <v>0.1885517364840673</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.02873605495833514</v>
+        <v>0.05556302924369655</v>
       </c>
       <c r="AC10">
-        <v>-0.02873605495833514</v>
+        <v>-0.05556302924369655</v>
       </c>
       <c r="AD10">
-        <v>46.6</v>
+        <v>1524.1</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>46.6</v>
+        <v>1524.1</v>
       </c>
       <c r="AG10">
-        <v>42.92</v>
+        <v>1481.2</v>
       </c>
       <c r="AH10">
-        <v>0.1693929480189022</v>
+        <v>0.2572450925785271</v>
       </c>
       <c r="AI10">
-        <v>0.4502415458937198</v>
+        <v>0.6578754262528597</v>
       </c>
       <c r="AJ10">
-        <v>0.1581313094097708</v>
+        <v>0.2518276718011493</v>
       </c>
       <c r="AK10">
-        <v>0.4299739531156082</v>
+        <v>0.6514205295100712</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1737,7 +1734,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Srisawad Corporation Public Company Limited (SET:SAWAD)</t>
+          <t>Saksiam Leasing Public Company Limited (SET:SAK)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1745,15 +1742,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D11">
-        <v>0.182</v>
-      </c>
-      <c r="E11">
-        <v>0.221</v>
-      </c>
-      <c r="F11">
-        <v>0.166</v>
-      </c>
       <c r="G11">
         <v>0</v>
       </c>
@@ -1761,34 +1749,34 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>2.730579999912908e-06</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>2.152686910332988e-06</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>144.8</v>
+        <v>18.2</v>
       </c>
       <c r="L11">
-        <v>0.4893545116593445</v>
+        <v>0.3540856031128405</v>
       </c>
       <c r="M11">
-        <v>73.5</v>
+        <v>6.44</v>
       </c>
       <c r="N11">
-        <v>0.02890969162995595</v>
+        <v>0.01741011084076778</v>
       </c>
       <c r="O11">
-        <v>0.5075966850828729</v>
+        <v>0.3538461538461539</v>
       </c>
       <c r="P11">
-        <v>73.5</v>
+        <v>6.44</v>
       </c>
       <c r="Q11">
-        <v>0.02890969162995595</v>
+        <v>0.01741011084076778</v>
       </c>
       <c r="R11">
-        <v>0.5075966850828729</v>
+        <v>0.3538461538461539</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1797,67 +1785,61 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>63.9</v>
+        <v>7.77</v>
       </c>
       <c r="V11">
-        <v>0.02513373190685966</v>
+        <v>0.02100567721005677</v>
       </c>
       <c r="W11">
-        <v>0.2197268588770865</v>
+        <v>0.1300929235167977</v>
       </c>
       <c r="X11">
-        <v>0.02803418215972561</v>
+        <v>0.05709616468160044</v>
       </c>
       <c r="Y11">
-        <v>0.1916926767173609</v>
+        <v>0.07299675883519727</v>
       </c>
       <c r="Z11">
-        <v>0.2359647316177315</v>
+        <v>0.2023064509780769</v>
       </c>
       <c r="AA11">
-        <v>5.079581890537272e-07</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.02900332684810186</v>
+        <v>0.05602726932696543</v>
       </c>
       <c r="AC11">
-        <v>-0.02900281888991281</v>
+        <v>-0.05602726932696543</v>
       </c>
       <c r="AD11">
-        <v>581.5</v>
+        <v>155.6</v>
       </c>
       <c r="AE11">
-        <v>0.0009601068901288523</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>581.5009601068901</v>
+        <v>155.6</v>
       </c>
       <c r="AG11">
-        <v>517.6009601068902</v>
+        <v>147.83</v>
       </c>
       <c r="AH11">
-        <v>0.1861457733560775</v>
+        <v>0.2960989533777355</v>
       </c>
       <c r="AI11">
-        <v>0.4316363908030116</v>
+        <v>0.5321477428180574</v>
       </c>
       <c r="AJ11">
-        <v>0.1691505874850476</v>
+        <v>0.2855349313348656</v>
       </c>
       <c r="AK11">
-        <v>0.403335597959638</v>
+        <v>0.5193760320415978</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
         <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>581500</v>
-      </c>
-      <c r="AP11">
-        <v>517600.9601068902</v>
       </c>
     </row>
     <row r="12">
@@ -1868,7 +1850,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Krungthai Card Public Company Limited (SET:KTC)</t>
+          <t>Srisawad Corporation Public Company Limited (SET:SAWAD)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1877,10 +1859,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.08650000000000001</v>
+        <v>0.108</v>
       </c>
       <c r="E12">
-        <v>0.2</v>
+        <v>0.1</v>
+      </c>
+      <c r="F12">
+        <v>0.12</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1895,28 +1880,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>177</v>
+        <v>116.7</v>
       </c>
       <c r="L12">
-        <v>0.4066161268090971</v>
+        <v>0.4197841726618705</v>
       </c>
       <c r="M12">
-        <v>67.5</v>
+        <v>65.5</v>
       </c>
       <c r="N12">
-        <v>0.01473638249099443</v>
+        <v>0.03382390911438161</v>
       </c>
       <c r="O12">
-        <v>0.3813559322033898</v>
+        <v>0.5612682090831191</v>
       </c>
       <c r="P12">
-        <v>67.5</v>
+        <v>65.5</v>
       </c>
       <c r="Q12">
-        <v>0.01473638249099443</v>
+        <v>0.03382390911438161</v>
       </c>
       <c r="R12">
-        <v>0.3813559322033898</v>
+        <v>0.5612682090831191</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1925,55 +1910,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>43</v>
+        <v>92.8</v>
       </c>
       <c r="V12">
-        <v>0.009387621438707564</v>
+        <v>0.04792150787503227</v>
       </c>
       <c r="W12">
-        <v>0.2605623435889887</v>
+        <v>0.1665952890792291</v>
       </c>
       <c r="X12">
-        <v>0.02893176931956295</v>
+        <v>0.05732409087725115</v>
       </c>
       <c r="Y12">
-        <v>0.2316305742694257</v>
+        <v>0.109271198201978</v>
       </c>
       <c r="Z12">
-        <v>0.1843554125021176</v>
+        <v>0.2282242837205484</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.03000412627802169</v>
+        <v>0.05614870219420283</v>
       </c>
       <c r="AC12">
-        <v>-0.03000412627802169</v>
+        <v>-0.05614870219420283</v>
       </c>
       <c r="AD12">
-        <v>1517.7</v>
+        <v>854.9</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>1517.7</v>
+        <v>854.9</v>
       </c>
       <c r="AG12">
-        <v>1474.7</v>
+        <v>762.1</v>
       </c>
       <c r="AH12">
-        <v>0.248876717719983</v>
+        <v>0.306262090707172</v>
       </c>
       <c r="AI12">
-        <v>0.6632144729942318</v>
+        <v>0.5379097715975587</v>
       </c>
       <c r="AJ12">
-        <v>0.2435427401241908</v>
+        <v>0.2824056918402135</v>
       </c>
       <c r="AK12">
-        <v>0.6567649416585019</v>
+        <v>0.50925492816572</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1990,7 +1975,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Next Capital Public Company Limited (SET:NCAP)</t>
+          <t>Srisawad Capital 1969 Public Company Limited (SET:SCAP)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1998,8 +1983,11 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="F13">
-        <v>0.375</v>
+      <c r="D13">
+        <v>0.3779999999999999</v>
+      </c>
+      <c r="E13">
+        <v>0.216</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2014,28 +2002,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>8.5</v>
+        <v>14.3</v>
       </c>
       <c r="L13">
-        <v>0.4450261780104712</v>
+        <v>0.2530973451327434</v>
       </c>
       <c r="M13">
-        <v>2.97</v>
+        <v>12</v>
       </c>
       <c r="N13">
-        <v>0.01106145251396648</v>
+        <v>0.01191776740490615</v>
       </c>
       <c r="O13">
-        <v>0.3494117647058824</v>
+        <v>0.8391608391608392</v>
       </c>
       <c r="P13">
-        <v>2.97</v>
+        <v>12</v>
       </c>
       <c r="Q13">
-        <v>0.01106145251396648</v>
+        <v>0.01191776740490615</v>
       </c>
       <c r="R13">
-        <v>0.3494117647058824</v>
+        <v>0.8391608391608392</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2044,55 +2032,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="V13">
-        <v>0.0074487895716946</v>
+        <v>0.05164365875459331</v>
       </c>
       <c r="W13">
-        <v>0.2768729641693811</v>
+        <v>0.05017543859649123</v>
       </c>
       <c r="X13">
-        <v>0.02863647298915012</v>
+        <v>0.0563244072321989</v>
       </c>
       <c r="Y13">
-        <v>0.248236491180231</v>
+        <v>-0.006148968635707672</v>
       </c>
       <c r="Z13">
-        <v>0.1671011880806985</v>
+        <v>0.2032374100719425</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.03025132030639145</v>
+        <v>0.05718595759361757</v>
       </c>
       <c r="AC13">
-        <v>-0.03025132030639145</v>
+        <v>-0.05718595759361757</v>
       </c>
       <c r="AD13">
-        <v>79.90000000000001</v>
+        <v>352.6</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>79.90000000000001</v>
+        <v>352.6</v>
       </c>
       <c r="AG13">
-        <v>77.90000000000001</v>
+        <v>300.6</v>
       </c>
       <c r="AH13">
-        <v>0.2293340987370839</v>
+        <v>0.2593600588451637</v>
       </c>
       <c r="AI13">
-        <v>0.5840643274853801</v>
+        <v>0.5536190924791961</v>
       </c>
       <c r="AJ13">
-        <v>0.2248845265588915</v>
+        <v>0.2299043977055449</v>
       </c>
       <c r="AK13">
-        <v>0.5778931750741839</v>
+        <v>0.5139340058129594</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2109,7 +2097,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S 11 Group Public Company Limited (SET:S11)</t>
+          <t>Ngern Tid Lor Public Company Limited (SET:TIDLOR)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2117,12 +2105,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D14">
-        <v>0.0281</v>
-      </c>
-      <c r="E14">
-        <v>-0.00776</v>
-      </c>
       <c r="G14">
         <v>0</v>
       </c>
@@ -2136,28 +2118,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>11.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L14">
-        <v>0.3973063973063973</v>
+        <v>0.2763688760806917</v>
       </c>
       <c r="M14">
-        <v>4.56</v>
+        <v>16.8</v>
       </c>
       <c r="N14">
-        <v>0.03815899581589958</v>
+        <v>0.007882882882882884</v>
       </c>
       <c r="O14">
-        <v>0.3864406779661017</v>
+        <v>0.1751824817518248</v>
       </c>
       <c r="P14">
-        <v>4.56</v>
+        <v>16.8</v>
       </c>
       <c r="Q14">
-        <v>0.03815899581589958</v>
+        <v>0.007882882882882884</v>
       </c>
       <c r="R14">
-        <v>0.3864406779661017</v>
+        <v>0.1751824817518248</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2166,55 +2148,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>1.18</v>
+        <v>48.1</v>
       </c>
       <c r="V14">
-        <v>0.009874476987447698</v>
+        <v>0.02256944444444445</v>
       </c>
       <c r="W14">
-        <v>0.1331828442437923</v>
+        <v>0.149144634525661</v>
       </c>
       <c r="X14">
-        <v>0.03176479949825184</v>
+        <v>0.05961411332471581</v>
       </c>
       <c r="Y14">
-        <v>0.1014180447455405</v>
+        <v>0.08953052120094518</v>
       </c>
       <c r="Z14">
-        <v>0.145838448318193</v>
+        <v>0.2098629540478754</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.0308865961620241</v>
+        <v>0.05719881400983738</v>
       </c>
       <c r="AC14">
-        <v>-0.0308865961620241</v>
+        <v>-0.05719881400983738</v>
       </c>
       <c r="AD14">
-        <v>78.3</v>
+        <v>1386.5</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>78.3</v>
+        <v>1386.5</v>
       </c>
       <c r="AG14">
-        <v>77.11999999999999</v>
+        <v>1338.4</v>
       </c>
       <c r="AH14">
-        <v>0.3958543983822042</v>
+        <v>0.3941495863774626</v>
       </c>
       <c r="AI14">
-        <v>0.4638625592417061</v>
+        <v>0.6802570895888529</v>
       </c>
       <c r="AJ14">
-        <v>0.3922286644288475</v>
+        <v>0.3857505187917916</v>
       </c>
       <c r="AK14">
-        <v>0.4600882949528695</v>
+        <v>0.6725290186422793</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2231,7 +2213,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Muangthai Capital Public Company Limited (SET:MTC)</t>
+          <t>S 11 Group Public Company Limited (SET:S11)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2240,13 +2222,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.318</v>
+        <v>-0.024</v>
       </c>
       <c r="E15">
-        <v>0.337</v>
-      </c>
-      <c r="F15">
-        <v>0.194</v>
+        <v>-0.0184</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2261,28 +2240,28 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>155.1</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="L15">
-        <v>0.3995363214837713</v>
+        <v>0.4361990950226244</v>
       </c>
       <c r="M15">
-        <v>23.3</v>
+        <v>4.22</v>
       </c>
       <c r="N15">
-        <v>0.006239121703039229</v>
+        <v>0.04757609921082299</v>
       </c>
       <c r="O15">
-        <v>0.1502256608639587</v>
+        <v>0.437759336099585</v>
       </c>
       <c r="P15">
-        <v>23.3</v>
+        <v>4.22</v>
       </c>
       <c r="Q15">
-        <v>0.006239121703039229</v>
+        <v>0.04757609921082299</v>
       </c>
       <c r="R15">
-        <v>0.1502256608639587</v>
+        <v>0.437759336099585</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2291,55 +2270,55 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>45.2</v>
+        <v>1.62</v>
       </c>
       <c r="V15">
-        <v>0.0121033605569688</v>
+        <v>0.01826381059751973</v>
       </c>
       <c r="W15">
-        <v>0.2535971223021583</v>
+        <v>0.1065193370165746</v>
       </c>
       <c r="X15">
-        <v>0.03067321053819775</v>
+        <v>0.06047766712063649</v>
       </c>
       <c r="Y15">
-        <v>0.2229239117639605</v>
+        <v>0.04604166989593811</v>
       </c>
       <c r="Z15">
-        <v>0.1737456921630936</v>
+        <v>0.1318458417849899</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.03156302696239124</v>
+        <v>0.05752887031700117</v>
       </c>
       <c r="AC15">
-        <v>-0.03156302696239124</v>
+        <v>-0.05752887031700117</v>
       </c>
       <c r="AD15">
-        <v>1980.9</v>
+        <v>64.7</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>1980.9</v>
+        <v>64.7</v>
       </c>
       <c r="AG15">
-        <v>1935.7</v>
+        <v>63.08000000000001</v>
       </c>
       <c r="AH15">
-        <v>0.3465899149665815</v>
+        <v>0.4217731421121252</v>
       </c>
       <c r="AI15">
-        <v>0.7371613575468891</v>
+        <v>0.4290450928381963</v>
       </c>
       <c r="AJ15">
-        <v>0.3413812563930726</v>
+        <v>0.4156015285281329</v>
       </c>
       <c r="AK15">
-        <v>0.732664647993944</v>
+        <v>0.4228448853733744</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2356,7 +2335,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ngern Tid Lor Public Company Limited (SET:TIDLOR)</t>
+          <t>Heng Leasing and Capital Public Company Limited (SET:HENG)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2364,9 +2343,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="F16">
-        <v>0.262</v>
-      </c>
       <c r="G16">
         <v>0</v>
       </c>
@@ -2380,82 +2356,85 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>89.09999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="L16">
-        <v>0.2870489690721649</v>
+        <v>0.2588832487309645</v>
       </c>
       <c r="M16">
-        <v>-0</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>-0</v>
+        <v>0.003117283950617284</v>
       </c>
       <c r="O16">
-        <v>-0</v>
+        <v>0.09901960784313726</v>
       </c>
       <c r="P16">
-        <v>-0</v>
+        <v>1.01</v>
       </c>
       <c r="Q16">
-        <v>-0</v>
+        <v>0.003117283950617284</v>
       </c>
       <c r="R16">
-        <v>-0</v>
+        <v>0.09901960784313726</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
       <c r="U16">
-        <v>122.5</v>
+        <v>3.61</v>
       </c>
       <c r="V16">
-        <v>0.04826825328027109</v>
+        <v>0.01114197530864197</v>
       </c>
       <c r="W16">
-        <v>0.2576633892423366</v>
+        <v>0.1083953241232731</v>
       </c>
       <c r="X16">
-        <v>0.02996845484171226</v>
+        <v>0.05795835944536275</v>
       </c>
       <c r="Y16">
-        <v>0.2276949344006243</v>
+        <v>0.05043696467791037</v>
       </c>
       <c r="Z16">
-        <v>0.206260922725249</v>
+        <v>0.1566363730331004</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.0317399825521309</v>
+        <v>0.05852052255000606</v>
       </c>
       <c r="AC16">
-        <v>-0.0317399825521309</v>
+        <v>-0.05852052255000606</v>
       </c>
       <c r="AD16">
-        <v>1141.7</v>
+        <v>161.8</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>1141.7</v>
+        <v>161.8</v>
       </c>
       <c r="AG16">
-        <v>1019.2</v>
+        <v>158.19</v>
       </c>
       <c r="AH16">
-        <v>0.3102782911185998</v>
+        <v>0.3330588719637711</v>
       </c>
       <c r="AI16">
-        <v>0.6397153583235278</v>
+        <v>0.5482887156895967</v>
       </c>
       <c r="AJ16">
-        <v>0.286525540468359</v>
+        <v>0.3280657002426429</v>
       </c>
       <c r="AK16">
-        <v>0.613163277583925</v>
+        <v>0.5426944320559882</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2472,7 +2451,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SGF Capital Public Company Limited (SET:SGF)</t>
+          <t>Muangthai Capital Public Company Limited (SET:MTC)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2481,10 +2460,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.215</v>
+        <v>0.207</v>
       </c>
       <c r="E17">
-        <v>0.0867</v>
+        <v>0.177</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2499,82 +2478,85 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>2.23</v>
+        <v>134.1</v>
       </c>
       <c r="L17">
-        <v>0.2808564231738035</v>
+        <v>0.3568387440127727</v>
       </c>
       <c r="M17">
-        <v>-0</v>
+        <v>20.8</v>
       </c>
       <c r="N17">
-        <v>-0</v>
+        <v>0.008925506350841057</v>
       </c>
       <c r="O17">
-        <v>-0</v>
+        <v>0.1551081282624907</v>
       </c>
       <c r="P17">
-        <v>-0</v>
+        <v>20.8</v>
       </c>
       <c r="Q17">
-        <v>-0</v>
+        <v>0.008925506350841057</v>
       </c>
       <c r="R17">
-        <v>-0</v>
+        <v>0.1551081282624907</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
       <c r="U17">
-        <v>1.44</v>
+        <v>96.8</v>
       </c>
       <c r="V17">
-        <v>0.03214285714285715</v>
+        <v>0.04153793340199107</v>
       </c>
       <c r="W17">
-        <v>0.04247619047619047</v>
+        <v>0.1898626645901175</v>
       </c>
       <c r="X17">
-        <v>0.03155895331941132</v>
+        <v>0.06410207458992499</v>
       </c>
       <c r="Y17">
-        <v>0.01091723715677916</v>
+        <v>0.1257605900001925</v>
       </c>
       <c r="Z17">
-        <v>0.1209259823332318</v>
+        <v>0.1422407267221802</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.0322099709226763</v>
+        <v>0.05863861681996427</v>
       </c>
       <c r="AC17">
-        <v>-0.0322099709226763</v>
+        <v>-0.05863861681996427</v>
       </c>
       <c r="AD17">
-        <v>28.3</v>
+        <v>2471.1</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>28.3</v>
+        <v>2471.1</v>
       </c>
       <c r="AG17">
-        <v>26.86</v>
+        <v>2374.3</v>
       </c>
       <c r="AH17">
-        <v>0.3871409028727771</v>
+        <v>0.5146516713527023</v>
       </c>
       <c r="AI17">
-        <v>0.3546365914786967</v>
+        <v>0.7690225002334048</v>
       </c>
       <c r="AJ17">
-        <v>0.3748255651688529</v>
+        <v>0.5046655472187387</v>
       </c>
       <c r="AK17">
-        <v>0.3427769270035733</v>
+        <v>0.7618482271779239</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2591,7 +2573,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ratchthani Leasing Public Company Limited (SET:THANI)</t>
+          <t>Mida Assets Public Company Limited (SET:MIDA)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2600,109 +2582,115 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.131</v>
-      </c>
-      <c r="E18">
-        <v>0.164</v>
+        <v>-0.0396</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>0.08856015779092702</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>0.08856015779092702</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>0.04260355029585799</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>0.04260355029585799</v>
       </c>
       <c r="K18">
-        <v>51.6</v>
+        <v>-5.38</v>
       </c>
       <c r="L18">
-        <v>0.6378244746600742</v>
+        <v>-0.1061143984220907</v>
       </c>
       <c r="M18">
-        <v>28.6</v>
+        <v>-0</v>
       </c>
       <c r="N18">
-        <v>0.03845636681457577</v>
+        <v>-0</v>
       </c>
       <c r="O18">
-        <v>0.5542635658914729</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>28.6</v>
+        <v>-0</v>
       </c>
       <c r="Q18">
-        <v>0.03845636681457577</v>
+        <v>-0</v>
       </c>
       <c r="R18">
-        <v>0.5542635658914729</v>
+        <v>0</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
       <c r="U18">
-        <v>24.7</v>
+        <v>3.23</v>
       </c>
       <c r="V18">
-        <v>0.03321231679440634</v>
+        <v>0.096996996996997</v>
       </c>
       <c r="W18">
-        <v>0.1928971962616823</v>
+        <v>-0.04967682363804247</v>
       </c>
       <c r="X18">
-        <v>0.03901099180182555</v>
+        <v>0.09968275883748498</v>
       </c>
       <c r="Y18">
-        <v>0.1538862044598567</v>
+        <v>-0.1493595824755274</v>
       </c>
       <c r="Z18">
-        <v>0.05479916006231796</v>
+        <v>0.197506817296455</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>0.008414491624464357</v>
       </c>
       <c r="AB18">
-        <v>0.03335707892603475</v>
+        <v>0.06718705372537358</v>
       </c>
       <c r="AC18">
-        <v>-0.03335707892603475</v>
+        <v>-0.05877256210090922</v>
       </c>
       <c r="AD18">
-        <v>1103.4</v>
+        <v>143.5</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>1103.4</v>
+        <v>143.5</v>
       </c>
       <c r="AG18">
-        <v>1078.7</v>
+        <v>140.27</v>
       </c>
       <c r="AH18">
-        <v>0.5973688484651616</v>
+        <v>0.8116515837104072</v>
       </c>
       <c r="AI18">
-        <v>0.7695097287119046</v>
+        <v>0.5338541666666666</v>
       </c>
       <c r="AJ18">
-        <v>0.5919117647058824</v>
+        <v>0.8081465691075648</v>
       </c>
       <c r="AK18">
-        <v>0.7654697700823162</v>
+        <v>0.5281846594118312</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>5.49</v>
+      </c>
+      <c r="AN18">
+        <v>28.08219178082192</v>
+      </c>
+      <c r="AO18">
+        <v>0.3297709923664122</v>
+      </c>
+      <c r="AP18">
+        <v>27.45009784735812</v>
+      </c>
+      <c r="AQ18">
+        <v>0.3934426229508197</v>
       </c>
     </row>
     <row r="19">
@@ -2713,7 +2701,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Eastern Commercial Leasing Public Company Limited (SET:ECL)</t>
+          <t>AEON Thana Sinsap (Thailand) Public Company Limited (SET:AEONTS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2722,10 +2710,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.219</v>
+        <v>0.0261</v>
       </c>
       <c r="E19">
-        <v>0.5570000000000001</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2734,34 +2722,34 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0.0006345721235944322</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>0.000501754702376993</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>4.42</v>
+        <v>102.5</v>
       </c>
       <c r="L19">
-        <v>0.2728395061728395</v>
+        <v>0.298572676958928</v>
       </c>
       <c r="M19">
-        <v>3.3</v>
+        <v>35.7</v>
       </c>
       <c r="N19">
-        <v>0.03423236514522821</v>
+        <v>0.02712353745631363</v>
       </c>
       <c r="O19">
-        <v>0.746606334841629</v>
+        <v>0.3482926829268293</v>
       </c>
       <c r="P19">
-        <v>3.3</v>
+        <v>35.7</v>
       </c>
       <c r="Q19">
-        <v>0.03423236514522821</v>
+        <v>0.02712353745631363</v>
       </c>
       <c r="R19">
-        <v>0.746606334841629</v>
+        <v>0.3482926829268293</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2770,67 +2758,61 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>0.65</v>
+        <v>114.4</v>
       </c>
       <c r="V19">
-        <v>0.006742738589211618</v>
+        <v>0.08691688193283696</v>
       </c>
       <c r="W19">
-        <v>0.08095238095238094</v>
+        <v>0.1823843416370107</v>
       </c>
       <c r="X19">
-        <v>0.03450993879513315</v>
+        <v>0.06857381024299018</v>
       </c>
       <c r="Y19">
-        <v>0.04644244215724779</v>
+        <v>0.1138105313940205</v>
       </c>
       <c r="Z19">
-        <v>0.08160033379527294</v>
+        <v>0.1398199812650185</v>
       </c>
       <c r="AA19">
-        <v>4.094335119731045e-05</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.03388521676453</v>
+        <v>0.05959778929253862</v>
       </c>
       <c r="AC19">
-        <v>-0.0338442734133327</v>
+        <v>-0.05959778929253862</v>
       </c>
       <c r="AD19">
-        <v>93.40000000000001</v>
+        <v>1933.1</v>
       </c>
       <c r="AE19">
-        <v>0.01859965798885099</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>93.41859965798886</v>
+        <v>1933.1</v>
       </c>
       <c r="AG19">
-        <v>92.76859965798886</v>
+        <v>1818.7</v>
       </c>
       <c r="AH19">
-        <v>0.492146711788563</v>
+        <v>0.5949281383682639</v>
       </c>
       <c r="AI19">
-        <v>0.6410890571090339</v>
+        <v>0.762263406940063</v>
       </c>
       <c r="AJ19">
-        <v>0.4904016830790718</v>
+        <v>0.5801460971641839</v>
       </c>
       <c r="AK19">
-        <v>0.6394809068033914</v>
+        <v>0.7510323752890651</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
         <v>0</v>
-      </c>
-      <c r="AN19">
-        <v>6671.428571428572</v>
-      </c>
-      <c r="AP19">
-        <v>6626.328546999204</v>
       </c>
     </row>
     <row r="20">
@@ -2841,7 +2823,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Asia Sermkij Leasing Public Company Limited (SET:ASK)</t>
+          <t>Micro Leasing Public Company Limited (SET:MICRO)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2849,12 +2831,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D20">
-        <v>0.08839999999999999</v>
-      </c>
-      <c r="E20">
-        <v>0.08740000000000001</v>
-      </c>
       <c r="G20">
         <v>0</v>
       </c>
@@ -2868,28 +2844,28 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>32.1</v>
+        <v>3.29</v>
       </c>
       <c r="L20">
-        <v>0.4686131386861314</v>
+        <v>0.2284722222222222</v>
       </c>
       <c r="M20">
-        <v>17.8</v>
+        <v>1.91</v>
       </c>
       <c r="N20">
-        <v>0.02541767813794088</v>
+        <v>0.01642304385210662</v>
       </c>
       <c r="O20">
-        <v>0.5545171339563862</v>
+        <v>0.5805471124620061</v>
       </c>
       <c r="P20">
-        <v>17.8</v>
+        <v>1.91</v>
       </c>
       <c r="Q20">
-        <v>0.02541767813794088</v>
+        <v>0.01642304385210662</v>
       </c>
       <c r="R20">
-        <v>0.5545171339563862</v>
+        <v>0.5805471124620061</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -2898,55 +2874,55 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>14.5</v>
+        <v>7.35</v>
       </c>
       <c r="V20">
-        <v>0.02070541196630016</v>
+        <v>0.06319862424763542</v>
       </c>
       <c r="W20">
-        <v>0.1853348729792148</v>
+        <v>0.05782073813708261</v>
       </c>
       <c r="X20">
-        <v>0.04174872532200896</v>
+        <v>0.05978723025297186</v>
       </c>
       <c r="Y20">
-        <v>0.1435861476572058</v>
+        <v>-0.001966492115889257</v>
       </c>
       <c r="Z20">
-        <v>0.05158482126047699</v>
+        <v>0.1442596674013224</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.03390951506172515</v>
+        <v>0.05973084811485634</v>
       </c>
       <c r="AC20">
-        <v>-0.03390951506172515</v>
+        <v>-0.05973084811485634</v>
       </c>
       <c r="AD20">
-        <v>1258.2</v>
+        <v>77.5</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>1258.2</v>
+        <v>77.5</v>
       </c>
       <c r="AG20">
-        <v>1243.7</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="AH20">
-        <v>0.6424304314526423</v>
+        <v>0.3998968008255934</v>
       </c>
       <c r="AI20">
-        <v>0.8259699336965797</v>
+        <v>0.5762081784386617</v>
       </c>
       <c r="AJ20">
-        <v>0.6397633744855967</v>
+        <v>0.3762402788951462</v>
       </c>
       <c r="AK20">
-        <v>0.824297454931071</v>
+        <v>0.5517105780574125</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2963,7 +2939,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mida Assets Public Company Limited (SET:MIDA)</t>
+          <t>Ratchthani Leasing Public Company Limited (SET:THANI)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2972,115 +2948,109 @@
         </is>
       </c>
       <c r="D21">
-        <v>-0.05769999999999999</v>
+        <v>0.115</v>
+      </c>
+      <c r="E21">
+        <v>0.122</v>
       </c>
       <c r="G21">
-        <v>0.1788756388415673</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>0.1788756388415673</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>0.02163543441226576</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>0.02163543441226576</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>-7.26</v>
+        <v>49.1</v>
       </c>
       <c r="L21">
-        <v>-0.1236797274275979</v>
+        <v>0.6084262701363073</v>
       </c>
       <c r="M21">
-        <v>-0</v>
+        <v>25.5</v>
       </c>
       <c r="N21">
-        <v>-0</v>
+        <v>0.03741746148202495</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>0.5193482688391039</v>
       </c>
       <c r="P21">
-        <v>-0</v>
+        <v>25.5</v>
       </c>
       <c r="Q21">
-        <v>-0</v>
+        <v>0.03741746148202495</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>0.5193482688391039</v>
       </c>
       <c r="S21">
         <v>0</v>
       </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
       <c r="U21">
-        <v>7.3</v>
+        <v>29.7</v>
       </c>
       <c r="V21">
-        <v>0.1802469135802469</v>
+        <v>0.04358033749082905</v>
       </c>
       <c r="W21">
-        <v>-0.05916870415647921</v>
+        <v>0.1485627836611195</v>
       </c>
       <c r="X21">
-        <v>0.05966044132639566</v>
+        <v>0.06987035293911362</v>
       </c>
       <c r="Y21">
-        <v>-0.1188291454828749</v>
+        <v>0.07869243072200591</v>
       </c>
       <c r="Z21">
-        <v>0.2116306738291812</v>
+        <v>0.05726653420380358</v>
       </c>
       <c r="AA21">
-        <v>0.004578721563254858</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.03869420292116586</v>
+        <v>0.0598192735093507</v>
       </c>
       <c r="AC21">
-        <v>-0.034115481357911</v>
+        <v>-0.0598192735093507</v>
       </c>
       <c r="AD21">
-        <v>155.7</v>
+        <v>1081.6</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>155.7</v>
+        <v>1081.6</v>
       </c>
       <c r="AG21">
-        <v>148.4</v>
+        <v>1051.9</v>
       </c>
       <c r="AH21">
-        <v>0.7935779816513762</v>
+        <v>0.6134649197436334</v>
       </c>
       <c r="AI21">
-        <v>0.5176196808510639</v>
+        <v>0.7727922263503858</v>
       </c>
       <c r="AJ21">
-        <v>0.7856008470089995</v>
+        <v>0.6068420445367485</v>
       </c>
       <c r="AK21">
-        <v>0.5056218057921634</v>
+        <v>0.7678662676107745</v>
       </c>
       <c r="AL21">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="AM21">
-        <v>6.39</v>
-      </c>
-      <c r="AN21">
-        <v>32.71008403361344</v>
-      </c>
-      <c r="AO21">
-        <v>0.1638709677419355</v>
-      </c>
-      <c r="AP21">
-        <v>31.17647058823529</v>
-      </c>
-      <c r="AQ21">
-        <v>0.1987480438184664</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3091,7 +3061,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mida Leasing Public Company Limited (SET:ML)</t>
+          <t>SGF Capital Public Company Limited (SET:SGF)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3100,10 +3070,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>-0.0242</v>
+        <v>0.0876</v>
       </c>
       <c r="E22">
-        <v>-0.00676</v>
+        <v>-0.109</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3118,85 +3088,82 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>3.62</v>
+        <v>1.26</v>
       </c>
       <c r="L22">
-        <v>0.3584158415841585</v>
+        <v>0.1752433936022253</v>
       </c>
       <c r="M22">
-        <v>1.58</v>
+        <v>-0</v>
       </c>
       <c r="N22">
-        <v>0.03511111111111111</v>
+        <v>-0</v>
       </c>
       <c r="O22">
-        <v>0.4364640883977901</v>
+        <v>-0</v>
       </c>
       <c r="P22">
-        <v>1.58</v>
+        <v>-0</v>
       </c>
       <c r="Q22">
-        <v>0.03511111111111111</v>
+        <v>-0</v>
       </c>
       <c r="R22">
-        <v>0.4364640883977901</v>
+        <v>-0</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
       <c r="U22">
-        <v>4.44</v>
+        <v>1.52</v>
       </c>
       <c r="V22">
-        <v>0.09866666666666668</v>
+        <v>0.05277777777777778</v>
       </c>
       <c r="W22">
-        <v>0.05829307568438003</v>
+        <v>0.02446601941747573</v>
       </c>
       <c r="X22">
-        <v>0.03744339249932031</v>
+        <v>0.06165364463654884</v>
       </c>
       <c r="Y22">
-        <v>0.02084968318505972</v>
+        <v>-0.03718762521907311</v>
       </c>
       <c r="Z22">
-        <v>0.08646519989726907</v>
+        <v>0.09175599795814192</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.03506435259248976</v>
+        <v>0.06073911746987637</v>
       </c>
       <c r="AC22">
-        <v>-0.03506435259248976</v>
+        <v>-0.06073911746987637</v>
       </c>
       <c r="AD22">
-        <v>58.7</v>
+        <v>24.1</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>58.7</v>
+        <v>24.1</v>
       </c>
       <c r="AG22">
-        <v>54.26000000000001</v>
+        <v>22.58</v>
       </c>
       <c r="AH22">
-        <v>0.5660559305689489</v>
+        <v>0.4555765595463138</v>
       </c>
       <c r="AI22">
-        <v>0.492863140218304</v>
+        <v>0.338008415147265</v>
       </c>
       <c r="AJ22">
-        <v>0.5466451742897441</v>
+        <v>0.4394706111327365</v>
       </c>
       <c r="AK22">
-        <v>0.4732251875109019</v>
+        <v>0.3235884207509315</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3213,7 +3180,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AEON Thana Sinsap (Thailand) Public Company Limited (SET:AEONTS)</t>
+          <t>Next Capital Public Company Limited (SET:NCAP)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3221,12 +3188,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D23">
-        <v>0.0435</v>
-      </c>
-      <c r="E23">
-        <v>0.12</v>
-      </c>
       <c r="G23">
         <v>0</v>
       </c>
@@ -3240,85 +3201,82 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>124.6</v>
+        <v>4.83</v>
       </c>
       <c r="L23">
-        <v>0.3104135525660189</v>
+        <v>0.2555555555555556</v>
       </c>
       <c r="M23">
-        <v>35.8</v>
+        <v>-0</v>
       </c>
       <c r="N23">
-        <v>0.02533616418966737</v>
+        <v>-0</v>
       </c>
       <c r="O23">
-        <v>0.2873194221508828</v>
+        <v>-0</v>
       </c>
       <c r="P23">
-        <v>35.8</v>
+        <v>-0</v>
       </c>
       <c r="Q23">
-        <v>0.02533616418966737</v>
+        <v>-0</v>
       </c>
       <c r="R23">
-        <v>0.2873194221508828</v>
+        <v>-0</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
       <c r="U23">
-        <v>156</v>
+        <v>18.5</v>
       </c>
       <c r="V23">
-        <v>0.1104033970276009</v>
+        <v>0.1489533011272142</v>
       </c>
       <c r="W23">
-        <v>0.2563786008230453</v>
+        <v>0.0853356890459364</v>
       </c>
       <c r="X23">
-        <v>0.03871933359305531</v>
+        <v>0.06205650012448723</v>
       </c>
       <c r="Y23">
-        <v>0.2176592672299899</v>
+        <v>0.02327918892144917</v>
       </c>
       <c r="Z23">
-        <v>0.1578885261377493</v>
+        <v>0.1405204460966543</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.03547650175262528</v>
+        <v>0.06093267810999252</v>
       </c>
       <c r="AC23">
-        <v>-0.03547650175262528</v>
+        <v>-0.06093267810999252</v>
       </c>
       <c r="AD23">
-        <v>2049.3</v>
+        <v>108.5</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>2049.3</v>
+        <v>108.5</v>
       </c>
       <c r="AG23">
-        <v>1893.3</v>
+        <v>90</v>
       </c>
       <c r="AH23">
-        <v>0.5918897842474656</v>
+        <v>0.4662655779974216</v>
       </c>
       <c r="AI23">
-        <v>0.7818473160123612</v>
+        <v>0.4963403476669717</v>
       </c>
       <c r="AJ23">
-        <v>0.5726340622448054</v>
+        <v>0.4201680672268908</v>
       </c>
       <c r="AK23">
-        <v>0.7680418644274065</v>
+        <v>0.4497751124437781</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3335,7 +3293,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>G Capital Public Company Limited (SET:GCAP)</t>
+          <t>Lease IT Public Company Limited (SET:LIT)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3343,101 +3301,80 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D24">
-        <v>-0.0326</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
       <c r="K24">
-        <v>-1.07</v>
-      </c>
-      <c r="L24">
-        <v>-0.419607843137255</v>
+        <v>-4.17</v>
       </c>
       <c r="M24">
-        <v>0.446</v>
+        <v>-0</v>
       </c>
       <c r="N24">
-        <v>0.02275510204081633</v>
+        <v>-0</v>
       </c>
       <c r="O24">
-        <v>-0.4168224299065421</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>0.446</v>
+        <v>-0</v>
       </c>
       <c r="Q24">
-        <v>0.02275510204081633</v>
+        <v>-0</v>
       </c>
       <c r="R24">
-        <v>-0.4168224299065421</v>
+        <v>0</v>
       </c>
       <c r="S24">
         <v>0</v>
       </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
       <c r="U24">
-        <v>1.38</v>
+        <v>5.14</v>
       </c>
       <c r="V24">
-        <v>0.07040816326530611</v>
+        <v>0.2196581196581197</v>
       </c>
       <c r="W24">
-        <v>-0.06524390243902441</v>
+        <v>-0.1353896103896104</v>
       </c>
       <c r="X24">
-        <v>0.0448215059433396</v>
+        <v>0.06231763763955622</v>
       </c>
       <c r="Y24">
-        <v>-0.110065408382364</v>
+        <v>-0.1977072480291666</v>
       </c>
       <c r="Z24">
-        <v>0.03564290007408132</v>
+        <v>0</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.03691943225468146</v>
+        <v>0.06105413806171008</v>
       </c>
       <c r="AC24">
-        <v>-0.03691943225468146</v>
+        <v>-0.06105413806171008</v>
       </c>
       <c r="AD24">
-        <v>42.1</v>
+        <v>21</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>42.1</v>
+        <v>21</v>
       </c>
       <c r="AG24">
-        <v>40.72</v>
+        <v>15.86</v>
       </c>
       <c r="AH24">
-        <v>0.6823338735818476</v>
+        <v>0.472972972972973</v>
       </c>
       <c r="AI24">
-        <v>0.7544802867383513</v>
+        <v>0.4093567251461989</v>
       </c>
       <c r="AJ24">
-        <v>0.6750663129973474</v>
+        <v>0.4039735099337748</v>
       </c>
       <c r="AK24">
-        <v>0.7482543182653436</v>
+        <v>0.3435875216637782</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3454,7 +3391,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lease IT Public Company Limited (SET:LIT)</t>
+          <t>Eastern Commercial Leasing Public Company Limited (SET:ECL)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3463,10 +3400,10 @@
         </is>
       </c>
       <c r="D25">
-        <v>-0.0556</v>
+        <v>0.09380000000000001</v>
       </c>
       <c r="E25">
-        <v>-0.257</v>
+        <v>0.121</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3475,34 +3412,34 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>0.0005811314488577302</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>0.0004692159772517479</v>
       </c>
       <c r="K25">
-        <v>0.617</v>
+        <v>5.65</v>
       </c>
       <c r="L25">
-        <v>0.1418390804597701</v>
+        <v>0.4094202898550725</v>
       </c>
       <c r="M25">
-        <v>1.19</v>
+        <v>3.82</v>
       </c>
       <c r="N25">
-        <v>0.07484276729559748</v>
+        <v>0.0584097859327217</v>
       </c>
       <c r="O25">
-        <v>1.928687196110211</v>
+        <v>0.6761061946902654</v>
       </c>
       <c r="P25">
-        <v>1.19</v>
+        <v>3.82</v>
       </c>
       <c r="Q25">
-        <v>0.07484276729559748</v>
+        <v>0.0584097859327217</v>
       </c>
       <c r="R25">
-        <v>1.928687196110211</v>
+        <v>0.6761061946902654</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -3511,61 +3448,67 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>4.48</v>
+        <v>0.607</v>
       </c>
       <c r="V25">
-        <v>0.2817610062893082</v>
+        <v>0.009281345565749234</v>
       </c>
       <c r="W25">
-        <v>0.01847305389221557</v>
+        <v>0.1080305927342256</v>
       </c>
       <c r="X25">
-        <v>0.05078887838994983</v>
+        <v>0.06404619817641923</v>
       </c>
       <c r="Y25">
-        <v>-0.03231582449773426</v>
+        <v>0.04398439455780641</v>
       </c>
       <c r="Z25">
-        <v>0.06066945606694561</v>
+        <v>0.09512983372543379</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>4.46364378972757e-05</v>
       </c>
       <c r="AB25">
-        <v>0.03782213851551589</v>
+        <v>0.06178705295525799</v>
       </c>
       <c r="AC25">
-        <v>-0.03782213851551589</v>
+        <v>-0.06174241651736072</v>
       </c>
       <c r="AD25">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>0.01490193002881661</v>
       </c>
       <c r="AF25">
-        <v>45</v>
+        <v>69.01490193002881</v>
       </c>
       <c r="AG25">
-        <v>40.52</v>
+        <v>68.40790193002881</v>
       </c>
       <c r="AH25">
-        <v>0.7389162561576355</v>
+        <v>0.5134468049231274</v>
       </c>
       <c r="AI25">
-        <v>0.5936675461741425</v>
+        <v>0.5872863849311803</v>
       </c>
       <c r="AJ25">
-        <v>0.7181850407656859</v>
+        <v>0.5112396274309783</v>
       </c>
       <c r="AK25">
-        <v>0.5681435782389231</v>
+        <v>0.5851435258069382</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
         <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>6272.727272727273</v>
+      </c>
+      <c r="AP25">
+        <v>6218.900175457165</v>
       </c>
     </row>
     <row r="26">
@@ -3576,7 +3519,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ASIA Capital Group Public Company Limited (SET:ACAP)</t>
+          <t>Mida Leasing Public Company Limited (SET:ML)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3584,23 +3527,29 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D26">
+        <v>-0.0623</v>
+      </c>
+      <c r="E26">
+        <v>-0.05690000000000001</v>
+      </c>
       <c r="G26">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>-0.0008973006014350316</v>
+        <v>0</v>
       </c>
       <c r="J26">
-        <v>-0.0008973006014350316</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>-11.2</v>
+        <v>2.41</v>
       </c>
       <c r="L26">
-        <v>1.354292623941959</v>
+        <v>0.3077905491698595</v>
       </c>
       <c r="M26">
         <v>-0</v>
@@ -3609,7 +3558,7 @@
         <v>-0</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P26">
         <v>-0</v>
@@ -3618,61 +3567,61 @@
         <v>-0</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
       <c r="U26">
-        <v>0.011</v>
+        <v>0.65</v>
       </c>
       <c r="V26">
-        <v>0.0009401709401709402</v>
+        <v>0.01884057971014493</v>
       </c>
       <c r="W26">
-        <v>-0.7671232876712328</v>
+        <v>0.03990066225165563</v>
       </c>
       <c r="X26">
-        <v>0.08689751795070523</v>
+        <v>0.06772623645815369</v>
       </c>
       <c r="Y26">
-        <v>-0.8540208056219381</v>
+        <v>-0.02782557420649806</v>
       </c>
       <c r="Z26">
-        <v>-0.07871999826819159</v>
+        <v>0.06828885400313972</v>
       </c>
       <c r="AA26">
-        <v>7.063550179101296e-05</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.0460417998298353</v>
+        <v>0.06302514675572832</v>
       </c>
       <c r="AC26">
-        <v>-0.04597116432804429</v>
+        <v>-0.06302514675572832</v>
       </c>
       <c r="AD26">
-        <v>81.40000000000001</v>
+        <v>48</v>
       </c>
       <c r="AE26">
-        <v>0.01289662013066145</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>81.41289662013067</v>
+        <v>48</v>
       </c>
       <c r="AG26">
-        <v>81.40189662013067</v>
+        <v>47.35</v>
       </c>
       <c r="AH26">
-        <v>0.874346084971107</v>
+        <v>0.5818181818181818</v>
       </c>
       <c r="AI26">
-        <v>0.9710172227110703</v>
+        <v>0.4610951008645534</v>
       </c>
       <c r="AJ26">
-        <v>0.8743312389463159</v>
+        <v>0.5784972510690287</v>
       </c>
       <c r="AK26">
-        <v>0.9710134197367487</v>
+        <v>0.457709038182697</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -3680,11 +3629,344 @@
       <c r="AM26">
         <v>0</v>
       </c>
-      <c r="AN26">
-        <v>8140</v>
-      </c>
-      <c r="AP26">
-        <v>8140.189662013067</v>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>G Capital Public Company Limited (SET:GCAP)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>-0.0565</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>-0.398</v>
+      </c>
+      <c r="L27">
+        <v>-0.2</v>
+      </c>
+      <c r="M27">
+        <v>0.794</v>
+      </c>
+      <c r="N27">
+        <v>0.06061068702290077</v>
+      </c>
+      <c r="O27">
+        <v>-1.994974874371859</v>
+      </c>
+      <c r="P27">
+        <v>0.794</v>
+      </c>
+      <c r="Q27">
+        <v>0.06061068702290077</v>
+      </c>
+      <c r="R27">
+        <v>-1.994974874371859</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>1.4</v>
+      </c>
+      <c r="V27">
+        <v>0.1068702290076336</v>
+      </c>
+      <c r="W27">
+        <v>-0.02905109489051095</v>
+      </c>
+      <c r="X27">
+        <v>0.07422516659821951</v>
+      </c>
+      <c r="Y27">
+        <v>-0.1032762614887305</v>
+      </c>
+      <c r="Z27">
+        <v>0.03656743844174936</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0.06453073872817232</v>
+      </c>
+      <c r="AC27">
+        <v>-0.06453073872817232</v>
+      </c>
+      <c r="AD27">
+        <v>26</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>26</v>
+      </c>
+      <c r="AG27">
+        <v>24.6</v>
+      </c>
+      <c r="AH27">
+        <v>0.6649616368286445</v>
+      </c>
+      <c r="AI27">
+        <v>0.6582278481012658</v>
+      </c>
+      <c r="AJ27">
+        <v>0.6525198938992043</v>
+      </c>
+      <c r="AK27">
+        <v>0.6456692913385826</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Asia Sermkij Leasing Public Company Limited (SET:ASK)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>0.138</v>
+      </c>
+      <c r="E28">
+        <v>0.15</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>38.3</v>
+      </c>
+      <c r="L28">
+        <v>0.4903969270166453</v>
+      </c>
+      <c r="M28">
+        <v>15.9</v>
+      </c>
+      <c r="N28">
+        <v>0.02933038184836746</v>
+      </c>
+      <c r="O28">
+        <v>0.4151436031331593</v>
+      </c>
+      <c r="P28">
+        <v>15.9</v>
+      </c>
+      <c r="Q28">
+        <v>0.02933038184836746</v>
+      </c>
+      <c r="R28">
+        <v>0.4151436031331593</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>12.5</v>
+      </c>
+      <c r="V28">
+        <v>0.02305847629588637</v>
+      </c>
+      <c r="W28">
+        <v>0.1444737834779328</v>
+      </c>
+      <c r="X28">
+        <v>0.08184083748052443</v>
+      </c>
+      <c r="Y28">
+        <v>0.0626329459974084</v>
+      </c>
+      <c r="Z28">
+        <v>0.0517629904559915</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0.06567716188546117</v>
+      </c>
+      <c r="AC28">
+        <v>-0.06567716188546117</v>
+      </c>
+      <c r="AD28">
+        <v>1452.9</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>1452.9</v>
+      </c>
+      <c r="AG28">
+        <v>1440.4</v>
+      </c>
+      <c r="AH28">
+        <v>0.7282706766917294</v>
+      </c>
+      <c r="AI28">
+        <v>0.8475673783689185</v>
+      </c>
+      <c r="AJ28">
+        <v>0.7265573770491803</v>
+      </c>
+      <c r="AK28">
+        <v>0.8464476699770818</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ASIA Capital Group Public Company Limited (SET:ACAP)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="K29">
+        <v>-11.4</v>
+      </c>
+      <c r="M29">
+        <v>-0</v>
+      </c>
+      <c r="N29">
+        <v>-0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>-0</v>
+      </c>
+      <c r="Q29">
+        <v>-0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0.143</v>
+      </c>
+      <c r="V29">
+        <v>0.01953551912568306</v>
+      </c>
+      <c r="W29">
+        <v>-4.691358024691358</v>
+      </c>
+      <c r="X29">
+        <v>0.1608074555594594</v>
+      </c>
+      <c r="Y29">
+        <v>-4.852165480250817</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0.07169586357777237</v>
+      </c>
+      <c r="AC29">
+        <v>-0.07169586357777237</v>
+      </c>
+      <c r="AD29">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AG29">
+        <v>72.25700000000001</v>
+      </c>
+      <c r="AH29">
+        <v>0.9081786251881586</v>
+      </c>
+      <c r="AI29">
+        <v>1.143940590930637</v>
+      </c>
+      <c r="AJ29">
+        <v>0.908013622026465</v>
+      </c>
+      <c r="AK29">
+        <v>1.144266552646998</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/thailand/thailand_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ29"/>
+  <dimension ref="A1:AQ39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0851</v>
+        <v>0.00223</v>
       </c>
       <c r="E2">
-        <v>0.1105</v>
+        <v>-0.00698</v>
       </c>
       <c r="F2">
-        <v>0.12</v>
+        <v>0.2075</v>
       </c>
       <c r="G2">
-        <v>0.05025350190126426</v>
+        <v>0.05608429301244361</v>
       </c>
       <c r="H2">
-        <v>0.05025350190126426</v>
+        <v>0.05602853162339327</v>
       </c>
       <c r="I2">
-        <v>0.04715695858329336</v>
+        <v>0.03462949695327272</v>
       </c>
       <c r="J2">
-        <v>0.0395179092224999</v>
+        <v>0.03000024947148416</v>
       </c>
       <c r="K2">
-        <v>850.102</v>
+        <v>918.71</v>
       </c>
       <c r="L2">
-        <v>0.3453565276739575</v>
+        <v>0.2613701312981564</v>
       </c>
       <c r="M2">
-        <v>340.057</v>
+        <v>581.631</v>
       </c>
       <c r="N2">
-        <v>0.01751379752911438</v>
+        <v>0.03602817927399903</v>
       </c>
       <c r="O2">
-        <v>0.400019056536745</v>
+        <v>0.6330953184356325</v>
       </c>
       <c r="P2">
-        <v>340.057</v>
+        <v>518.535</v>
       </c>
       <c r="Q2">
-        <v>0.01751379752911438</v>
+        <v>0.03211980093881359</v>
       </c>
       <c r="R2">
-        <v>0.400019056536745</v>
+        <v>0.5644164099661482</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>63.09600000000001</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1084811504201117</v>
       </c>
       <c r="U2">
-        <v>621.24</v>
+        <v>763.098</v>
       </c>
       <c r="V2">
-        <v>0.03199543481530161</v>
+        <v>0.04726885524951405</v>
       </c>
       <c r="W2">
-        <v>0.1080305927342256</v>
+        <v>0.07422680412371134</v>
       </c>
       <c r="X2">
-        <v>0.06047766712063649</v>
+        <v>0.06966063600642619</v>
       </c>
       <c r="Y2">
-        <v>0.04755292561358915</v>
+        <v>0.004566168117285149</v>
       </c>
       <c r="Z2">
-        <v>0.1537544000608181</v>
+        <v>0.1838350211616652</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05959778929253862</v>
+        <v>0.05968316251505363</v>
       </c>
       <c r="AC2">
-        <v>-0.05852052255000606</v>
+        <v>-0.05924996492128815</v>
       </c>
       <c r="AD2">
-        <v>12663.8</v>
+        <v>16584.59</v>
       </c>
       <c r="AE2">
-        <v>0.5910165402585904</v>
+        <v>3.310573438381539</v>
       </c>
       <c r="AF2">
-        <v>12664.39101654026</v>
+        <v>16587.90057343838</v>
       </c>
       <c r="AG2">
-        <v>12043.15101654026</v>
+        <v>15824.80257343838</v>
       </c>
       <c r="AH2">
-        <v>0.3947640704470879</v>
+        <v>0.5067842616947507</v>
       </c>
       <c r="AI2">
-        <v>0.6722724983596186</v>
+        <v>0.665786873534276</v>
       </c>
       <c r="AJ2">
-        <v>0.382812363492563</v>
+        <v>0.4950110796149804</v>
       </c>
       <c r="AK2">
-        <v>0.6610962293617548</v>
+        <v>0.6552270338379639</v>
       </c>
       <c r="AL2">
-        <v>32.79</v>
+        <v>68.54299999999999</v>
       </c>
       <c r="AM2">
-        <v>31.73</v>
+        <v>65.22099999999999</v>
       </c>
       <c r="AN2">
-        <v>103.830575734221</v>
+        <v>160.6255690072639</v>
       </c>
       <c r="AO2">
-        <v>3.528514791094846</v>
+        <v>1.748916738397794</v>
       </c>
       <c r="AP2">
-        <v>98.74187082088663</v>
+        <v>153.2668530115098</v>
       </c>
       <c r="AQ2">
-        <v>3.646391427670974</v>
+        <v>1.837996964167983</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SG Capital Public Company Limited (SET:SGC)</t>
+          <t>BA Airport Leasehold Real Estate Investment Trust (SET:BAREIT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,40 +725,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.5837742504409171</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.5837742504409171</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.5784832451499118</v>
+        <v>0.9176829268292684</v>
       </c>
       <c r="J3">
-        <v>0.4744174761811446</v>
+        <v>0.9176829268292684</v>
       </c>
       <c r="K3">
-        <v>15.5</v>
+        <v>24.4</v>
       </c>
       <c r="L3">
-        <v>0.27336860670194</v>
+        <v>0.7439024390243902</v>
       </c>
       <c r="M3">
-        <v>11.7</v>
+        <v>21.693</v>
       </c>
       <c r="N3">
-        <v>0.02493606138107417</v>
+        <v>0.07214166943797806</v>
       </c>
       <c r="O3">
-        <v>0.7548387096774193</v>
+        <v>0.8890573770491804</v>
       </c>
       <c r="P3">
-        <v>11.7</v>
+        <v>21.693</v>
       </c>
       <c r="Q3">
-        <v>0.02493606138107417</v>
+        <v>0.07214166943797806</v>
       </c>
       <c r="R3">
-        <v>0.7548387096774193</v>
+        <v>0.8890573770491804</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,58 +767,52 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>9.25</v>
+        <v>6.13</v>
       </c>
       <c r="V3">
-        <v>0.01971440750213129</v>
+        <v>0.02038576654472897</v>
       </c>
       <c r="X3">
-        <v>0.05981370990339367</v>
+        <v>0.06065014342311598</v>
       </c>
       <c r="AB3">
-        <v>0.06096492252624325</v>
+        <v>0.05954844343308275</v>
       </c>
       <c r="AD3">
-        <v>313.8</v>
+        <v>118.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>313.8</v>
+        <v>118.4</v>
       </c>
       <c r="AG3">
-        <v>304.55</v>
+        <v>112.27</v>
       </c>
       <c r="AH3">
-        <v>0.4007662835249042</v>
+        <v>0.2825101407778573</v>
       </c>
       <c r="AI3">
-        <v>0.8292811839323468</v>
+        <v>0.2977867203219316</v>
       </c>
       <c r="AJ3">
-        <v>0.3936025848142165</v>
+        <v>0.2718599414001017</v>
       </c>
       <c r="AK3">
-        <v>0.8250033861573887</v>
+        <v>0.2867908141109153</v>
       </c>
       <c r="AL3">
-        <v>13.8</v>
+        <v>5.63</v>
       </c>
       <c r="AM3">
-        <v>13.8</v>
-      </c>
-      <c r="AN3">
-        <v>9.423423423423424</v>
+        <v>5.63</v>
       </c>
       <c r="AO3">
-        <v>2.376811594202898</v>
-      </c>
-      <c r="AP3">
-        <v>9.145645645645647</v>
+        <v>5.346358792184725</v>
       </c>
       <c r="AQ3">
-        <v>2.376811594202898</v>
+        <v>5.346358792184725</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Knight Club Capital Asset Management Public Company Limited (SET:KCC)</t>
+          <t>Forth Smart Service Public Company Limited (SET:FSMART)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -837,41 +831,47 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.0974</v>
+      </c>
+      <c r="E4">
+        <v>-0.133</v>
+      </c>
       <c r="G4">
-        <v>0.5071574642126789</v>
+        <v>0.4021739130434782</v>
       </c>
       <c r="H4">
-        <v>0.5071574642126789</v>
+        <v>0.4021739130434782</v>
       </c>
       <c r="I4">
-        <v>0.6871165644171779</v>
+        <v>0.1217391304347826</v>
       </c>
       <c r="J4">
-        <v>0.5507544354170121</v>
+        <v>0.1005381208628982</v>
       </c>
       <c r="K4">
-        <v>2.07</v>
+        <v>7.53</v>
       </c>
       <c r="L4">
-        <v>0.4233128834355828</v>
+        <v>0.1364130434782609</v>
       </c>
       <c r="M4">
-        <v>0.623</v>
+        <v>7</v>
       </c>
       <c r="N4">
-        <v>0.004792307692307692</v>
+        <v>0.04323656578134651</v>
       </c>
       <c r="O4">
-        <v>0.3009661835748793</v>
+        <v>0.9296148738379814</v>
       </c>
       <c r="P4">
-        <v>0.623</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>0.004792307692307692</v>
+        <v>0.04323656578134651</v>
       </c>
       <c r="R4">
-        <v>0.3009661835748793</v>
+        <v>0.9296148738379814</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,58 +880,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>7.21</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>0.0445336627547869</v>
+      </c>
+      <c r="W4">
+        <v>0.2651408450704226</v>
       </c>
       <c r="X4">
-        <v>0.05388779307908484</v>
+        <v>0.056278207362573</v>
+      </c>
+      <c r="Y4">
+        <v>0.2088626377078496</v>
+      </c>
+      <c r="Z4">
+        <v>1.606986899563319</v>
+      </c>
+      <c r="AA4">
+        <v>0.161563443133391</v>
       </c>
       <c r="AB4">
-        <v>0.05488406998577119</v>
+        <v>0.05617692579214275</v>
+      </c>
+      <c r="AC4">
+        <v>0.1053865173412483</v>
       </c>
       <c r="AD4">
-        <v>16.6</v>
+        <v>10.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>16.6</v>
+        <v>10.5</v>
       </c>
       <c r="AG4">
-        <v>16.6</v>
+        <v>3.29</v>
       </c>
       <c r="AH4">
-        <v>0.1132332878581173</v>
+        <v>0.06090487238979118</v>
       </c>
       <c r="AI4">
-        <v>0.3656387665198238</v>
+        <v>0.2599009900990099</v>
       </c>
       <c r="AJ4">
-        <v>0.1132332878581173</v>
+        <v>0.01991645983413039</v>
       </c>
       <c r="AK4">
-        <v>0.3656387665198238</v>
+        <v>0.0991262428442302</v>
       </c>
       <c r="AL4">
-        <v>0.775</v>
+        <v>0.465</v>
       </c>
       <c r="AM4">
-        <v>0.775</v>
+        <v>-0.427</v>
       </c>
       <c r="AN4">
-        <v>4.882352941176471</v>
+        <v>0.5898876404494382</v>
       </c>
       <c r="AO4">
-        <v>4.335483870967741</v>
+        <v>14.4516129032258</v>
       </c>
       <c r="AP4">
-        <v>4.882352941176471</v>
+        <v>0.1848314606741573</v>
       </c>
       <c r="AQ4">
-        <v>4.335483870967741</v>
+        <v>-15.73770491803279</v>
       </c>
     </row>
     <row r="5">
@@ -951,49 +966,49 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.273</v>
+        <v>0.235</v>
       </c>
       <c r="E5">
-        <v>0.274</v>
+        <v>0.329</v>
       </c>
       <c r="F5">
-        <v>0.229</v>
+        <v>0.121</v>
       </c>
       <c r="G5">
-        <v>0.5297202797202797</v>
+        <v>0.4622926093514329</v>
       </c>
       <c r="H5">
-        <v>0.5297202797202797</v>
+        <v>0.4622926093514329</v>
       </c>
       <c r="I5">
-        <v>0.4956293706293706</v>
+        <v>0.469079939668175</v>
       </c>
       <c r="J5">
-        <v>0.436193338533976</v>
+        <v>0.4033348772579898</v>
       </c>
       <c r="K5">
-        <v>45.9</v>
+        <v>53.6</v>
       </c>
       <c r="L5">
-        <v>0.4012237762237762</v>
+        <v>0.4042232277526395</v>
       </c>
       <c r="M5">
-        <v>34.9</v>
+        <v>37.1</v>
       </c>
       <c r="N5">
-        <v>0.01198283261802575</v>
+        <v>0.03406795224977043</v>
       </c>
       <c r="O5">
-        <v>0.7603485838779956</v>
+        <v>0.6921641791044776</v>
       </c>
       <c r="P5">
-        <v>34.9</v>
+        <v>37.1</v>
       </c>
       <c r="Q5">
-        <v>0.01198283261802575</v>
+        <v>0.03406795224977043</v>
       </c>
       <c r="R5">
-        <v>0.7603485838779956</v>
+        <v>0.6921641791044776</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1002,73 +1017,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>34.2</v>
+        <v>28.7</v>
       </c>
       <c r="V5">
-        <v>0.01174248927038627</v>
+        <v>0.0263544536271809</v>
       </c>
       <c r="W5">
-        <v>0.1822875297855441</v>
+        <v>0.08982738394503099</v>
       </c>
       <c r="X5">
-        <v>0.05302369140842133</v>
+        <v>0.05913542055289175</v>
       </c>
       <c r="Y5">
-        <v>0.1292638383771227</v>
+        <v>0.03069196339213924</v>
       </c>
       <c r="Z5">
-        <v>0.2315039663266958</v>
+        <v>0.1901484190148419</v>
       </c>
       <c r="AA5">
-        <v>0.1009804879558986</v>
+        <v>0.07669348924415208</v>
       </c>
       <c r="AB5">
-        <v>0.05304520910182675</v>
+        <v>0.05814719296589397</v>
       </c>
       <c r="AC5">
-        <v>0.04793527885407185</v>
+        <v>0.01854629627825811</v>
       </c>
       <c r="AD5">
-        <v>142.1</v>
+        <v>304.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>142.1</v>
+        <v>304.7</v>
       </c>
       <c r="AG5">
-        <v>107.9</v>
+        <v>276</v>
       </c>
       <c r="AH5">
-        <v>0.04652000261900085</v>
+        <v>0.2186266771902131</v>
       </c>
       <c r="AI5">
-        <v>0.1918196544276458</v>
+        <v>0.2939417325873047</v>
       </c>
       <c r="AJ5">
-        <v>0.03572374519931135</v>
+        <v>0.2021978021978022</v>
       </c>
       <c r="AK5">
-        <v>0.1527030851967167</v>
+        <v>0.2738366901478321</v>
       </c>
       <c r="AL5">
-        <v>7.64</v>
+        <v>11.7</v>
       </c>
       <c r="AM5">
-        <v>7.64</v>
+        <v>11.7</v>
       </c>
       <c r="AN5">
-        <v>2.424914675767918</v>
+        <v>4.775862068965517</v>
       </c>
       <c r="AO5">
-        <v>7.421465968586388</v>
+        <v>5.316239316239317</v>
       </c>
       <c r="AP5">
-        <v>1.841296928327645</v>
+        <v>4.326018808777429</v>
       </c>
       <c r="AQ5">
-        <v>7.421465968586388</v>
+        <v>5.316239316239317</v>
       </c>
     </row>
     <row r="6">
@@ -1079,7 +1094,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amanah Leasing Public Company Limited (SET:AMANAH)</t>
+          <t>Knight Club Capital Asset Management Public Company Limited (SET:KCC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1087,47 +1102,41 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.132</v>
-      </c>
-      <c r="E6">
-        <v>0.506</v>
-      </c>
       <c r="G6">
-        <v>0.5517241379310345</v>
+        <v>0.6312292358803987</v>
       </c>
       <c r="H6">
-        <v>0.5517241379310345</v>
+        <v>0.6312292358803987</v>
       </c>
       <c r="I6">
-        <v>0.4741379310344828</v>
+        <v>0.6960132890365449</v>
       </c>
       <c r="J6">
-        <v>0.3996525572533343</v>
+        <v>0.5568106312292359</v>
       </c>
       <c r="K6">
-        <v>7.78</v>
+        <v>2.14</v>
       </c>
       <c r="L6">
-        <v>0.3353448275862069</v>
+        <v>0.3554817275747509</v>
       </c>
       <c r="M6">
-        <v>4.39</v>
+        <v>0.359</v>
       </c>
       <c r="N6">
-        <v>0.03874669020300088</v>
+        <v>0.00478029294274301</v>
       </c>
       <c r="O6">
-        <v>0.5642673521850899</v>
+        <v>0.1677570093457944</v>
       </c>
       <c r="P6">
-        <v>4.39</v>
+        <v>0.359</v>
       </c>
       <c r="Q6">
-        <v>0.03874669020300088</v>
+        <v>0.00478029294274301</v>
       </c>
       <c r="R6">
-        <v>0.5642673521850899</v>
+        <v>0.1677570093457944</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1136,73 +1145,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>0.01376875551632833</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>0.1584521384928717</v>
+        <v>0.07430555555555556</v>
       </c>
       <c r="X6">
-        <v>0.05814393930492617</v>
+        <v>0.0604783681042709</v>
       </c>
       <c r="Y6">
-        <v>0.1003081991879455</v>
+        <v>0.01382718745128465</v>
       </c>
       <c r="Z6">
-        <v>0.2264298262736678</v>
+        <v>0.1325991189427312</v>
       </c>
       <c r="AA6">
-        <v>0.09049325910869954</v>
+        <v>0.07383259911894273</v>
       </c>
       <c r="AB6">
-        <v>0.05865549055516051</v>
+        <v>0.05886134901701542</v>
       </c>
       <c r="AC6">
-        <v>0.03183776855353903</v>
+        <v>0.01497125010192731</v>
       </c>
       <c r="AD6">
-        <v>58.5</v>
+        <v>28.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>58.5</v>
+        <v>28.6</v>
       </c>
       <c r="AG6">
-        <v>56.94</v>
+        <v>28.6</v>
       </c>
       <c r="AH6">
-        <v>0.3405122235157159</v>
+        <v>0.2757955641272903</v>
       </c>
       <c r="AI6">
-        <v>0.5545023696682464</v>
+        <v>0.4758735440931781</v>
       </c>
       <c r="AJ6">
-        <v>0.334468984962406</v>
+        <v>0.2757955641272903</v>
       </c>
       <c r="AK6">
-        <v>0.5478160477198384</v>
+        <v>0.4758735440931781</v>
       </c>
       <c r="AL6">
-        <v>1.96</v>
+        <v>1.52</v>
       </c>
       <c r="AM6">
-        <v>1.96</v>
+        <v>1.52</v>
       </c>
       <c r="AN6">
-        <v>5.27027027027027</v>
+        <v>6.761229314420803</v>
       </c>
       <c r="AO6">
-        <v>5.612244897959184</v>
+        <v>2.756578947368421</v>
       </c>
       <c r="AP6">
-        <v>5.129729729729729</v>
+        <v>6.761229314420803</v>
       </c>
       <c r="AQ6">
-        <v>5.612244897959184</v>
+        <v>2.756578947368421</v>
       </c>
     </row>
     <row r="7">
@@ -1222,46 +1231,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0104</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="E7">
-        <v>0.0159</v>
+        <v>-0.0103</v>
       </c>
       <c r="G7">
-        <v>0.6486486486486487</v>
+        <v>0.6730434782608696</v>
       </c>
       <c r="H7">
-        <v>0.6486486486486487</v>
+        <v>0.6730434782608696</v>
       </c>
       <c r="I7">
-        <v>0.6144144144144145</v>
+        <v>0.5817391304347826</v>
       </c>
       <c r="J7">
-        <v>0.4897343412882718</v>
+        <v>0.4651713651680776</v>
       </c>
       <c r="K7">
-        <v>4.35</v>
+        <v>4.22</v>
       </c>
       <c r="L7">
-        <v>0.3918918918918919</v>
+        <v>0.3669565217391304</v>
       </c>
       <c r="M7">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="N7">
-        <v>0.04870588235294118</v>
+        <v>0.05641025641025642</v>
       </c>
       <c r="O7">
-        <v>0.4758620689655172</v>
+        <v>0.5213270142180095</v>
       </c>
       <c r="P7">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Q7">
-        <v>0.04870588235294118</v>
+        <v>0.05641025641025642</v>
       </c>
       <c r="R7">
-        <v>0.4758620689655172</v>
+        <v>0.5213270142180095</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1270,73 +1279,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>13</v>
+        <v>9.9</v>
       </c>
       <c r="V7">
-        <v>0.3058823529411765</v>
+        <v>0.2538461538461538</v>
       </c>
       <c r="W7">
-        <v>0.09334763948497853</v>
+        <v>0.09634703196347032</v>
       </c>
       <c r="X7">
-        <v>0.06586308153276384</v>
+        <v>0.07112896518352277</v>
       </c>
       <c r="Y7">
-        <v>0.02748455795221469</v>
+        <v>0.02521806677994755</v>
       </c>
       <c r="Z7">
-        <v>0.1236080178173719</v>
+        <v>0.1390568319226119</v>
       </c>
       <c r="AA7">
-        <v>0.06053509118373961</v>
+        <v>0.06468525634138927</v>
       </c>
       <c r="AB7">
-        <v>0.05905844009490442</v>
+        <v>0.05966447224675922</v>
       </c>
       <c r="AC7">
-        <v>0.001476651088835185</v>
+        <v>0.005020784094630054</v>
       </c>
       <c r="AD7">
-        <v>51.9</v>
+        <v>46.1</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>51.9</v>
+        <v>46.1</v>
       </c>
       <c r="AG7">
-        <v>38.9</v>
+        <v>36.2</v>
       </c>
       <c r="AH7">
-        <v>0.5497881355932203</v>
+        <v>0.5417156286721505</v>
       </c>
       <c r="AI7">
-        <v>0.542319749216301</v>
+        <v>0.493576017130621</v>
       </c>
       <c r="AJ7">
-        <v>0.4778869778869778</v>
+        <v>0.4813829787234043</v>
       </c>
       <c r="AK7">
-        <v>0.4703748488512697</v>
+        <v>0.4335329341317365</v>
       </c>
       <c r="AL7">
-        <v>0.995</v>
+        <v>1.24</v>
       </c>
       <c r="AM7">
-        <v>0.995</v>
+        <v>1.24</v>
       </c>
       <c r="AN7">
-        <v>7.330508474576271</v>
+        <v>6.652236652236653</v>
       </c>
       <c r="AO7">
-        <v>6.85427135678392</v>
+        <v>5.395161290322581</v>
       </c>
       <c r="AP7">
-        <v>5.494350282485875</v>
+        <v>5.223665223665225</v>
       </c>
       <c r="AQ7">
-        <v>6.85427135678392</v>
+        <v>5.395161290322581</v>
       </c>
     </row>
     <row r="8">
@@ -1347,7 +1356,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AIRA Factoring Public Company Limited (SET:AF)</t>
+          <t>IMPACT Growth Real Estate Investment Trust (SET:IMPACT)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1356,46 +1365,46 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0116</v>
+        <v>-0.0474</v>
       </c>
       <c r="E8">
-        <v>0.0733</v>
+        <v>-0.0579</v>
       </c>
       <c r="G8">
-        <v>0.5118243243243243</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>0.5118243243243243</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>0.4831081081081081</v>
+        <v>0.5705645161290323</v>
       </c>
       <c r="J8">
-        <v>0.3705628114147667</v>
+        <v>0.5705645161290323</v>
       </c>
       <c r="K8">
-        <v>1.37</v>
+        <v>25.5</v>
       </c>
       <c r="L8">
-        <v>0.2314189189189189</v>
+        <v>0.5141129032258064</v>
       </c>
       <c r="M8">
-        <v>1.06</v>
+        <v>25.9</v>
       </c>
       <c r="N8">
-        <v>0.01992481203007519</v>
+        <v>0.04815916697657122</v>
       </c>
       <c r="O8">
-        <v>0.7737226277372262</v>
+        <v>1.015686274509804</v>
       </c>
       <c r="P8">
-        <v>1.06</v>
+        <v>25.9</v>
       </c>
       <c r="Q8">
-        <v>0.01992481203007519</v>
+        <v>0.04815916697657122</v>
       </c>
       <c r="R8">
-        <v>0.7737226277372262</v>
+        <v>1.015686274509804</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1404,73 +1413,67 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>4.49</v>
+        <v>7.72</v>
       </c>
       <c r="V8">
-        <v>0.0843984962406015</v>
+        <v>0.01435477872815173</v>
       </c>
       <c r="W8">
-        <v>0.0825301204819277</v>
+        <v>0.05912357987479713</v>
       </c>
       <c r="X8">
-        <v>0.06027069792984464</v>
+        <v>0.05802375828950546</v>
       </c>
       <c r="Y8">
-        <v>0.02225942255208306</v>
+        <v>0.00109982158529167</v>
       </c>
       <c r="Z8">
-        <v>0.1179752889597449</v>
+        <v>0.09461856889414547</v>
       </c>
       <c r="AA8">
-        <v>0.04371725475439256</v>
+        <v>0.05398599797790962</v>
       </c>
       <c r="AB8">
-        <v>0.06001130710309337</v>
+        <v>0.05670224527275269</v>
       </c>
       <c r="AC8">
-        <v>-0.01629405234870081</v>
+        <v>-0.002716247294843079</v>
       </c>
       <c r="AD8">
-        <v>37.8</v>
+        <v>105.5</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>37.8</v>
+        <v>105.5</v>
       </c>
       <c r="AG8">
-        <v>33.31</v>
+        <v>97.78</v>
       </c>
       <c r="AH8">
-        <v>0.4153846153846154</v>
+        <v>0.163998134618374</v>
       </c>
       <c r="AI8">
-        <v>0.7145557655954631</v>
+        <v>0.1917136107577685</v>
       </c>
       <c r="AJ8">
-        <v>0.385042191654144</v>
+        <v>0.1538437332829856</v>
       </c>
       <c r="AK8">
-        <v>0.6880809750051642</v>
+        <v>0.1802130561391868</v>
       </c>
       <c r="AL8">
-        <v>1.07</v>
+        <v>3.29</v>
       </c>
       <c r="AM8">
-        <v>1.07</v>
-      </c>
-      <c r="AN8">
-        <v>13.125</v>
+        <v>3.29</v>
       </c>
       <c r="AO8">
-        <v>2.672897196261682</v>
-      </c>
-      <c r="AP8">
-        <v>11.56597222222222</v>
+        <v>8.601823708206688</v>
       </c>
       <c r="AQ8">
-        <v>2.672897196261682</v>
+        <v>8.601823708206688</v>
       </c>
     </row>
     <row r="9">
@@ -1481,7 +1484,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Thitikorn Public Company Limited (SET:TK)</t>
+          <t>Chase Asia Public Company Limited (SET:CHASE)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1489,116 +1492,113 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D9">
-        <v>-0.0867</v>
-      </c>
-      <c r="E9">
-        <v>-0.00886</v>
-      </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.3230337078651686</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>0.3230337078651686</v>
       </c>
       <c r="I9">
-        <v>0.01002105902314486</v>
+        <v>0.2631440930081984</v>
       </c>
       <c r="J9">
-        <v>0.007496523000006442</v>
+        <v>0.2123236105907383</v>
       </c>
       <c r="K9">
-        <v>11.6</v>
+        <v>3.4</v>
       </c>
       <c r="L9">
-        <v>0.3143631436314363</v>
+        <v>0.1910112359550562</v>
       </c>
       <c r="M9">
-        <v>6.62</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.05448559670781893</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.5706896551724138</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>6.62</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.05448559670781893</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.5706896551724138</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>18</v>
+        <v>6.35</v>
       </c>
       <c r="V9">
-        <v>0.1481481481481481</v>
+        <v>0.0607074569789675</v>
       </c>
       <c r="W9">
-        <v>0.07051671732522796</v>
+        <v>0.06296296296296296</v>
       </c>
       <c r="X9">
-        <v>0.05382122773781757</v>
+        <v>0.05676574324032181</v>
       </c>
       <c r="Y9">
-        <v>0.01669548958741039</v>
+        <v>0.006197219722641145</v>
       </c>
       <c r="Z9">
-        <v>0.2282340844778392</v>
+        <v>0.2469814985410066</v>
       </c>
       <c r="AA9">
-        <v>0.001710962063673534</v>
+        <v>0.05244000351933769</v>
       </c>
       <c r="AB9">
-        <v>0.05378490560674654</v>
+        <v>0.05676433458007876</v>
       </c>
       <c r="AC9">
-        <v>-0.052073943543073</v>
+        <v>-0.004324331060741073</v>
       </c>
       <c r="AD9">
-        <v>14.2</v>
+        <v>10.5</v>
       </c>
       <c r="AE9">
-        <v>0.5761146102297738</v>
+        <v>0.120175722270338</v>
       </c>
       <c r="AF9">
-        <v>14.77611461022977</v>
+        <v>10.62017572227034</v>
       </c>
       <c r="AG9">
-        <v>-3.223885389770228</v>
+        <v>4.270175722270338</v>
       </c>
       <c r="AH9">
-        <v>0.1084277655882081</v>
+        <v>0.09217288253291231</v>
       </c>
       <c r="AI9">
-        <v>0.08791323290936212</v>
+        <v>0.1038951033612493</v>
       </c>
       <c r="AJ9">
-        <v>-0.02725728183069172</v>
+        <v>0.03922264012105233</v>
       </c>
       <c r="AK9">
-        <v>-0.02148166880614642</v>
+        <v>0.04454123182835045</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>0.549</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>0.549</v>
       </c>
       <c r="AN9">
-        <v>29.27835051546392</v>
+        <v>2.084160381103612</v>
+      </c>
+      <c r="AO9">
+        <v>8.43351548269581</v>
       </c>
       <c r="AP9">
-        <v>-6.647186370660264</v>
+        <v>0.8475934343529848</v>
+      </c>
+      <c r="AQ9">
+        <v>8.43351548269581</v>
       </c>
     </row>
     <row r="10">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Krungthai Card Public Company Limited (SET:KTC)</t>
+          <t>Amanah Leasing Public Company Limited (SET:AMANAH)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1618,49 +1618,46 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.08259999999999999</v>
+        <v>0.0901</v>
       </c>
       <c r="E10">
-        <v>0.173</v>
-      </c>
-      <c r="F10">
-        <v>0.117</v>
+        <v>0.07440000000000001</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.3652343749999999</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>0.3652343749999999</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>0.2640625</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>0.2165666946308725</v>
       </c>
       <c r="K10">
-        <v>176.5</v>
+        <v>6.11</v>
       </c>
       <c r="L10">
-        <v>0.4189413719439829</v>
+        <v>0.238671875</v>
       </c>
       <c r="M10">
-        <v>68.3</v>
+        <v>5.67</v>
       </c>
       <c r="N10">
-        <v>0.01552061082579648</v>
+        <v>0.089010989010989</v>
       </c>
       <c r="O10">
-        <v>0.3869688385269122</v>
+        <v>0.9279869067103109</v>
       </c>
       <c r="P10">
-        <v>68.3</v>
+        <v>5.67</v>
       </c>
       <c r="Q10">
-        <v>0.01552061082579648</v>
+        <v>0.089010989010989</v>
       </c>
       <c r="R10">
-        <v>0.3869688385269122</v>
+        <v>0.9279869067103109</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1669,61 +1666,73 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>42.9</v>
+        <v>3.96</v>
       </c>
       <c r="V10">
-        <v>0.009748670635822387</v>
+        <v>0.06216640502354788</v>
       </c>
       <c r="W10">
-        <v>0.2323285507437146</v>
+        <v>0.13</v>
       </c>
       <c r="X10">
-        <v>0.05628230314351224</v>
+        <v>0.07133834021219834</v>
       </c>
       <c r="Y10">
-        <v>0.1760462476002024</v>
+        <v>0.05866165978780166</v>
       </c>
       <c r="Z10">
-        <v>0.1885517364840673</v>
+        <v>0.2462959399653646</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>0.05333949761930282</v>
       </c>
       <c r="AB10">
-        <v>0.05556302924369655</v>
+        <v>0.05969022973348719</v>
       </c>
       <c r="AC10">
-        <v>-0.05556302924369655</v>
+        <v>-0.006350732114184361</v>
       </c>
       <c r="AD10">
-        <v>1524.1</v>
+        <v>76.3</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>1524.1</v>
+        <v>76.3</v>
       </c>
       <c r="AG10">
-        <v>1481.2</v>
+        <v>72.34</v>
       </c>
       <c r="AH10">
-        <v>0.2572450925785271</v>
+        <v>0.5449999999999999</v>
       </c>
       <c r="AI10">
-        <v>0.6578754262528597</v>
+        <v>0.6094249201277956</v>
       </c>
       <c r="AJ10">
-        <v>0.2518276718011493</v>
+        <v>0.5317553660688032</v>
       </c>
       <c r="AK10">
-        <v>0.6514205295100712</v>
+        <v>0.5966677664137249</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>2.86</v>
+      </c>
+      <c r="AN10">
+        <v>11.05797101449275</v>
+      </c>
+      <c r="AO10">
+        <v>2.363636363636364</v>
+      </c>
+      <c r="AP10">
+        <v>10.48405797101449</v>
+      </c>
+      <c r="AQ10">
+        <v>2.363636363636364</v>
       </c>
     </row>
     <row r="11">
@@ -1734,7 +1743,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Saksiam Leasing Public Company Limited (SET:SAK)</t>
+          <t>Shrinkflex (Thailand) Public Company Limited (SET:SFT)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1743,40 +1752,40 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>0.1409638554216867</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>0.1409638554216867</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>0.04664255470478881</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>0.03647686970502714</v>
       </c>
       <c r="K11">
-        <v>18.2</v>
+        <v>0.671</v>
       </c>
       <c r="L11">
-        <v>0.3540856031128405</v>
+        <v>0.02694779116465864</v>
       </c>
       <c r="M11">
-        <v>6.44</v>
+        <v>0.842</v>
       </c>
       <c r="N11">
-        <v>0.01741011084076778</v>
+        <v>0.01603809523809524</v>
       </c>
       <c r="O11">
-        <v>0.3538461538461539</v>
+        <v>1.254843517138599</v>
       </c>
       <c r="P11">
-        <v>6.44</v>
+        <v>0.842</v>
       </c>
       <c r="Q11">
-        <v>0.01741011084076778</v>
+        <v>0.01603809523809524</v>
       </c>
       <c r="R11">
-        <v>0.3538461538461539</v>
+        <v>1.254843517138599</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1785,61 +1794,73 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>7.77</v>
+        <v>0.164</v>
       </c>
       <c r="V11">
-        <v>0.02100567721005677</v>
+        <v>0.003123809523809524</v>
       </c>
       <c r="W11">
-        <v>0.1300929235167977</v>
+        <v>0.03355</v>
       </c>
       <c r="X11">
-        <v>0.05709616468160044</v>
+        <v>0.05664866659832204</v>
       </c>
       <c r="Y11">
-        <v>0.07299675883519727</v>
+        <v>-0.02309866659832204</v>
       </c>
       <c r="Z11">
-        <v>0.2023064509780769</v>
+        <v>1.161055569729487</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>0.04235167273731855</v>
       </c>
       <c r="AB11">
-        <v>0.05602726932696543</v>
+        <v>0.05608157543487559</v>
       </c>
       <c r="AC11">
-        <v>-0.05602726932696543</v>
+        <v>-0.01372990269755704</v>
       </c>
       <c r="AD11">
-        <v>155.6</v>
+        <v>4.82</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>0.04800193925379446</v>
       </c>
       <c r="AF11">
-        <v>155.6</v>
+        <v>4.868001939253794</v>
       </c>
       <c r="AG11">
-        <v>147.83</v>
+        <v>4.704001939253795</v>
       </c>
       <c r="AH11">
-        <v>0.2960989533777355</v>
+        <v>0.08485569960077145</v>
       </c>
       <c r="AI11">
-        <v>0.5321477428180574</v>
+        <v>0.1918953629422888</v>
       </c>
       <c r="AJ11">
-        <v>0.2855349313348656</v>
+        <v>0.08223204286037679</v>
       </c>
       <c r="AK11">
-        <v>0.5193760320415978</v>
+        <v>0.1866371043214205</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>0.211</v>
+      </c>
+      <c r="AN11">
+        <v>2.015892931827687</v>
+      </c>
+      <c r="AO11">
+        <v>5.308056872037915</v>
+      </c>
+      <c r="AP11">
+        <v>1.967378477312336</v>
+      </c>
+      <c r="AQ11">
+        <v>5.308056872037915</v>
       </c>
     </row>
     <row r="12">
@@ -1850,7 +1871,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Srisawad Corporation Public Company Limited (SET:SAWAD)</t>
+          <t>SABUY Technology Public Company Limited (SET:SABUY)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1858,113 +1879,119 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D12">
-        <v>0.108</v>
-      </c>
-      <c r="E12">
-        <v>0.1</v>
-      </c>
       <c r="F12">
-        <v>0.12</v>
+        <v>0.406</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>0.0890909090909091</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>0.0890909090909091</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>0.04127580146528694</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>0.04127580146528694</v>
       </c>
       <c r="K12">
-        <v>116.7</v>
+        <v>24.7</v>
       </c>
       <c r="L12">
-        <v>0.4197841726618705</v>
+        <v>0.08981818181818181</v>
       </c>
       <c r="M12">
-        <v>65.5</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="N12">
-        <v>0.03382390911438161</v>
+        <v>0.2582229150428683</v>
       </c>
       <c r="O12">
-        <v>0.5612682090831191</v>
+        <v>2.682591093117409</v>
       </c>
       <c r="P12">
-        <v>65.5</v>
+        <v>7.16</v>
       </c>
       <c r="Q12">
-        <v>0.03382390911438161</v>
+        <v>0.02790335151987529</v>
       </c>
       <c r="R12">
-        <v>0.5612682090831191</v>
+        <v>0.2898785425101215</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>59.10000000000001</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>0.8919408391186237</v>
       </c>
       <c r="U12">
-        <v>92.8</v>
+        <v>15.2</v>
       </c>
       <c r="V12">
-        <v>0.04792150787503227</v>
+        <v>0.05923616523772408</v>
       </c>
       <c r="W12">
-        <v>0.1665952890792291</v>
+        <v>0.1112612612612613</v>
       </c>
       <c r="X12">
-        <v>0.05732409087725115</v>
+        <v>0.06748618846425415</v>
       </c>
       <c r="Y12">
-        <v>0.109271198201978</v>
+        <v>0.04377507279700711</v>
       </c>
       <c r="Z12">
-        <v>0.2282242837205484</v>
+        <v>1.069224415347573</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>0.04413309468972391</v>
       </c>
       <c r="AB12">
-        <v>0.05614870219420283</v>
+        <v>0.06136098887973317</v>
       </c>
       <c r="AC12">
-        <v>-0.05614870219420283</v>
+        <v>-0.01722789419000927</v>
       </c>
       <c r="AD12">
-        <v>854.9</v>
+        <v>230.9</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>2.095772985230452</v>
       </c>
       <c r="AF12">
-        <v>854.9</v>
+        <v>232.9957729852304</v>
       </c>
       <c r="AG12">
-        <v>762.1</v>
+        <v>217.7957729852305</v>
       </c>
       <c r="AH12">
-        <v>0.306262090707172</v>
+        <v>0.4758941678858391</v>
       </c>
       <c r="AI12">
-        <v>0.5379097715975587</v>
+        <v>0.4165132885109987</v>
       </c>
       <c r="AJ12">
-        <v>0.2824056918402135</v>
+        <v>0.459101419927726</v>
       </c>
       <c r="AK12">
-        <v>0.50925492816572</v>
+        <v>0.4002158484078146</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="AN12">
+        <v>9.416802610114191</v>
+      </c>
+      <c r="AO12">
+        <v>0.8954545454545454</v>
+      </c>
+      <c r="AP12">
+        <v>8.882372470849528</v>
+      </c>
+      <c r="AQ12">
+        <v>0.8954545454545454</v>
       </c>
     </row>
     <row r="13">
@@ -1975,7 +2002,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Srisawad Capital 1969 Public Company Limited (SET:SCAP)</t>
+          <t>Mida Assets Public Company Limited (SET:MIDA)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1984,109 +2011,118 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.3779999999999999</v>
+        <v>0.0159</v>
       </c>
       <c r="E13">
-        <v>0.216</v>
+        <v>0.258</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>0.08368098159509203</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>0.08368098159509203</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>0.1447852760736196</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>0.113590630228667</v>
       </c>
       <c r="K13">
-        <v>14.3</v>
+        <v>7.44</v>
       </c>
       <c r="L13">
-        <v>0.2530973451327434</v>
+        <v>0.09128834355828222</v>
       </c>
       <c r="M13">
-        <v>12</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.01191776740490615</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>0.8391608391608392</v>
+        <v>-0</v>
       </c>
       <c r="P13">
-        <v>12</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.01191776740490615</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>0.8391608391608392</v>
+        <v>-0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
-        <v>52</v>
+        <v>6.2</v>
       </c>
       <c r="V13">
-        <v>0.05164365875459331</v>
+        <v>0.1627296587926509</v>
       </c>
       <c r="W13">
-        <v>0.05017543859649123</v>
+        <v>0.08184818481848184</v>
       </c>
       <c r="X13">
-        <v>0.0563244072321989</v>
+        <v>0.09979547764744315</v>
       </c>
       <c r="Y13">
-        <v>-0.006148968635707672</v>
+        <v>-0.01794729282896131</v>
       </c>
       <c r="Z13">
-        <v>0.2032374100719425</v>
+        <v>0.3525543971968681</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>0.04004687616748005</v>
       </c>
       <c r="AB13">
-        <v>0.05718595759361757</v>
+        <v>0.06145093590845349</v>
       </c>
       <c r="AC13">
-        <v>-0.05718595759361757</v>
+        <v>-0.02140405974097345</v>
       </c>
       <c r="AD13">
-        <v>352.6</v>
+        <v>127.2</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>352.6</v>
+        <v>127.2</v>
       </c>
       <c r="AG13">
-        <v>300.6</v>
+        <v>121</v>
       </c>
       <c r="AH13">
-        <v>0.2593600588451637</v>
+        <v>0.7695099818511797</v>
       </c>
       <c r="AI13">
-        <v>0.5536190924791961</v>
+        <v>0.4825493171471927</v>
       </c>
       <c r="AJ13">
-        <v>0.2299043977055449</v>
+        <v>0.7605279698302955</v>
       </c>
       <c r="AK13">
-        <v>0.5139340058129594</v>
+        <v>0.4700854700854701</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>8.69</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>7.51</v>
+      </c>
+      <c r="AN13">
+        <v>8.653061224489797</v>
+      </c>
+      <c r="AO13">
+        <v>1.357882623705409</v>
+      </c>
+      <c r="AP13">
+        <v>8.231292517006803</v>
+      </c>
+      <c r="AQ13">
+        <v>1.571238348868176</v>
       </c>
     </row>
     <row r="14">
@@ -2097,7 +2133,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ngern Tid Lor Public Company Limited (SET:TIDLOR)</t>
+          <t>AIRA Factoring Public Company Limited (SET:AF)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2105,41 +2141,47 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D14">
+        <v>0.00223</v>
+      </c>
+      <c r="E14">
+        <v>-0.208</v>
+      </c>
       <c r="G14">
-        <v>0</v>
+        <v>0.4494556765163297</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>0.4494556765163297</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>0.3534279181825711</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>0.2822338051673769</v>
       </c>
       <c r="K14">
-        <v>95.90000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="L14">
-        <v>0.2763688760806917</v>
+        <v>0.0864696734059098</v>
       </c>
       <c r="M14">
-        <v>16.8</v>
+        <v>1.4</v>
       </c>
       <c r="N14">
-        <v>0.007882882882882884</v>
+        <v>0.03888888888888889</v>
       </c>
       <c r="O14">
-        <v>0.1751824817518248</v>
+        <v>2.517985611510791</v>
       </c>
       <c r="P14">
-        <v>16.8</v>
+        <v>1.4</v>
       </c>
       <c r="Q14">
-        <v>0.007882882882882884</v>
+        <v>0.03888888888888889</v>
       </c>
       <c r="R14">
-        <v>0.1751824817518248</v>
+        <v>2.517985611510791</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2148,61 +2190,73 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>48.1</v>
+        <v>1.51</v>
       </c>
       <c r="V14">
-        <v>0.02256944444444445</v>
+        <v>0.04194444444444444</v>
       </c>
       <c r="W14">
-        <v>0.149144634525661</v>
+        <v>0.03682119205298014</v>
       </c>
       <c r="X14">
-        <v>0.05961411332471581</v>
+        <v>0.06966063600642619</v>
       </c>
       <c r="Y14">
-        <v>0.08953052120094518</v>
+        <v>-0.03283944395344605</v>
       </c>
       <c r="Z14">
-        <v>0.2098629540478754</v>
+        <v>0.1326120655061484</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>0.03742760785890571</v>
       </c>
       <c r="AB14">
-        <v>0.05719881400983738</v>
+        <v>0.05947283208812727</v>
       </c>
       <c r="AC14">
-        <v>-0.05719881400983738</v>
+        <v>-0.02204522422922157</v>
       </c>
       <c r="AD14">
-        <v>1386.5</v>
+        <v>38.5</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>0.0772924304303373</v>
       </c>
       <c r="AF14">
-        <v>1386.5</v>
+        <v>38.57729243043034</v>
       </c>
       <c r="AG14">
-        <v>1338.4</v>
+        <v>37.06729243043034</v>
       </c>
       <c r="AH14">
-        <v>0.3941495863774626</v>
+        <v>0.5172793376270303</v>
       </c>
       <c r="AI14">
-        <v>0.6802570895888529</v>
+        <v>0.7227285363098984</v>
       </c>
       <c r="AJ14">
-        <v>0.3857505187917916</v>
+        <v>0.5073034896663685</v>
       </c>
       <c r="AK14">
-        <v>0.6725290186422793</v>
+        <v>0.7146563989271032</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1.54</v>
+      </c>
+      <c r="AN14">
+        <v>16.25844594594595</v>
+      </c>
+      <c r="AO14">
+        <v>1.448051948051948</v>
+      </c>
+      <c r="AP14">
+        <v>15.6534174114993</v>
+      </c>
+      <c r="AQ14">
+        <v>1.448051948051948</v>
       </c>
     </row>
     <row r="15">
@@ -2213,7 +2267,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S 11 Group Public Company Limited (SET:S11)</t>
+          <t>T.K.S. Technologies Public Company Limited (SET:TKS)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2222,46 +2276,46 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.024</v>
+        <v>-0.032</v>
       </c>
       <c r="E15">
-        <v>-0.0184</v>
+        <v>-0.117</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>0.2073732718894009</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>0.2073732718894009</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>0.09907834101382489</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>0.09604798793144266</v>
       </c>
       <c r="K15">
-        <v>9.640000000000001</v>
+        <v>7.94</v>
       </c>
       <c r="L15">
-        <v>0.4361990950226244</v>
+        <v>0.1829493087557604</v>
       </c>
       <c r="M15">
-        <v>4.22</v>
+        <v>5.28</v>
       </c>
       <c r="N15">
-        <v>0.04757609921082299</v>
+        <v>0.05222551928783383</v>
       </c>
       <c r="O15">
-        <v>0.437759336099585</v>
+        <v>0.6649874055415617</v>
       </c>
       <c r="P15">
-        <v>4.22</v>
+        <v>5.28</v>
       </c>
       <c r="Q15">
-        <v>0.04757609921082299</v>
+        <v>0.05222551928783383</v>
       </c>
       <c r="R15">
-        <v>0.437759336099585</v>
+        <v>0.6649874055415617</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2270,61 +2324,73 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>1.62</v>
+        <v>4.05</v>
       </c>
       <c r="V15">
-        <v>0.01826381059751973</v>
+        <v>0.0400593471810089</v>
       </c>
       <c r="W15">
-        <v>0.1065193370165746</v>
+        <v>0.06661073825503355</v>
       </c>
       <c r="X15">
-        <v>0.06047766712063649</v>
+        <v>0.05862427241266263</v>
       </c>
       <c r="Y15">
-        <v>0.04604166989593811</v>
+        <v>0.007986465842370921</v>
       </c>
       <c r="Z15">
-        <v>0.1318458417849899</v>
+        <v>0.3120954983460377</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>0.02997614465859781</v>
       </c>
       <c r="AB15">
-        <v>0.05752887031700117</v>
+        <v>0.05694084506396821</v>
       </c>
       <c r="AC15">
-        <v>-0.05752887031700117</v>
+        <v>-0.0269647004053704</v>
       </c>
       <c r="AD15">
-        <v>64.7</v>
+        <v>24.4</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>64.7</v>
+        <v>24.4</v>
       </c>
       <c r="AG15">
-        <v>63.08000000000001</v>
+        <v>20.35</v>
       </c>
       <c r="AH15">
-        <v>0.4217731421121252</v>
+        <v>0.1944223107569721</v>
       </c>
       <c r="AI15">
-        <v>0.4290450928381963</v>
+        <v>0.176939811457578</v>
       </c>
       <c r="AJ15">
-        <v>0.4156015285281329</v>
+        <v>0.1675586661177439</v>
       </c>
       <c r="AK15">
-        <v>0.4228448853733744</v>
+        <v>0.1520358610384759</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>0.791</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>-0.3489999999999999</v>
+      </c>
+      <c r="AN15">
+        <v>3.403068340306834</v>
+      </c>
+      <c r="AO15">
+        <v>5.436156763590391</v>
+      </c>
+      <c r="AP15">
+        <v>2.838214783821478</v>
+      </c>
+      <c r="AQ15">
+        <v>-12.32091690544413</v>
       </c>
     </row>
     <row r="16">
@@ -2335,7 +2401,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Heng Leasing and Capital Public Company Limited (SET:HENG)</t>
+          <t>Plus Tech Innovation Public Company Limited (SET:PTECH)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2343,104 +2409,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D16">
+        <v>0.0345</v>
+      </c>
       <c r="G16">
-        <v>0</v>
+        <v>0.08005586592178772</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>0.07458100558659218</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>0.02547486033519553</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>0.02547486033519553</v>
       </c>
       <c r="K16">
-        <v>10.2</v>
+        <v>-0.083</v>
       </c>
       <c r="L16">
-        <v>0.2588832487309645</v>
+        <v>-0.002318435754189945</v>
       </c>
       <c r="M16">
+        <v>-0</v>
+      </c>
+      <c r="N16">
+        <v>-0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>-0</v>
+      </c>
+      <c r="Q16">
+        <v>-0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0.869</v>
+      </c>
+      <c r="V16">
+        <v>0.009118572927597062</v>
+      </c>
+      <c r="W16">
+        <v>-0.002985611510791367</v>
+      </c>
+      <c r="X16">
+        <v>0.05808025498782304</v>
+      </c>
+      <c r="Y16">
+        <v>-0.06106586649861441</v>
+      </c>
+      <c r="Z16">
+        <v>0.8608459374323706</v>
+      </c>
+      <c r="AA16">
+        <v>0.02192993002621011</v>
+      </c>
+      <c r="AB16">
+        <v>0.05750174628184613</v>
+      </c>
+      <c r="AC16">
+        <v>-0.03557181625563602</v>
+      </c>
+      <c r="AD16">
+        <v>19.1</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>19.1</v>
+      </c>
+      <c r="AG16">
+        <v>18.231</v>
+      </c>
+      <c r="AH16">
+        <v>0.166958041958042</v>
+      </c>
+      <c r="AI16">
+        <v>0.3913934426229509</v>
+      </c>
+      <c r="AJ16">
+        <v>0.1605816913442144</v>
+      </c>
+      <c r="AK16">
+        <v>0.3803592664455155</v>
+      </c>
+      <c r="AL16">
         <v>1.01</v>
       </c>
-      <c r="N16">
-        <v>0.003117283950617284</v>
-      </c>
-      <c r="O16">
-        <v>0.09901960784313726</v>
-      </c>
-      <c r="P16">
+      <c r="AM16">
         <v>1.01</v>
       </c>
-      <c r="Q16">
-        <v>0.003117283950617284</v>
-      </c>
-      <c r="R16">
-        <v>0.09901960784313726</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>3.61</v>
-      </c>
-      <c r="V16">
-        <v>0.01114197530864197</v>
-      </c>
-      <c r="W16">
-        <v>0.1083953241232731</v>
-      </c>
-      <c r="X16">
-        <v>0.05795835944536275</v>
-      </c>
-      <c r="Y16">
-        <v>0.05043696467791037</v>
-      </c>
-      <c r="Z16">
-        <v>0.1566363730331004</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0.05852052255000606</v>
-      </c>
-      <c r="AC16">
-        <v>-0.05852052255000606</v>
-      </c>
-      <c r="AD16">
-        <v>161.8</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>161.8</v>
-      </c>
-      <c r="AG16">
-        <v>158.19</v>
-      </c>
-      <c r="AH16">
-        <v>0.3330588719637711</v>
-      </c>
-      <c r="AI16">
-        <v>0.5482887156895967</v>
-      </c>
-      <c r="AJ16">
-        <v>0.3280657002426429</v>
-      </c>
-      <c r="AK16">
-        <v>0.5426944320559882</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
+      <c r="AN16">
+        <v>4.292134831460674</v>
+      </c>
+      <c r="AO16">
+        <v>0.902970297029703</v>
+      </c>
+      <c r="AP16">
+        <v>4.09685393258427</v>
+      </c>
+      <c r="AQ16">
+        <v>0.902970297029703</v>
       </c>
     </row>
     <row r="17">
@@ -2451,7 +2529,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Muangthai Capital Public Company Limited (SET:MTC)</t>
+          <t>Urbana Property Fund (leasehold) (SET:URBNPF)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2460,10 +2538,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.207</v>
+        <v>-0.185</v>
       </c>
       <c r="E17">
-        <v>0.177</v>
+        <v>-0.433</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2472,97 +2550,100 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>0.6028880866425993</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>0.6028880866425993</v>
       </c>
       <c r="K17">
-        <v>134.1</v>
+        <v>0.041</v>
       </c>
       <c r="L17">
-        <v>0.3568387440127727</v>
+        <v>0.0740072202166065</v>
       </c>
       <c r="M17">
-        <v>20.8</v>
+        <v>-0</v>
       </c>
       <c r="N17">
-        <v>0.008925506350841057</v>
+        <v>-0</v>
       </c>
       <c r="O17">
-        <v>0.1551081282624907</v>
+        <v>-0</v>
       </c>
       <c r="P17">
-        <v>20.8</v>
+        <v>-0</v>
       </c>
       <c r="Q17">
-        <v>0.008925506350841057</v>
+        <v>-0</v>
       </c>
       <c r="R17">
-        <v>0.1551081282624907</v>
+        <v>-0</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
       <c r="U17">
-        <v>96.8</v>
+        <v>0.216</v>
       </c>
       <c r="V17">
-        <v>0.04153793340199107</v>
+        <v>0.06033519553072626</v>
       </c>
       <c r="W17">
-        <v>0.1898626645901175</v>
+        <v>0.004933814681107099</v>
       </c>
       <c r="X17">
-        <v>0.06410207458992499</v>
+        <v>0.07862294275918751</v>
       </c>
       <c r="Y17">
-        <v>0.1257605900001925</v>
+        <v>-0.07368912807808041</v>
       </c>
       <c r="Z17">
-        <v>0.1422407267221802</v>
+        <v>0.03742737467909742</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>0.02256451830833671</v>
       </c>
       <c r="AB17">
-        <v>0.05863861681996427</v>
+        <v>0.06471622714090113</v>
       </c>
       <c r="AC17">
-        <v>-0.05863861681996427</v>
+        <v>-0.04215170883256442</v>
       </c>
       <c r="AD17">
-        <v>2471.1</v>
+        <v>6.25</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>2471.1</v>
+        <v>6.25</v>
       </c>
       <c r="AG17">
-        <v>2374.3</v>
+        <v>6.034</v>
       </c>
       <c r="AH17">
-        <v>0.5146516713527023</v>
+        <v>0.6358087487283824</v>
       </c>
       <c r="AI17">
-        <v>0.7690225002334048</v>
+        <v>0.4203093476798924</v>
       </c>
       <c r="AJ17">
-        <v>0.5046655472187387</v>
+        <v>0.6276263781984605</v>
       </c>
       <c r="AK17">
-        <v>0.7618482271779239</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>0.182</v>
+      </c>
+      <c r="AO17">
+        <v>1.835164835164835</v>
+      </c>
+      <c r="AQ17">
+        <v>1.835164835164835</v>
       </c>
     </row>
     <row r="18">
@@ -2573,7 +2654,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mida Assets Public Company Limited (SET:MIDA)</t>
+          <t>Thitikorn Public Company Limited (SET:TK)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2582,115 +2663,115 @@
         </is>
       </c>
       <c r="D18">
-        <v>-0.0396</v>
+        <v>-0.162</v>
+      </c>
+      <c r="E18">
+        <v>-0.184</v>
       </c>
       <c r="G18">
-        <v>0.08856015779092702</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>0.08856015779092702</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>0.04260355029585799</v>
+        <v>0.007056574936626907</v>
       </c>
       <c r="J18">
-        <v>0.04260355029585799</v>
+        <v>0.004623273234341766</v>
       </c>
       <c r="K18">
-        <v>-5.38</v>
+        <v>4.09</v>
       </c>
       <c r="L18">
-        <v>-0.1061143984220907</v>
+        <v>0.1526119402985074</v>
       </c>
       <c r="M18">
-        <v>-0</v>
+        <v>5.5</v>
       </c>
       <c r="N18">
-        <v>-0</v>
+        <v>0.06962025316455696</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.344743276283619</v>
       </c>
       <c r="P18">
-        <v>-0</v>
+        <v>5.5</v>
       </c>
       <c r="Q18">
-        <v>-0</v>
+        <v>0.06962025316455696</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.344743276283619</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
       <c r="U18">
-        <v>3.23</v>
+        <v>42</v>
       </c>
       <c r="V18">
-        <v>0.096996996996997</v>
+        <v>0.5316455696202531</v>
       </c>
       <c r="W18">
-        <v>-0.04967682363804247</v>
+        <v>0.02676701570680628</v>
       </c>
       <c r="X18">
-        <v>0.09968275883748498</v>
+        <v>0.05840016925756814</v>
       </c>
       <c r="Y18">
-        <v>-0.1493595824755274</v>
+        <v>-0.03163315355076186</v>
       </c>
       <c r="Z18">
-        <v>0.197506817296455</v>
+        <v>0.1787448151409407</v>
       </c>
       <c r="AA18">
-        <v>0.008414491624464357</v>
+        <v>0.0008263861196184779</v>
       </c>
       <c r="AB18">
-        <v>0.06718705372537358</v>
+        <v>0.05685386221625333</v>
       </c>
       <c r="AC18">
-        <v>-0.05877256210090922</v>
+        <v>-0.05602747609663485</v>
       </c>
       <c r="AD18">
-        <v>143.5</v>
+        <v>16.8</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>0.9344189584919944</v>
       </c>
       <c r="AF18">
-        <v>143.5</v>
+        <v>17.734418958492</v>
       </c>
       <c r="AG18">
-        <v>140.27</v>
+        <v>-24.265581041508</v>
       </c>
       <c r="AH18">
-        <v>0.8116515837104072</v>
+        <v>0.1833310123680145</v>
       </c>
       <c r="AI18">
-        <v>0.5338541666666666</v>
+        <v>0.1027877165932816</v>
       </c>
       <c r="AJ18">
-        <v>0.8081465691075648</v>
+        <v>-0.4433331257231373</v>
       </c>
       <c r="AK18">
-        <v>0.5281846594118312</v>
+        <v>-0.1858941207623109</v>
       </c>
       <c r="AL18">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AM18">
-        <v>5.49</v>
+        <v>0</v>
       </c>
       <c r="AN18">
-        <v>28.08219178082192</v>
-      </c>
-      <c r="AO18">
-        <v>0.3297709923664122</v>
+        <v>44.68085106382979</v>
       </c>
       <c r="AP18">
-        <v>27.45009784735812</v>
-      </c>
-      <c r="AQ18">
-        <v>0.3934426229508197</v>
+        <v>-64.53611979124469</v>
       </c>
     </row>
     <row r="19">
@@ -2701,7 +2782,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AEON Thana Sinsap (Thailand) Public Company Limited (SET:AEONTS)</t>
+          <t>Krungthai Card Public Company Limited (SET:KTC)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2710,10 +2791,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.0261</v>
+        <v>0.0566</v>
       </c>
       <c r="E19">
-        <v>0.07530000000000001</v>
+        <v>0.08220000000000001</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2728,28 +2809,28 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>102.5</v>
+        <v>196.9</v>
       </c>
       <c r="L19">
-        <v>0.298572676958928</v>
+        <v>0.4118385275047061</v>
       </c>
       <c r="M19">
-        <v>35.7</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="N19">
-        <v>0.02712353745631363</v>
+        <v>0.02471656710959405</v>
       </c>
       <c r="O19">
-        <v>0.3482926829268293</v>
+        <v>0.4118842051802945</v>
       </c>
       <c r="P19">
-        <v>35.7</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Q19">
-        <v>0.02712353745631363</v>
+        <v>0.02471656710959405</v>
       </c>
       <c r="R19">
-        <v>0.3482926829268293</v>
+        <v>0.4118842051802945</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2758,55 +2839,55 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>114.4</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="V19">
-        <v>0.08691688193283696</v>
+        <v>0.02288796781665244</v>
       </c>
       <c r="W19">
-        <v>0.1823843416370107</v>
+        <v>0.2504770385447144</v>
       </c>
       <c r="X19">
-        <v>0.06857381024299018</v>
+        <v>0.06242066782013758</v>
       </c>
       <c r="Y19">
-        <v>0.1138105313940205</v>
+        <v>0.1880563707245768</v>
       </c>
       <c r="Z19">
-        <v>0.1398199812650185</v>
+        <v>0.2108675517134919</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.05959778929253862</v>
+        <v>0.05812249453976137</v>
       </c>
       <c r="AC19">
-        <v>-0.05959778929253862</v>
+        <v>-0.05812249453976137</v>
       </c>
       <c r="AD19">
-        <v>1933.1</v>
+        <v>1729</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>1933.1</v>
+        <v>1729</v>
       </c>
       <c r="AG19">
-        <v>1818.7</v>
+        <v>1653.9</v>
       </c>
       <c r="AH19">
-        <v>0.5949281383682639</v>
+        <v>0.3450960041515309</v>
       </c>
       <c r="AI19">
-        <v>0.762263406940063</v>
+        <v>0.649487246910334</v>
       </c>
       <c r="AJ19">
-        <v>0.5801460971641839</v>
+        <v>0.3351299872343012</v>
       </c>
       <c r="AK19">
-        <v>0.7510323752890651</v>
+        <v>0.6393119443370699</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2823,7 +2904,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Micro Leasing Public Company Limited (SET:MICRO)</t>
+          <t>Srisawad Capital 1969 Public Company Limited (SET:SCAP)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2831,6 +2912,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D20">
+        <v>0.293</v>
+      </c>
+      <c r="E20">
+        <v>0.233</v>
+      </c>
       <c r="G20">
         <v>0</v>
       </c>
@@ -2844,28 +2931,28 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>3.29</v>
+        <v>29.5</v>
       </c>
       <c r="L20">
-        <v>0.2284722222222222</v>
+        <v>0.2204783258594918</v>
       </c>
       <c r="M20">
-        <v>1.91</v>
+        <v>56.9</v>
       </c>
       <c r="N20">
-        <v>0.01642304385210662</v>
+        <v>0.08492537313432835</v>
       </c>
       <c r="O20">
-        <v>0.5805471124620061</v>
+        <v>1.928813559322034</v>
       </c>
       <c r="P20">
-        <v>1.91</v>
+        <v>56.9</v>
       </c>
       <c r="Q20">
-        <v>0.01642304385210662</v>
+        <v>0.08492537313432835</v>
       </c>
       <c r="R20">
-        <v>0.5805471124620061</v>
+        <v>1.928813559322034</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -2874,55 +2961,55 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>7.35</v>
+        <v>22</v>
       </c>
       <c r="V20">
-        <v>0.06319862424763542</v>
+        <v>0.03283582089552239</v>
       </c>
       <c r="W20">
-        <v>0.05782073813708261</v>
+        <v>0.1045728465083304</v>
       </c>
       <c r="X20">
-        <v>0.05978723025297186</v>
+        <v>0.06804433540059308</v>
       </c>
       <c r="Y20">
-        <v>-0.001966492115889257</v>
+        <v>0.03652851110773729</v>
       </c>
       <c r="Z20">
-        <v>0.1442596674013224</v>
+        <v>0.2296207310794577</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.05973084811485634</v>
+        <v>0.05923677580184739</v>
       </c>
       <c r="AC20">
-        <v>-0.05973084811485634</v>
+        <v>-0.05923677580184739</v>
       </c>
       <c r="AD20">
-        <v>77.5</v>
+        <v>636.5</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>77.5</v>
+        <v>636.5</v>
       </c>
       <c r="AG20">
-        <v>70.15000000000001</v>
+        <v>614.5</v>
       </c>
       <c r="AH20">
-        <v>0.3998968008255934</v>
+        <v>0.4871794871794872</v>
       </c>
       <c r="AI20">
-        <v>0.5762081784386617</v>
+        <v>0.7039371820393718</v>
       </c>
       <c r="AJ20">
-        <v>0.3762402788951462</v>
+        <v>0.4783962631374076</v>
       </c>
       <c r="AK20">
-        <v>0.5517105780574125</v>
+        <v>0.6965540693720245</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2939,7 +3026,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ratchthani Leasing Public Company Limited (SET:THANI)</t>
+          <t>Ngern Tid Lor Public Company Limited (SET:TIDLOR)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2947,12 +3034,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D21">
-        <v>0.115</v>
-      </c>
-      <c r="E21">
-        <v>0.122</v>
-      </c>
       <c r="G21">
         <v>0</v>
       </c>
@@ -2966,85 +3047,85 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>49.1</v>
+        <v>101.4</v>
       </c>
       <c r="L21">
-        <v>0.6084262701363073</v>
+        <v>0.225986182304435</v>
       </c>
       <c r="M21">
-        <v>25.5</v>
+        <v>20.746</v>
       </c>
       <c r="N21">
-        <v>0.03741746148202495</v>
+        <v>0.01121829881576813</v>
       </c>
       <c r="O21">
-        <v>0.5193482688391039</v>
+        <v>0.2045956607495069</v>
       </c>
       <c r="P21">
-        <v>25.5</v>
+        <v>19.9</v>
       </c>
       <c r="Q21">
-        <v>0.03741746148202495</v>
+        <v>0.01076082842156492</v>
       </c>
       <c r="R21">
-        <v>0.5193482688391039</v>
+        <v>0.1962524654832347</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>0.8460000000000001</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>0.04077894533886051</v>
       </c>
       <c r="U21">
-        <v>29.7</v>
+        <v>37</v>
       </c>
       <c r="V21">
-        <v>0.04358033749082905</v>
+        <v>0.02000757043205537</v>
       </c>
       <c r="W21">
-        <v>0.1485627836611195</v>
+        <v>0.1555930642933865</v>
       </c>
       <c r="X21">
-        <v>0.06987035293911362</v>
+        <v>0.06812962173486405</v>
       </c>
       <c r="Y21">
-        <v>0.07869243072200591</v>
+        <v>0.08746344255852247</v>
       </c>
       <c r="Z21">
-        <v>0.05726653420380358</v>
+        <v>0.2263520841846129</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.0598192735093507</v>
+        <v>0.05924996492128815</v>
       </c>
       <c r="AC21">
-        <v>-0.0598192735093507</v>
+        <v>-0.05924996492128815</v>
       </c>
       <c r="AD21">
-        <v>1081.6</v>
+        <v>1768.7</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>1081.6</v>
+        <v>1768.7</v>
       </c>
       <c r="AG21">
-        <v>1051.9</v>
+        <v>1731.7</v>
       </c>
       <c r="AH21">
-        <v>0.6134649197436334</v>
+        <v>0.4888612493090105</v>
       </c>
       <c r="AI21">
-        <v>0.7727922263503858</v>
+        <v>0.7011416792198526</v>
       </c>
       <c r="AJ21">
-        <v>0.6068420445367485</v>
+        <v>0.4835800055850321</v>
       </c>
       <c r="AK21">
-        <v>0.7678662676107745</v>
+        <v>0.6966929514000644</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3061,7 +3142,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SGF Capital Public Company Limited (SET:SGF)</t>
+          <t>Muangthai Capital Public Company Limited (SET:MTC)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3070,10 +3151,13 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.0876</v>
+        <v>0.149</v>
       </c>
       <c r="E22">
-        <v>-0.109</v>
+        <v>0.063</v>
+      </c>
+      <c r="F22">
+        <v>0.219</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3088,82 +3172,85 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>1.26</v>
+        <v>128.2</v>
       </c>
       <c r="L22">
-        <v>0.1752433936022253</v>
+        <v>0.2876374242764191</v>
       </c>
       <c r="M22">
-        <v>-0</v>
+        <v>55.1</v>
       </c>
       <c r="N22">
-        <v>-0</v>
+        <v>0.01974273531835609</v>
       </c>
       <c r="O22">
-        <v>-0</v>
+        <v>0.4297971918876756</v>
       </c>
       <c r="P22">
-        <v>-0</v>
+        <v>55.1</v>
       </c>
       <c r="Q22">
-        <v>-0</v>
+        <v>0.01974273531835609</v>
       </c>
       <c r="R22">
-        <v>-0</v>
+        <v>0.4297971918876756</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
       <c r="U22">
-        <v>1.52</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="V22">
-        <v>0.05277777777777778</v>
+        <v>0.02744634347343151</v>
       </c>
       <c r="W22">
-        <v>0.02446601941747573</v>
+        <v>0.1727297224467798</v>
       </c>
       <c r="X22">
-        <v>0.06165364463654884</v>
+        <v>0.07008451547400815</v>
       </c>
       <c r="Y22">
-        <v>-0.03718762521907311</v>
+        <v>0.1026452069727717</v>
       </c>
       <c r="Z22">
-        <v>0.09175599795814192</v>
+        <v>0.1430129953473448</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.06073911746987637</v>
+        <v>0.05953022155781329</v>
       </c>
       <c r="AC22">
-        <v>-0.06073911746987637</v>
+        <v>-0.05953022155781329</v>
       </c>
       <c r="AD22">
-        <v>24.1</v>
+        <v>3079.7</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>24.1</v>
+        <v>3079.7</v>
       </c>
       <c r="AG22">
-        <v>22.58</v>
+        <v>3003.1</v>
       </c>
       <c r="AH22">
-        <v>0.4555765595463138</v>
+        <v>0.5245971450959015</v>
       </c>
       <c r="AI22">
-        <v>0.338008415147265</v>
+        <v>0.7860789218438919</v>
       </c>
       <c r="AJ22">
-        <v>0.4394706111327365</v>
+        <v>0.5183120469451156</v>
       </c>
       <c r="AK22">
-        <v>0.3235884207509315</v>
+        <v>0.7818129751119443</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3180,7 +3267,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Next Capital Public Company Limited (SET:NCAP)</t>
+          <t>Heng Leasing and Capital Public Company Limited (SET:HENG)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3201,82 +3288,85 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>4.83</v>
+        <v>12.9</v>
       </c>
       <c r="L23">
-        <v>0.2555555555555556</v>
+        <v>0.2311827956989247</v>
       </c>
       <c r="M23">
-        <v>-0</v>
+        <v>6.94</v>
       </c>
       <c r="N23">
-        <v>-0</v>
+        <v>0.03242990654205608</v>
       </c>
       <c r="O23">
-        <v>-0</v>
+        <v>0.537984496124031</v>
       </c>
       <c r="P23">
-        <v>-0</v>
+        <v>6.94</v>
       </c>
       <c r="Q23">
-        <v>-0</v>
+        <v>0.03242990654205608</v>
       </c>
       <c r="R23">
-        <v>-0</v>
+        <v>0.537984496124031</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
       <c r="U23">
-        <v>18.5</v>
+        <v>7.62</v>
       </c>
       <c r="V23">
-        <v>0.1489533011272142</v>
+        <v>0.03560747663551402</v>
       </c>
       <c r="W23">
-        <v>0.0853356890459364</v>
+        <v>0.09677419354838709</v>
       </c>
       <c r="X23">
-        <v>0.06205650012448723</v>
+        <v>0.07128059256790595</v>
       </c>
       <c r="Y23">
-        <v>0.02327918892144917</v>
+        <v>0.02549360098048115</v>
       </c>
       <c r="Z23">
-        <v>0.1405204460966543</v>
+        <v>0.1914302377440049</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.06093267810999252</v>
+        <v>0.05968316251505363</v>
       </c>
       <c r="AC23">
-        <v>-0.06093267810999252</v>
+        <v>-0.05968316251505363</v>
       </c>
       <c r="AD23">
-        <v>108.5</v>
+        <v>255.4</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>108.5</v>
+        <v>255.4</v>
       </c>
       <c r="AG23">
-        <v>90</v>
+        <v>247.78</v>
       </c>
       <c r="AH23">
-        <v>0.4662655779974216</v>
+        <v>0.544098849595228</v>
       </c>
       <c r="AI23">
-        <v>0.4963403476669717</v>
+        <v>0.639939864695565</v>
       </c>
       <c r="AJ23">
-        <v>0.4201680672268908</v>
+        <v>0.5365758586339816</v>
       </c>
       <c r="AK23">
-        <v>0.4497751124437781</v>
+        <v>0.6329314396648615</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3293,7 +3383,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lease IT Public Company Limited (SET:LIT)</t>
+          <t>S 11 Group Public Company Limited (SET:S11)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3301,80 +3391,104 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D24">
+        <v>-0.0843</v>
+      </c>
+      <c r="E24">
+        <v>-0.15</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
       <c r="K24">
-        <v>-4.17</v>
+        <v>5.2</v>
+      </c>
+      <c r="L24">
+        <v>0.2765957446808511</v>
       </c>
       <c r="M24">
-        <v>-0</v>
+        <v>3.35</v>
       </c>
       <c r="N24">
-        <v>-0</v>
+        <v>0.04738330975954738</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>0.6442307692307693</v>
       </c>
       <c r="P24">
-        <v>-0</v>
+        <v>3.35</v>
       </c>
       <c r="Q24">
-        <v>-0</v>
+        <v>0.04738330975954738</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>0.6442307692307693</v>
       </c>
       <c r="S24">
         <v>0</v>
       </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
       <c r="U24">
-        <v>5.14</v>
+        <v>2.52</v>
       </c>
       <c r="V24">
-        <v>0.2196581196581197</v>
+        <v>0.03564356435643564</v>
       </c>
       <c r="W24">
-        <v>-0.1353896103896104</v>
+        <v>0.06039488966318235</v>
       </c>
       <c r="X24">
-        <v>0.06231763763955622</v>
+        <v>0.07553403644651455</v>
       </c>
       <c r="Y24">
-        <v>-0.1977072480291666</v>
+        <v>-0.0151391467833322</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>0.126022254993967</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.06105413806171008</v>
+        <v>0.06013833451483665</v>
       </c>
       <c r="AC24">
-        <v>-0.06105413806171008</v>
+        <v>-0.06013833451483665</v>
       </c>
       <c r="AD24">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="AG24">
-        <v>15.86</v>
+        <v>104.48</v>
       </c>
       <c r="AH24">
-        <v>0.472972972972973</v>
+        <v>0.60213843556556</v>
       </c>
       <c r="AI24">
-        <v>0.4093567251461989</v>
+        <v>0.541224076884168</v>
       </c>
       <c r="AJ24">
-        <v>0.4039735099337748</v>
+        <v>0.5964151158808083</v>
       </c>
       <c r="AK24">
-        <v>0.3435875216637782</v>
+        <v>0.5353007480274619</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3391,7 +3505,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Eastern Commercial Leasing Public Company Limited (SET:ECL)</t>
+          <t>Micro Leasing Public Company Limited (SET:MICRO)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3399,12 +3513,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D25">
-        <v>0.09380000000000001</v>
-      </c>
-      <c r="E25">
-        <v>0.121</v>
-      </c>
       <c r="G25">
         <v>0</v>
       </c>
@@ -3412,34 +3520,34 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0.0005811314488577302</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>0.0004692159772517479</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>5.65</v>
+        <v>-1.14</v>
       </c>
       <c r="L25">
-        <v>0.4094202898550725</v>
+        <v>-0.08085106382978723</v>
       </c>
       <c r="M25">
-        <v>3.82</v>
+        <v>0.921</v>
       </c>
       <c r="N25">
-        <v>0.0584097859327217</v>
+        <v>0.01545302013422819</v>
       </c>
       <c r="O25">
-        <v>0.6761061946902654</v>
+        <v>-0.8078947368421053</v>
       </c>
       <c r="P25">
-        <v>3.82</v>
+        <v>0.921</v>
       </c>
       <c r="Q25">
-        <v>0.0584097859327217</v>
+        <v>0.01545302013422819</v>
       </c>
       <c r="R25">
-        <v>0.6761061946902654</v>
+        <v>-0.8078947368421053</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -3448,67 +3556,61 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>0.607</v>
+        <v>18</v>
       </c>
       <c r="V25">
-        <v>0.009281345565749234</v>
+        <v>0.302013422818792</v>
       </c>
       <c r="W25">
-        <v>0.1080305927342256</v>
+        <v>-0.02192307692307692</v>
       </c>
       <c r="X25">
-        <v>0.06404619817641923</v>
+        <v>0.07664902164033441</v>
       </c>
       <c r="Y25">
-        <v>0.04398439455780641</v>
+        <v>-0.09857209856341133</v>
       </c>
       <c r="Z25">
-        <v>0.09512983372543379</v>
+        <v>0.1154318460908719</v>
       </c>
       <c r="AA25">
-        <v>4.46364378972757e-05</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.06178705295525799</v>
+        <v>0.06023909924516677</v>
       </c>
       <c r="AC25">
-        <v>-0.06174241651736072</v>
+        <v>-0.06023909924516677</v>
       </c>
       <c r="AD25">
-        <v>69</v>
+        <v>95.2</v>
       </c>
       <c r="AE25">
-        <v>0.01490193002881661</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>69.01490193002881</v>
+        <v>95.2</v>
       </c>
       <c r="AG25">
-        <v>68.40790193002881</v>
+        <v>77.2</v>
       </c>
       <c r="AH25">
-        <v>0.5134468049231274</v>
+        <v>0.6149870801033591</v>
       </c>
       <c r="AI25">
-        <v>0.5872863849311803</v>
+        <v>0.6189856957087125</v>
       </c>
       <c r="AJ25">
-        <v>0.5112396274309783</v>
+        <v>0.5643274853801169</v>
       </c>
       <c r="AK25">
-        <v>0.5851435258069382</v>
+        <v>0.5684830633284241</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
         <v>0</v>
-      </c>
-      <c r="AN25">
-        <v>6272.727272727273</v>
-      </c>
-      <c r="AP25">
-        <v>6218.900175457165</v>
       </c>
     </row>
     <row r="26">
@@ -3519,7 +3621,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mida Leasing Public Company Limited (SET:ML)</t>
+          <t>AEON Thana Sinsap (Thailand) Public Company Limited (SET:AEONTS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3528,10 +3630,10 @@
         </is>
       </c>
       <c r="D26">
-        <v>-0.0623</v>
+        <v>-0.00895</v>
       </c>
       <c r="E26">
-        <v>-0.05690000000000001</v>
+        <v>-0.0125</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3546,82 +3648,85 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>2.41</v>
+        <v>93</v>
       </c>
       <c r="L26">
-        <v>0.3077905491698595</v>
+        <v>0.2655625356938892</v>
       </c>
       <c r="M26">
-        <v>-0</v>
+        <v>39.4</v>
       </c>
       <c r="N26">
-        <v>-0</v>
+        <v>0.0336694582122714</v>
       </c>
       <c r="O26">
-        <v>-0</v>
+        <v>0.4236559139784946</v>
       </c>
       <c r="P26">
-        <v>-0</v>
+        <v>39.4</v>
       </c>
       <c r="Q26">
-        <v>-0</v>
+        <v>0.0336694582122714</v>
       </c>
       <c r="R26">
-        <v>-0</v>
+        <v>0.4236559139784946</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
       <c r="U26">
-        <v>0.65</v>
+        <v>108.4</v>
       </c>
       <c r="V26">
-        <v>0.01884057971014493</v>
+        <v>0.09263373782259443</v>
       </c>
       <c r="W26">
-        <v>0.03990066225165563</v>
+        <v>0.1576805696846389</v>
       </c>
       <c r="X26">
-        <v>0.06772623645815369</v>
+        <v>0.07735014637444365</v>
       </c>
       <c r="Y26">
-        <v>-0.02782557420649806</v>
+        <v>0.08033042331019521</v>
       </c>
       <c r="Z26">
-        <v>0.06828885400313972</v>
+        <v>0.1454017023043388</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.06302514675572832</v>
+        <v>0.06029919545349274</v>
       </c>
       <c r="AC26">
-        <v>-0.06302514675572832</v>
+        <v>-0.06029919545349274</v>
       </c>
       <c r="AD26">
-        <v>48</v>
+        <v>1930.9</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>48</v>
+        <v>1930.9</v>
       </c>
       <c r="AG26">
-        <v>47.35</v>
+        <v>1822.5</v>
       </c>
       <c r="AH26">
-        <v>0.5818181818181818</v>
+        <v>0.6226500274096288</v>
       </c>
       <c r="AI26">
-        <v>0.4610951008645534</v>
+        <v>0.7360856968587985</v>
       </c>
       <c r="AJ26">
-        <v>0.5784972510690287</v>
+        <v>0.6089818558492331</v>
       </c>
       <c r="AK26">
-        <v>0.457709038182697</v>
+        <v>0.7247097184666772</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -3638,7 +3743,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>G Capital Public Company Limited (SET:GCAP)</t>
+          <t>Eastern Commercial Leasing Public Company Limited (SET:ECL)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3647,7 +3752,10 @@
         </is>
       </c>
       <c r="D27">
-        <v>-0.0565</v>
+        <v>0.0183</v>
+      </c>
+      <c r="E27">
+        <v>0.0114</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3656,34 +3764,34 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>0.0008562150560608691</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>0.0006857331248985272</v>
       </c>
       <c r="K27">
-        <v>-0.398</v>
+        <v>3.6</v>
       </c>
       <c r="L27">
-        <v>-0.2</v>
+        <v>0.288</v>
       </c>
       <c r="M27">
-        <v>0.794</v>
+        <v>2.43</v>
       </c>
       <c r="N27">
-        <v>0.06061068702290077</v>
+        <v>0.05317286652078775</v>
       </c>
       <c r="O27">
-        <v>-1.994974874371859</v>
+        <v>0.675</v>
       </c>
       <c r="P27">
-        <v>0.794</v>
+        <v>2.43</v>
       </c>
       <c r="Q27">
-        <v>0.06061068702290077</v>
+        <v>0.05317286652078775</v>
       </c>
       <c r="R27">
-        <v>-1.994974874371859</v>
+        <v>0.675</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -3692,61 +3800,67 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>1.4</v>
+        <v>1.07</v>
       </c>
       <c r="V27">
-        <v>0.1068702290076336</v>
+        <v>0.02341356673960613</v>
       </c>
       <c r="W27">
-        <v>-0.02905109489051095</v>
+        <v>0.07422680412371134</v>
       </c>
       <c r="X27">
-        <v>0.07422516659821951</v>
+        <v>0.07912992417666709</v>
       </c>
       <c r="Y27">
-        <v>-0.1032762614887305</v>
+        <v>-0.004903120052955748</v>
       </c>
       <c r="Z27">
-        <v>0.03656743844174936</v>
+        <v>0.1069111776649194</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>7.331253594674681e-05</v>
       </c>
       <c r="AB27">
-        <v>0.06453073872817232</v>
+        <v>0.06044152036810833</v>
       </c>
       <c r="AC27">
-        <v>-0.06453073872817232</v>
+        <v>-0.06036820783216158</v>
       </c>
       <c r="AD27">
-        <v>26</v>
+        <v>81.5</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>0.02648655899619569</v>
       </c>
       <c r="AF27">
-        <v>26</v>
+        <v>81.5264865589962</v>
       </c>
       <c r="AG27">
-        <v>24.6</v>
+        <v>80.4564865589962</v>
       </c>
       <c r="AH27">
-        <v>0.6649616368286445</v>
+        <v>0.6407980662202092</v>
       </c>
       <c r="AI27">
-        <v>0.6582278481012658</v>
+        <v>0.6142442904397843</v>
       </c>
       <c r="AJ27">
-        <v>0.6525198938992043</v>
+        <v>0.637751484315246</v>
       </c>
       <c r="AK27">
-        <v>0.6456692913385826</v>
+        <v>0.6111091725278806</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27">
         <v>0</v>
+      </c>
+      <c r="AN27">
+        <v>5093.75</v>
+      </c>
+      <c r="AP27">
+        <v>5028.530409937262</v>
       </c>
     </row>
     <row r="28">
@@ -3757,7 +3871,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Asia Sermkij Leasing Public Company Limited (SET:ASK)</t>
+          <t>Mida Leasing Public Company Limited (SET:ML)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3766,10 +3880,10 @@
         </is>
       </c>
       <c r="D28">
-        <v>0.138</v>
+        <v>-0.0289</v>
       </c>
       <c r="E28">
-        <v>0.15</v>
+        <v>-0.277</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3784,85 +3898,82 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>38.3</v>
+        <v>0.534</v>
       </c>
       <c r="L28">
-        <v>0.4903969270166453</v>
+        <v>0.059070796460177</v>
       </c>
       <c r="M28">
-        <v>15.9</v>
+        <v>-0</v>
       </c>
       <c r="N28">
-        <v>0.02933038184836746</v>
+        <v>-0</v>
       </c>
       <c r="O28">
-        <v>0.4151436031331593</v>
+        <v>-0</v>
       </c>
       <c r="P28">
-        <v>15.9</v>
+        <v>-0</v>
       </c>
       <c r="Q28">
-        <v>0.02933038184836746</v>
+        <v>-0</v>
       </c>
       <c r="R28">
-        <v>0.4151436031331593</v>
+        <v>-0</v>
       </c>
       <c r="S28">
         <v>0</v>
       </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
       <c r="U28">
-        <v>12.5</v>
+        <v>2.64</v>
       </c>
       <c r="V28">
-        <v>0.02305847629588637</v>
+        <v>0.1047619047619048</v>
       </c>
       <c r="W28">
-        <v>0.1444737834779328</v>
+        <v>0.009518716577540108</v>
       </c>
       <c r="X28">
-        <v>0.08184083748052443</v>
+        <v>0.08242385529633925</v>
       </c>
       <c r="Y28">
-        <v>0.0626329459974084</v>
+        <v>-0.07290513871879914</v>
       </c>
       <c r="Z28">
-        <v>0.0517629904559915</v>
+        <v>0.0873852102464959</v>
       </c>
       <c r="AA28">
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>0.06567716188546117</v>
+        <v>0.06067176659328245</v>
       </c>
       <c r="AC28">
-        <v>-0.06567716188546117</v>
+        <v>-0.06067176659328245</v>
       </c>
       <c r="AD28">
-        <v>1452.9</v>
+        <v>51.2</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>1452.9</v>
+        <v>51.2</v>
       </c>
       <c r="AG28">
-        <v>1440.4</v>
+        <v>48.56</v>
       </c>
       <c r="AH28">
-        <v>0.7282706766917294</v>
+        <v>0.6701570680628273</v>
       </c>
       <c r="AI28">
-        <v>0.8475673783689185</v>
+        <v>0.4667274384685506</v>
       </c>
       <c r="AJ28">
-        <v>0.7265573770491803</v>
+        <v>0.658351409978308</v>
       </c>
       <c r="AK28">
-        <v>0.8464476699770818</v>
+        <v>0.4535774332150196</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -3879,7 +3990,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ASIA Capital Group Public Company Limited (SET:ACAP)</t>
+          <t>Lease IT Public Company Limited (SET:LIT)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3888,7 +3999,7 @@
         </is>
       </c>
       <c r="K29">
-        <v>-11.4</v>
+        <v>-3.35</v>
       </c>
       <c r="M29">
         <v>-0</v>
@@ -3912,19 +4023,19 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>0.143</v>
+        <v>4.97</v>
       </c>
       <c r="V29">
-        <v>0.01953551912568306</v>
+        <v>0.3793893129770992</v>
       </c>
       <c r="W29">
-        <v>-4.691358024691358</v>
+        <v>-0.1105610561056106</v>
       </c>
       <c r="X29">
-        <v>0.1608074555594594</v>
+        <v>0.06528936070896886</v>
       </c>
       <c r="Y29">
-        <v>-4.852165480250817</v>
+        <v>-0.1758504168145794</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3933,40 +4044,1257 @@
         <v>0</v>
       </c>
       <c r="AB29">
-        <v>0.07169586357777237</v>
+        <v>0.06074012743397185</v>
       </c>
       <c r="AC29">
-        <v>-0.07169586357777237</v>
+        <v>-0.06074012743397185</v>
       </c>
       <c r="AD29">
-        <v>72.40000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>72.40000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="AG29">
-        <v>72.25700000000001</v>
+        <v>4.760000000000001</v>
       </c>
       <c r="AH29">
-        <v>0.9081786251881586</v>
+        <v>0.4261936049058257</v>
       </c>
       <c r="AI29">
-        <v>1.143940590930637</v>
+        <v>0.2578849721706865</v>
       </c>
       <c r="AJ29">
-        <v>0.908013622026465</v>
+        <v>0.2665173572228444</v>
       </c>
       <c r="AK29">
-        <v>1.144266552646998</v>
+        <v>0.1452991452991453</v>
       </c>
       <c r="AL29">
         <v>0</v>
       </c>
       <c r="AM29">
         <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Saksiam Leasing Public Company Limited (SET:SAK)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>20.5</v>
+      </c>
+      <c r="L30">
+        <v>0.3355155482815057</v>
+      </c>
+      <c r="M30">
+        <v>7.85</v>
+      </c>
+      <c r="N30">
+        <v>0.03077224617796942</v>
+      </c>
+      <c r="O30">
+        <v>0.3829268292682927</v>
+      </c>
+      <c r="P30">
+        <v>7.85</v>
+      </c>
+      <c r="Q30">
+        <v>0.03077224617796942</v>
+      </c>
+      <c r="R30">
+        <v>0.3829268292682927</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>11.1</v>
+      </c>
+      <c r="V30">
+        <v>0.04351234809878479</v>
+      </c>
+      <c r="W30">
+        <v>0.1501831501831502</v>
+      </c>
+      <c r="X30">
+        <v>0.06573358372862968</v>
+      </c>
+      <c r="Y30">
+        <v>0.08444956645452049</v>
+      </c>
+      <c r="Z30">
+        <v>0.2148911476101713</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0.06087499177941574</v>
+      </c>
+      <c r="AC30">
+        <v>-0.06087499177941574</v>
+      </c>
+      <c r="AD30">
+        <v>198</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>198</v>
+      </c>
+      <c r="AG30">
+        <v>186.9</v>
+      </c>
+      <c r="AH30">
+        <v>0.4369896270139042</v>
+      </c>
+      <c r="AI30">
+        <v>0.5625</v>
+      </c>
+      <c r="AJ30">
+        <v>0.4228506787330317</v>
+      </c>
+      <c r="AK30">
+        <v>0.5482546201232034</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ratchthani Leasing Public Company Limited (SET:THANI)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>0.0164</v>
+      </c>
+      <c r="E31">
+        <v>-0.00366</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>40.4</v>
+      </c>
+      <c r="L31">
+        <v>0.5674157303370786</v>
+      </c>
+      <c r="M31">
+        <v>26.3</v>
+      </c>
+      <c r="N31">
+        <v>0.06106338518690504</v>
+      </c>
+      <c r="O31">
+        <v>0.650990099009901</v>
+      </c>
+      <c r="P31">
+        <v>26.3</v>
+      </c>
+      <c r="Q31">
+        <v>0.06106338518690504</v>
+      </c>
+      <c r="R31">
+        <v>0.650990099009901</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>18.3</v>
+      </c>
+      <c r="V31">
+        <v>0.04248897144183887</v>
+      </c>
+      <c r="W31">
+        <v>0.1270440251572327</v>
+      </c>
+      <c r="X31">
+        <v>0.09098929021890145</v>
+      </c>
+      <c r="Y31">
+        <v>0.03605473493833125</v>
+      </c>
+      <c r="Z31">
+        <v>0.05197459668588949</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0.0611251863287879</v>
+      </c>
+      <c r="AC31">
+        <v>-0.0611251863287879</v>
+      </c>
+      <c r="AD31">
+        <v>1152.6</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>1152.6</v>
+      </c>
+      <c r="AG31">
+        <v>1134.3</v>
+      </c>
+      <c r="AH31">
+        <v>0.7279732204888524</v>
+      </c>
+      <c r="AI31">
+        <v>0.7709183332218581</v>
+      </c>
+      <c r="AJ31">
+        <v>0.7247923322683706</v>
+      </c>
+      <c r="AK31">
+        <v>0.7680796316359697</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Asia Sermkij Leasing Public Company Limited (SET:ASK)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>0.138</v>
+      </c>
+      <c r="E32">
+        <v>0.134</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>40.2</v>
+      </c>
+      <c r="L32">
+        <v>0.4663573085846868</v>
+      </c>
+      <c r="M32">
+        <v>20.8</v>
+      </c>
+      <c r="N32">
+        <v>0.06768630003254149</v>
+      </c>
+      <c r="O32">
+        <v>0.5174129353233831</v>
+      </c>
+      <c r="P32">
+        <v>20.8</v>
+      </c>
+      <c r="Q32">
+        <v>0.06768630003254149</v>
+      </c>
+      <c r="R32">
+        <v>0.5174129353233831</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>13</v>
+      </c>
+      <c r="V32">
+        <v>0.04230393752033843</v>
+      </c>
+      <c r="W32">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="X32">
+        <v>0.1312629441575492</v>
+      </c>
+      <c r="Y32">
+        <v>0.02258320968860461</v>
+      </c>
+      <c r="Z32">
+        <v>0.05065522712581536</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0.0620890434055902</v>
+      </c>
+      <c r="AC32">
+        <v>-0.0620890434055902</v>
+      </c>
+      <c r="AD32">
+        <v>1753.4</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>1753.4</v>
+      </c>
+      <c r="AG32">
+        <v>1740.4</v>
+      </c>
+      <c r="AH32">
+        <v>0.8508759159508904</v>
+      </c>
+      <c r="AI32">
+        <v>0.8587520814967186</v>
+      </c>
+      <c r="AJ32">
+        <v>0.8499291888460224</v>
+      </c>
+      <c r="AK32">
+        <v>0.8578470031545741</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Srisawad Corporation Public Company Limited (SET:SAWAD)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>0.206</v>
+      </c>
+      <c r="E33">
+        <v>0.148</v>
+      </c>
+      <c r="F33">
+        <v>0.196</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>135.3</v>
+      </c>
+      <c r="L33">
+        <v>0.3461243284727552</v>
+      </c>
+      <c r="M33">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="N33">
+        <v>0.0415514168049665</v>
+      </c>
+      <c r="O33">
+        <v>0.4996304508499629</v>
+      </c>
+      <c r="P33">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="Q33">
+        <v>0.0415514168049665</v>
+      </c>
+      <c r="R33">
+        <v>0.4996304508499629</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>196.5</v>
+      </c>
+      <c r="V33">
+        <v>0.1207818550617739</v>
+      </c>
+      <c r="W33">
+        <v>0.208667489204195</v>
+      </c>
+      <c r="X33">
+        <v>0.07255410152095595</v>
+      </c>
+      <c r="Y33">
+        <v>0.136113387683239</v>
+      </c>
+      <c r="Z33">
+        <v>0.2771357674583481</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0.06245134156543991</v>
+      </c>
+      <c r="AC33">
+        <v>-0.06245134156543991</v>
+      </c>
+      <c r="AD33">
+        <v>2097.5</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>2097.5</v>
+      </c>
+      <c r="AG33">
+        <v>1901</v>
+      </c>
+      <c r="AH33">
+        <v>0.5631779615508539</v>
+      </c>
+      <c r="AI33">
+        <v>0.7184941595587983</v>
+      </c>
+      <c r="AJ33">
+        <v>0.5388474730009354</v>
+      </c>
+      <c r="AK33">
+        <v>0.6981783458204789</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Next Capital Public Company Limited (SET:NCAP)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>7.89</v>
+      </c>
+      <c r="L34">
+        <v>0.3491150442477876</v>
+      </c>
+      <c r="M34">
+        <v>3.15</v>
+      </c>
+      <c r="N34">
+        <v>0.0302013422818792</v>
+      </c>
+      <c r="O34">
+        <v>0.3992395437262358</v>
+      </c>
+      <c r="P34">
+        <v>-0</v>
+      </c>
+      <c r="Q34">
+        <v>-0</v>
+      </c>
+      <c r="R34">
+        <v>-0</v>
+      </c>
+      <c r="S34">
+        <v>3.15</v>
+      </c>
+      <c r="T34">
+        <v>1</v>
+      </c>
+      <c r="U34">
+        <v>3.06</v>
+      </c>
+      <c r="V34">
+        <v>0.02933844678811122</v>
+      </c>
+      <c r="W34">
+        <v>0.07179253867151955</v>
+      </c>
+      <c r="X34">
+        <v>0.07302948391969967</v>
+      </c>
+      <c r="Y34">
+        <v>-0.001236945248180119</v>
+      </c>
+      <c r="Z34">
+        <v>0.1130565282641321</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0.06253527490683161</v>
+      </c>
+      <c r="AC34">
+        <v>-0.06253527490683161</v>
+      </c>
+      <c r="AD34">
+        <v>138.2</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>138.2</v>
+      </c>
+      <c r="AG34">
+        <v>135.14</v>
+      </c>
+      <c r="AH34">
+        <v>0.5698969072164948</v>
+      </c>
+      <c r="AI34">
+        <v>0.5317429780684879</v>
+      </c>
+      <c r="AJ34">
+        <v>0.5644002672903441</v>
+      </c>
+      <c r="AK34">
+        <v>0.5261641488864662</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SGF Capital Public Company Limited (SET:SGF)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>-0.0839</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>-0.439</v>
+      </c>
+      <c r="L35">
+        <v>-0.06353111432706222</v>
+      </c>
+      <c r="M35">
+        <v>-0</v>
+      </c>
+      <c r="N35">
+        <v>-0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>-0</v>
+      </c>
+      <c r="Q35">
+        <v>-0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>1.31</v>
+      </c>
+      <c r="V35">
+        <v>0.0775147928994083</v>
+      </c>
+      <c r="W35">
+        <v>-0.009300847457627118</v>
+      </c>
+      <c r="X35">
+        <v>0.08074336162551443</v>
+      </c>
+      <c r="Y35">
+        <v>-0.09004420908314155</v>
+      </c>
+      <c r="Z35">
+        <v>0.09902550874175979</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0.06360843579368711</v>
+      </c>
+      <c r="AC35">
+        <v>-0.06360843579368711</v>
+      </c>
+      <c r="AD35">
+        <v>32.2</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>32.2</v>
+      </c>
+      <c r="AG35">
+        <v>30.89</v>
+      </c>
+      <c r="AH35">
+        <v>0.6558044806517312</v>
+      </c>
+      <c r="AI35">
+        <v>0.4</v>
+      </c>
+      <c r="AJ35">
+        <v>0.6463695333751831</v>
+      </c>
+      <c r="AK35">
+        <v>0.3900745043566107</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>G Capital Public Company Limited (SET:GCAP)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>-0.426</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>-2.15</v>
+      </c>
+      <c r="L36">
+        <v>-8.49802371541502</v>
+      </c>
+      <c r="M36">
+        <v>-0</v>
+      </c>
+      <c r="N36">
+        <v>-0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>-0</v>
+      </c>
+      <c r="Q36">
+        <v>-0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0.467</v>
+      </c>
+      <c r="V36">
+        <v>0.0686764705882353</v>
+      </c>
+      <c r="W36">
+        <v>-0.1592592592592592</v>
+      </c>
+      <c r="X36">
+        <v>0.09353538711340952</v>
+      </c>
+      <c r="Y36">
+        <v>-0.2527946463726687</v>
+      </c>
+      <c r="Z36">
+        <v>0.006640419947506562</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0.06467825896763288</v>
+      </c>
+      <c r="AC36">
+        <v>-0.06467825896763288</v>
+      </c>
+      <c r="AD36">
+        <v>19.5</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>19.5</v>
+      </c>
+      <c r="AG36">
+        <v>19.033</v>
+      </c>
+      <c r="AH36">
+        <v>0.7414448669201521</v>
+      </c>
+      <c r="AI36">
+        <v>0.6037151702786379</v>
+      </c>
+      <c r="AJ36">
+        <v>0.7367707970425424</v>
+      </c>
+      <c r="AK36">
+        <v>0.5979015487073163</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Salee Printing Public Company Limited (SET:SLP)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>0.014</v>
+      </c>
+      <c r="G37">
+        <v>0.03302158273381295</v>
+      </c>
+      <c r="H37">
+        <v>0.03302158273381295</v>
+      </c>
+      <c r="I37">
+        <v>-0.1016320121396896</v>
+      </c>
+      <c r="J37">
+        <v>-0.1016320121396896</v>
+      </c>
+      <c r="K37">
+        <v>-1.31</v>
+      </c>
+      <c r="L37">
+        <v>-0.09424460431654677</v>
+      </c>
+      <c r="M37">
+        <v>-0</v>
+      </c>
+      <c r="N37">
+        <v>-0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>-0</v>
+      </c>
+      <c r="Q37">
+        <v>-0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0.48</v>
+      </c>
+      <c r="V37">
+        <v>0.03692307692307692</v>
+      </c>
+      <c r="W37">
+        <v>-0.05954545454545455</v>
+      </c>
+      <c r="X37">
+        <v>0.05596665478940765</v>
+      </c>
+      <c r="Y37">
+        <v>-0.1155121093348622</v>
+      </c>
+      <c r="Z37">
+        <v>0.6019811282851908</v>
+      </c>
+      <c r="AA37">
+        <v>-0.06118055333774455</v>
+      </c>
+      <c r="AB37">
+        <v>0.05591290966746056</v>
+      </c>
+      <c r="AC37">
+        <v>-0.1170934630052051</v>
+      </c>
+      <c r="AD37">
+        <v>0.53</v>
+      </c>
+      <c r="AE37">
+        <v>0.008424843708427728</v>
+      </c>
+      <c r="AF37">
+        <v>0.5384248437084278</v>
+      </c>
+      <c r="AG37">
+        <v>0.05842484370842782</v>
+      </c>
+      <c r="AH37">
+        <v>0.03977012465808712</v>
+      </c>
+      <c r="AI37">
+        <v>0.02443118541941251</v>
+      </c>
+      <c r="AJ37">
+        <v>0.004474111112763881</v>
+      </c>
+      <c r="AK37">
+        <v>0.002710070152712406</v>
+      </c>
+      <c r="AL37">
+        <v>0.041</v>
+      </c>
+      <c r="AM37">
+        <v>0.041</v>
+      </c>
+      <c r="AN37">
+        <v>4.045801526717558</v>
+      </c>
+      <c r="AO37">
+        <v>-34.63414634146341</v>
+      </c>
+      <c r="AP37">
+        <v>0.4459911733467772</v>
+      </c>
+      <c r="AQ37">
+        <v>-34.63414634146341</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SG Capital Public Company Limited (SET:SGC)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G38">
+        <v>0.6026587887740029</v>
+      </c>
+      <c r="H38">
+        <v>0.6026587887740029</v>
+      </c>
+      <c r="I38">
+        <v>-0.7991137370753323</v>
+      </c>
+      <c r="J38">
+        <v>-0.7991137370753323</v>
+      </c>
+      <c r="K38">
+        <v>-56.8</v>
+      </c>
+      <c r="L38">
+        <v>-0.8389955686853766</v>
+      </c>
+      <c r="M38">
+        <v>9.84</v>
+      </c>
+      <c r="N38">
+        <v>0.07094448449891853</v>
+      </c>
+      <c r="O38">
+        <v>-0.1732394366197183</v>
+      </c>
+      <c r="P38">
+        <v>9.84</v>
+      </c>
+      <c r="Q38">
+        <v>0.07094448449891853</v>
+      </c>
+      <c r="R38">
+        <v>-0.1732394366197183</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>21.9</v>
+      </c>
+      <c r="V38">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="W38">
+        <v>-0.8792569659442725</v>
+      </c>
+      <c r="X38">
+        <v>0.08190602003933196</v>
+      </c>
+      <c r="Y38">
+        <v>-0.9611629859836045</v>
+      </c>
+      <c r="Z38">
+        <v>0.1833942841663281</v>
+      </c>
+      <c r="AA38">
+        <v>-0.1465528917784099</v>
+      </c>
+      <c r="AB38">
+        <v>0.06515584737080059</v>
+      </c>
+      <c r="AC38">
+        <v>-0.2117087391492105</v>
+      </c>
+      <c r="AD38">
+        <v>276.4</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>276.4</v>
+      </c>
+      <c r="AG38">
+        <v>254.5</v>
+      </c>
+      <c r="AH38">
+        <v>0.6658636473139002</v>
+      </c>
+      <c r="AI38">
+        <v>0.7645919778699861</v>
+      </c>
+      <c r="AJ38">
+        <v>0.6472533062054934</v>
+      </c>
+      <c r="AK38">
+        <v>0.7494110718492344</v>
+      </c>
+      <c r="AL38">
+        <v>17.2</v>
+      </c>
+      <c r="AM38">
+        <v>17.2</v>
+      </c>
+      <c r="AN38">
+        <v>-5.137546468401487</v>
+      </c>
+      <c r="AO38">
+        <v>-3.145348837209303</v>
+      </c>
+      <c r="AP38">
+        <v>-4.730483271375465</v>
+      </c>
+      <c r="AQ38">
+        <v>-3.145348837209303</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Oriental Payment Group Holdings Limited (SEHK:8613)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D39">
+        <v>-0.339</v>
+      </c>
+      <c r="G39">
+        <v>-1.954314720812183</v>
+      </c>
+      <c r="H39">
+        <v>-1.954314720812183</v>
+      </c>
+      <c r="I39">
+        <v>-2.406091370558376</v>
+      </c>
+      <c r="J39">
+        <v>-2.406091370558376</v>
+      </c>
+      <c r="K39">
+        <v>-3.88</v>
+      </c>
+      <c r="L39">
+        <v>-1.969543147208122</v>
+      </c>
+      <c r="M39">
+        <v>-0</v>
+      </c>
+      <c r="N39">
+        <v>-0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>-0</v>
+      </c>
+      <c r="Q39">
+        <v>-0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0.882</v>
+      </c>
+      <c r="V39">
+        <v>0.04366336633663367</v>
+      </c>
+      <c r="W39">
+        <v>-10.02583979328165</v>
+      </c>
+      <c r="X39">
+        <v>0.05729816084857497</v>
+      </c>
+      <c r="Y39">
+        <v>-10.08313795413023</v>
+      </c>
+      <c r="Z39">
+        <v>0.5682145947505046</v>
+      </c>
+      <c r="AA39">
+        <v>-1.367176233054514</v>
+      </c>
+      <c r="AB39">
+        <v>0.0572302326966431</v>
+      </c>
+      <c r="AC39">
+        <v>-1.424406465751157</v>
+      </c>
+      <c r="AD39">
+        <v>2.86</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>2.86</v>
+      </c>
+      <c r="AG39">
+        <v>1.978</v>
+      </c>
+      <c r="AH39">
+        <v>0.1240242844752819</v>
+      </c>
+      <c r="AI39">
+        <v>0.3588456712672521</v>
+      </c>
+      <c r="AJ39">
+        <v>0.08918748309135179</v>
+      </c>
+      <c r="AK39">
+        <v>0.2790632054176072</v>
+      </c>
+      <c r="AL39">
+        <v>0.624</v>
+      </c>
+      <c r="AM39">
+        <v>0.514</v>
+      </c>
+      <c r="AN39">
+        <v>-0.7586206896551724</v>
+      </c>
+      <c r="AO39">
+        <v>-7.596153846153847</v>
+      </c>
+      <c r="AP39">
+        <v>-0.5246684350132625</v>
+      </c>
+      <c r="AQ39">
+        <v>-9.221789883268483</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/thailand/thailand_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,109 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.132</v>
+        <v>-0.0193</v>
       </c>
       <c r="E2">
-        <v>0.0668</v>
+        <v>-0.0838</v>
+      </c>
+      <c r="F2">
+        <v>0.0732</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.01668553134947667</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.01668553134947667</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.02015489053717213</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01726311327627811</v>
       </c>
       <c r="K2">
-        <v>175.5</v>
+        <v>772.5169999999999</v>
       </c>
       <c r="L2">
-        <v>0.3022214568624074</v>
+        <v>0.2000909130938166</v>
       </c>
       <c r="M2">
-        <v>13.8</v>
+        <v>326.53</v>
       </c>
       <c r="N2">
-        <v>0.004654614139233675</v>
+        <v>0.02272496342765356</v>
       </c>
       <c r="O2">
-        <v>0.07863247863247863</v>
+        <v>0.4226832548668832</v>
       </c>
       <c r="P2">
-        <v>13.8</v>
+        <v>318</v>
       </c>
       <c r="Q2">
-        <v>0.004654614139233675</v>
+        <v>0.02213131525432222</v>
       </c>
       <c r="R2">
-        <v>0.07863247863247863</v>
+        <v>0.4116414266611609</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>8.530000000000001</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.02612317398095122</v>
       </c>
       <c r="U2">
-        <v>248.6</v>
+        <v>981.681</v>
       </c>
       <c r="V2">
-        <v>0.08385051268213707</v>
+        <v>0.06832041412005752</v>
       </c>
       <c r="W2">
-        <v>0.2094022193055721</v>
+        <v>0.03877790834312574</v>
       </c>
       <c r="X2">
-        <v>0.07843697142345817</v>
+        <v>0.08647062676564476</v>
       </c>
       <c r="Y2">
-        <v>0.1309652478821139</v>
+        <v>-0.04769271842251903</v>
       </c>
       <c r="Z2">
-        <v>0.1511767156097053</v>
+        <v>0.1473030378742715</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07183430967375638</v>
+        <v>0.06680736669660246</v>
       </c>
       <c r="AC2">
-        <v>-0.07183430967375638</v>
+        <v>-0.06665064965181507</v>
       </c>
       <c r="AD2">
-        <v>4104.3</v>
+        <v>21310.25</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>2.516969836848626</v>
       </c>
       <c r="AF2">
-        <v>4104.3</v>
+        <v>21312.76696983685</v>
       </c>
       <c r="AG2">
-        <v>3855.7</v>
+        <v>20331.08596983685</v>
       </c>
       <c r="AH2">
-        <v>0.580597247174322</v>
+        <v>0.5973050156108268</v>
       </c>
       <c r="AI2">
-        <v>0.7881819753039003</v>
+        <v>0.6784943122531107</v>
       </c>
       <c r="AJ2">
-        <v>0.5653104611098894</v>
+        <v>0.585912521607715</v>
       </c>
       <c r="AK2">
-        <v>0.7775626676346622</v>
+        <v>0.6681225018832302</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>72.32000000000001</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>67.54400000000001</v>
+      </c>
+      <c r="AN2">
+        <v>188.3229643507308</v>
+      </c>
+      <c r="AO2">
+        <v>1.054756637168142</v>
+      </c>
+      <c r="AP2">
+        <v>179.6698949242373</v>
+      </c>
+      <c r="AQ2">
+        <v>1.129337913064077</v>
       </c>
     </row>
     <row r="3">
@@ -701,118 +716,3823 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Forth Smart Service Public Company Limited (SET:FSMART)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>-0.06419999999999999</v>
+      </c>
+      <c r="E3">
+        <v>-0.0774</v>
+      </c>
+      <c r="G3">
+        <v>0.2672292545710268</v>
+      </c>
+      <c r="H3">
+        <v>0.2672292545710268</v>
+      </c>
+      <c r="I3">
+        <v>0.1617440225035162</v>
+      </c>
+      <c r="J3">
+        <v>0.1314716615349527</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
+        <v>0.1687763713080169</v>
+      </c>
+      <c r="M3">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="N3">
+        <v>0.05407701019252549</v>
+      </c>
+      <c r="O3">
+        <v>0.7958333333333334</v>
+      </c>
+      <c r="P3">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="Q3">
+        <v>0.05407701019252549</v>
+      </c>
+      <c r="R3">
+        <v>0.7958333333333334</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>7.54</v>
+      </c>
+      <c r="V3">
+        <v>0.04269535673839184</v>
+      </c>
+      <c r="W3">
+        <v>0.4013377926421405</v>
+      </c>
+      <c r="X3">
+        <v>0.06304247208525612</v>
+      </c>
+      <c r="Y3">
+        <v>0.3382953205568844</v>
+      </c>
+      <c r="Z3">
+        <v>2.142211509490811</v>
+      </c>
+      <c r="AA3">
+        <v>0.2816401065120559</v>
+      </c>
+      <c r="AB3">
+        <v>0.06227868420333527</v>
+      </c>
+      <c r="AC3">
+        <v>0.2193614223087206</v>
+      </c>
+      <c r="AD3">
+        <v>25.1</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>25.1</v>
+      </c>
+      <c r="AG3">
+        <v>17.56</v>
+      </c>
+      <c r="AH3">
+        <v>0.1244422409519088</v>
+      </c>
+      <c r="AI3">
+        <v>0.4087947882736157</v>
+      </c>
+      <c r="AJ3">
+        <v>0.09044087350638649</v>
+      </c>
+      <c r="AK3">
+        <v>0.3260304493130338</v>
+      </c>
+      <c r="AL3">
+        <v>0.446</v>
+      </c>
+      <c r="AM3">
+        <v>-2.274</v>
+      </c>
+      <c r="AN3">
+        <v>1.206730769230769</v>
+      </c>
+      <c r="AO3">
+        <v>25.7847533632287</v>
+      </c>
+      <c r="AP3">
+        <v>0.8442307692307693</v>
+      </c>
+      <c r="AQ3">
+        <v>-5.05716798592788</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>IFS Capital (Thailand) Public Company Limited (SET:IFS)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.00872</v>
+      </c>
+      <c r="E4">
+        <v>-0.0902</v>
+      </c>
+      <c r="G4">
+        <v>0.5573529411764706</v>
+      </c>
+      <c r="H4">
+        <v>0.5573529411764706</v>
+      </c>
+      <c r="I4">
+        <v>0.5801470588235293</v>
+      </c>
+      <c r="J4">
+        <v>0.4621510468594217</v>
+      </c>
+      <c r="K4">
+        <v>4.23</v>
+      </c>
+      <c r="L4">
+        <v>0.3110294117647059</v>
+      </c>
+      <c r="M4">
+        <v>2.56</v>
+      </c>
+      <c r="N4">
+        <v>0.07071823204419889</v>
+      </c>
+      <c r="O4">
+        <v>0.6052009456264775</v>
+      </c>
+      <c r="P4">
+        <v>2.56</v>
+      </c>
+      <c r="Q4">
+        <v>0.07071823204419889</v>
+      </c>
+      <c r="R4">
+        <v>0.6052009456264775</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>17.6</v>
+      </c>
+      <c r="V4">
+        <v>0.4861878453038674</v>
+      </c>
+      <c r="W4">
+        <v>0.08942917547568711</v>
+      </c>
+      <c r="X4">
+        <v>0.08109235832183642</v>
+      </c>
+      <c r="Y4">
+        <v>0.008336817153850692</v>
+      </c>
+      <c r="Z4">
+        <v>0.162874251497006</v>
+      </c>
+      <c r="AA4">
+        <v>0.07527250583578605</v>
+      </c>
+      <c r="AB4">
+        <v>0.06448682530719119</v>
+      </c>
+      <c r="AC4">
+        <v>0.01078568052859487</v>
+      </c>
+      <c r="AD4">
+        <v>57.9</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>57.9</v>
+      </c>
+      <c r="AG4">
+        <v>40.3</v>
+      </c>
+      <c r="AH4">
+        <v>0.6153028692879915</v>
+      </c>
+      <c r="AI4">
+        <v>0.5119363395225465</v>
+      </c>
+      <c r="AJ4">
+        <v>0.526797385620915</v>
+      </c>
+      <c r="AK4">
+        <v>0.4219895287958115</v>
+      </c>
+      <c r="AL4">
+        <v>1.72</v>
+      </c>
+      <c r="AM4">
+        <v>1.72</v>
+      </c>
+      <c r="AN4">
+        <v>7.086903304773561</v>
+      </c>
+      <c r="AO4">
+        <v>4.587209302325581</v>
+      </c>
+      <c r="AP4">
+        <v>4.932680538555691</v>
+      </c>
+      <c r="AQ4">
+        <v>4.587209302325581</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Knight Club Capital Holding Public Company Limited (SET:KCC)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>0.6797385620915033</v>
+      </c>
+      <c r="H5">
+        <v>0.6797385620915033</v>
+      </c>
+      <c r="I5">
+        <v>0.7241830065359477</v>
+      </c>
+      <c r="J5">
+        <v>0.5738335934142976</v>
+      </c>
+      <c r="K5">
+        <v>2.29</v>
+      </c>
+      <c r="L5">
+        <v>0.2993464052287582</v>
+      </c>
+      <c r="M5">
+        <v>1.04</v>
+      </c>
+      <c r="N5">
+        <v>0.02803234501347709</v>
+      </c>
+      <c r="O5">
+        <v>0.4541484716157205</v>
+      </c>
+      <c r="P5">
+        <v>1.04</v>
+      </c>
+      <c r="Q5">
+        <v>0.02803234501347709</v>
+      </c>
+      <c r="R5">
+        <v>0.4541484716157205</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.018</v>
+      </c>
+      <c r="V5">
+        <v>0.0004851752021563342</v>
+      </c>
+      <c r="W5">
+        <v>0.07269841269841269</v>
+      </c>
+      <c r="X5">
+        <v>0.07663901938512671</v>
+      </c>
+      <c r="Y5">
+        <v>-0.003940606686714018</v>
+      </c>
+      <c r="Z5">
+        <v>0.127287853577371</v>
+      </c>
+      <c r="AA5">
+        <v>0.0730420464162958</v>
+      </c>
+      <c r="AB5">
+        <v>0.06682223346576269</v>
+      </c>
+      <c r="AC5">
+        <v>0.006219812950533116</v>
+      </c>
+      <c r="AD5">
+        <v>46</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>46</v>
+      </c>
+      <c r="AG5">
+        <v>45.982</v>
+      </c>
+      <c r="AH5">
+        <v>0.5535499398315283</v>
+      </c>
+      <c r="AI5">
+        <v>0.5569007263922519</v>
+      </c>
+      <c r="AJ5">
+        <v>0.5534532148961268</v>
+      </c>
+      <c r="AK5">
+        <v>0.5568041461819767</v>
+      </c>
+      <c r="AL5">
+        <v>2.65</v>
+      </c>
+      <c r="AM5">
+        <v>2.65</v>
+      </c>
+      <c r="AN5">
+        <v>8.243727598566307</v>
+      </c>
+      <c r="AO5">
+        <v>2.090566037735849</v>
+      </c>
+      <c r="AP5">
+        <v>8.240501792114696</v>
+      </c>
+      <c r="AQ5">
+        <v>2.090566037735849</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>JMT Network Services Public Company Limited (SET:JMT)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.174</v>
+      </c>
+      <c r="E6">
+        <v>0.234</v>
+      </c>
+      <c r="F6">
+        <v>0.0732</v>
+      </c>
+      <c r="G6">
+        <v>0.4231936854887675</v>
+      </c>
+      <c r="H6">
+        <v>0.4231936854887675</v>
+      </c>
+      <c r="I6">
+        <v>0.3982999392835458</v>
+      </c>
+      <c r="J6">
+        <v>0.3343305550955824</v>
+      </c>
+      <c r="K6">
+        <v>54.3</v>
+      </c>
+      <c r="L6">
+        <v>0.3296903460837887</v>
+      </c>
+      <c r="M6">
+        <v>39.6</v>
+      </c>
+      <c r="N6">
+        <v>0.05116279069767442</v>
+      </c>
+      <c r="O6">
+        <v>0.7292817679558011</v>
+      </c>
+      <c r="P6">
+        <v>39.6</v>
+      </c>
+      <c r="Q6">
+        <v>0.05116279069767442</v>
+      </c>
+      <c r="R6">
+        <v>0.7292817679558011</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>19.4</v>
+      </c>
+      <c r="V6">
+        <v>0.02506459948320413</v>
+      </c>
+      <c r="W6">
+        <v>0.07631763879128602</v>
+      </c>
+      <c r="X6">
+        <v>0.06659962907373011</v>
+      </c>
+      <c r="Y6">
+        <v>0.009718009717555903</v>
+      </c>
+      <c r="Z6">
+        <v>0.168110971614049</v>
+      </c>
+      <c r="AA6">
+        <v>0.05620463445738271</v>
+      </c>
+      <c r="AB6">
+        <v>0.06368758205964201</v>
+      </c>
+      <c r="AC6">
+        <v>-0.007482947602259295</v>
+      </c>
+      <c r="AD6">
+        <v>332.3</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>332.3</v>
+      </c>
+      <c r="AG6">
+        <v>312.9</v>
+      </c>
+      <c r="AH6">
+        <v>0.3003706047184308</v>
+      </c>
+      <c r="AI6">
+        <v>0.2827844438771169</v>
+      </c>
+      <c r="AJ6">
+        <v>0.2878829699144356</v>
+      </c>
+      <c r="AK6">
+        <v>0.2707450030284676</v>
+      </c>
+      <c r="AL6">
+        <v>16.1</v>
+      </c>
+      <c r="AM6">
+        <v>16.1</v>
+      </c>
+      <c r="AN6">
+        <v>4.879588839941263</v>
+      </c>
+      <c r="AO6">
+        <v>4.074534161490683</v>
+      </c>
+      <c r="AP6">
+        <v>4.594713656387666</v>
+      </c>
+      <c r="AQ6">
+        <v>4.074534161490683</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SG Capital Public Company Limited (SET:SGC)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>-1.154804270462634</v>
+      </c>
+      <c r="H7">
+        <v>-1.154804270462634</v>
+      </c>
+      <c r="I7">
+        <v>0.395017793594306</v>
+      </c>
+      <c r="J7">
+        <v>0.3003591518113387</v>
+      </c>
+      <c r="K7">
+        <v>3.3</v>
+      </c>
+      <c r="L7">
+        <v>0.0587188612099644</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>-0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>-0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>43.7</v>
+      </c>
+      <c r="V7">
+        <v>0.2020342117429496</v>
+      </c>
+      <c r="W7">
+        <v>0.03877790834312574</v>
+      </c>
+      <c r="X7">
+        <v>0.07366206429357806</v>
+      </c>
+      <c r="Y7">
+        <v>-0.03488415595045233</v>
+      </c>
+      <c r="Z7">
+        <v>0.1654888103651355</v>
+      </c>
+      <c r="AA7">
+        <v>0.04970607871553955</v>
+      </c>
+      <c r="AB7">
+        <v>0.06528536051153602</v>
+      </c>
+      <c r="AC7">
+        <v>-0.01557928179599648</v>
+      </c>
+      <c r="AD7">
+        <v>216.2</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>216.2</v>
+      </c>
+      <c r="AG7">
+        <v>172.5</v>
+      </c>
+      <c r="AH7">
+        <v>0.4998843930635838</v>
+      </c>
+      <c r="AI7">
+        <v>0.4966689639329199</v>
+      </c>
+      <c r="AJ7">
+        <v>0.4436728395061728</v>
+      </c>
+      <c r="AK7">
+        <v>0.4405005107252298</v>
+      </c>
+      <c r="AL7">
+        <v>17.8</v>
+      </c>
+      <c r="AM7">
+        <v>17.8</v>
+      </c>
+      <c r="AN7">
+        <v>9.608888888888888</v>
+      </c>
+      <c r="AO7">
+        <v>1.247191011235955</v>
+      </c>
+      <c r="AP7">
+        <v>7.666666666666667</v>
+      </c>
+      <c r="AQ7">
+        <v>1.247191011235955</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Chase Asia Public Company Limited (SET:CHASE)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G8">
+        <v>0.2385245901639345</v>
+      </c>
+      <c r="H8">
+        <v>0.2385245901639345</v>
+      </c>
+      <c r="I8">
+        <v>0.2055822723315577</v>
+      </c>
+      <c r="J8">
+        <v>0.1640231766090298</v>
+      </c>
+      <c r="K8">
+        <v>3.33</v>
+      </c>
+      <c r="L8">
+        <v>0.1364754098360656</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>-0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>-0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>2.93</v>
+      </c>
+      <c r="V8">
+        <v>0.05167548500881834</v>
+      </c>
+      <c r="W8">
+        <v>0.03635371179039302</v>
+      </c>
+      <c r="X8">
+        <v>0.06585497108691676</v>
+      </c>
+      <c r="Y8">
+        <v>-0.02950125929652374</v>
+      </c>
+      <c r="Z8">
+        <v>0.2547399302864132</v>
+      </c>
+      <c r="AA8">
+        <v>0.0417832525747403</v>
+      </c>
+      <c r="AB8">
+        <v>0.06344155672529381</v>
+      </c>
+      <c r="AC8">
+        <v>-0.0216583041505535</v>
+      </c>
+      <c r="AD8">
+        <v>20.9</v>
+      </c>
+      <c r="AE8">
+        <v>0.0339627755499721</v>
+      </c>
+      <c r="AF8">
+        <v>20.93396277554997</v>
+      </c>
+      <c r="AG8">
+        <v>18.00396277554997</v>
+      </c>
+      <c r="AH8">
+        <v>0.2696495454711338</v>
+      </c>
+      <c r="AI8">
+        <v>0.1637590067696304</v>
+      </c>
+      <c r="AJ8">
+        <v>0.2410041195490975</v>
+      </c>
+      <c r="AK8">
+        <v>0.1441424465283199</v>
+      </c>
+      <c r="AL8">
+        <v>0.878</v>
+      </c>
+      <c r="AM8">
+        <v>0.878</v>
+      </c>
+      <c r="AN8">
+        <v>3.435804701627486</v>
+      </c>
+      <c r="AO8">
+        <v>5.683371298405468</v>
+      </c>
+      <c r="AP8">
+        <v>2.959717701060327</v>
+      </c>
+      <c r="AQ8">
+        <v>5.683371298405468</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AIRA Factoring Public Company Limited (SET:AF)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0226</v>
+      </c>
+      <c r="E9">
+        <v>-0.275</v>
+      </c>
+      <c r="G9">
+        <v>0.270543615676359</v>
+      </c>
+      <c r="H9">
+        <v>0.270543615676359</v>
+      </c>
+      <c r="I9">
+        <v>0.3624773126108027</v>
+      </c>
+      <c r="J9">
+        <v>0.2715906708057342</v>
+      </c>
+      <c r="K9">
+        <v>0.254</v>
+      </c>
+      <c r="L9">
+        <v>0.03211125158027813</v>
+      </c>
+      <c r="M9">
+        <v>1.6</v>
+      </c>
+      <c r="N9">
+        <v>0.049079754601227</v>
+      </c>
+      <c r="O9">
+        <v>6.299212598425197</v>
+      </c>
+      <c r="P9">
+        <v>1.6</v>
+      </c>
+      <c r="Q9">
+        <v>0.049079754601227</v>
+      </c>
+      <c r="R9">
+        <v>6.299212598425197</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>3.99</v>
+      </c>
+      <c r="V9">
+        <v>0.1223926380368098</v>
+      </c>
+      <c r="W9">
+        <v>0.01716216216216216</v>
+      </c>
+      <c r="X9">
+        <v>0.08254066024698661</v>
+      </c>
+      <c r="Y9">
+        <v>-0.06537849808482446</v>
+      </c>
+      <c r="Z9">
+        <v>0.1525730383404103</v>
+      </c>
+      <c r="AA9">
+        <v>0.04143741382974103</v>
+      </c>
+      <c r="AB9">
+        <v>0.06760602021481563</v>
+      </c>
+      <c r="AC9">
+        <v>-0.02616860638507459</v>
+      </c>
+      <c r="AD9">
+        <v>55.9</v>
+      </c>
+      <c r="AE9">
+        <v>0.05402228624275061</v>
+      </c>
+      <c r="AF9">
+        <v>55.95402228624275</v>
+      </c>
+      <c r="AG9">
+        <v>51.96402228624274</v>
+      </c>
+      <c r="AH9">
+        <v>0.6318631366667514</v>
+      </c>
+      <c r="AI9">
+        <v>0.7787180244877643</v>
+      </c>
+      <c r="AJ9">
+        <v>0.6144932665377305</v>
+      </c>
+      <c r="AK9">
+        <v>0.7657079633014441</v>
+      </c>
+      <c r="AL9">
+        <v>2.48</v>
+      </c>
+      <c r="AM9">
+        <v>2.479</v>
+      </c>
+      <c r="AN9">
+        <v>19.35595567867036</v>
+      </c>
+      <c r="AO9">
+        <v>1.137096774193548</v>
+      </c>
+      <c r="AP9">
+        <v>17.99308250908683</v>
+      </c>
+      <c r="AQ9">
+        <v>1.137555465913675</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mida Assets Public Company Limited (SET:MIDA)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>-0.0475</v>
+      </c>
+      <c r="G10">
+        <v>0.2280966767371601</v>
+      </c>
+      <c r="H10">
+        <v>0.2280966767371601</v>
+      </c>
+      <c r="I10">
+        <v>0.03489425981873111</v>
+      </c>
+      <c r="J10">
+        <v>0.03489425981873111</v>
+      </c>
+      <c r="K10">
+        <v>-5.85</v>
+      </c>
+      <c r="L10">
+        <v>-0.08836858006042295</v>
+      </c>
+      <c r="M10">
+        <v>-0</v>
+      </c>
+      <c r="N10">
+        <v>-0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>3.83</v>
+      </c>
+      <c r="V10">
+        <v>0.1748858447488585</v>
+      </c>
+      <c r="W10">
+        <v>-0.05797819623389494</v>
+      </c>
+      <c r="X10">
+        <v>0.154089907197341</v>
+      </c>
+      <c r="Y10">
+        <v>-0.212068103431236</v>
+      </c>
+      <c r="Z10">
+        <v>0.2983325822442541</v>
+      </c>
+      <c r="AA10">
+        <v>0.01041009463722397</v>
+      </c>
+      <c r="AB10">
+        <v>0.06834754692925649</v>
+      </c>
+      <c r="AC10">
+        <v>-0.05793745229203251</v>
+      </c>
+      <c r="AD10">
+        <v>164.1</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>164.1</v>
+      </c>
+      <c r="AG10">
+        <v>160.27</v>
+      </c>
+      <c r="AH10">
+        <v>0.882258064516129</v>
+      </c>
+      <c r="AI10">
+        <v>0.5236119974473517</v>
+      </c>
+      <c r="AJ10">
+        <v>0.8797826206290826</v>
+      </c>
+      <c r="AK10">
+        <v>0.517718125141325</v>
+      </c>
+      <c r="AL10">
+        <v>10</v>
+      </c>
+      <c r="AM10">
+        <v>8.33</v>
+      </c>
+      <c r="AN10">
+        <v>37.21088435374149</v>
+      </c>
+      <c r="AO10">
+        <v>0.231</v>
+      </c>
+      <c r="AP10">
+        <v>36.34240362811791</v>
+      </c>
+      <c r="AQ10">
+        <v>0.2773109243697479</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Thitikorn Public Company Limited (SET:TK)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>-0.194</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0.01354622311910052</v>
+      </c>
+      <c r="J11">
+        <v>0.01354622311910052</v>
+      </c>
+      <c r="K11">
+        <v>-1.02</v>
+      </c>
+      <c r="L11">
+        <v>-0.05543478260869566</v>
+      </c>
+      <c r="M11">
+        <v>3.87</v>
+      </c>
+      <c r="N11">
+        <v>0.05724852071005918</v>
+      </c>
+      <c r="O11">
+        <v>-3.794117647058823</v>
+      </c>
+      <c r="P11">
+        <v>3.87</v>
+      </c>
+      <c r="Q11">
+        <v>0.05724852071005918</v>
+      </c>
+      <c r="R11">
+        <v>-3.794117647058823</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>48.3</v>
+      </c>
+      <c r="V11">
+        <v>0.7144970414201184</v>
+      </c>
+      <c r="W11">
+        <v>-0.0066147859922179</v>
+      </c>
+      <c r="X11">
+        <v>0.06305727993220506</v>
+      </c>
+      <c r="Y11">
+        <v>-0.06967206592442296</v>
+      </c>
+      <c r="Z11">
+        <v>0.1419438231000914</v>
+      </c>
+      <c r="AA11">
+        <v>0.001922802698091972</v>
+      </c>
+      <c r="AB11">
+        <v>0.0619350144991847</v>
+      </c>
+      <c r="AC11">
+        <v>-0.06001221180109273</v>
+      </c>
+      <c r="AD11">
+        <v>9.06</v>
+      </c>
+      <c r="AE11">
+        <v>0.6287474730427527</v>
+      </c>
+      <c r="AF11">
+        <v>9.688747473042753</v>
+      </c>
+      <c r="AG11">
+        <v>-38.61125252695724</v>
+      </c>
+      <c r="AH11">
+        <v>0.1253578016181729</v>
+      </c>
+      <c r="AI11">
+        <v>0.05511585702906567</v>
+      </c>
+      <c r="AJ11">
+        <v>-1.331939317587373</v>
+      </c>
+      <c r="AK11">
+        <v>-0.3028600821034932</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>-0.351</v>
+      </c>
+      <c r="AN11">
+        <v>24.16</v>
+      </c>
+      <c r="AP11">
+        <v>-102.963340071886</v>
+      </c>
+      <c r="AQ11">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Krungthai Card Public Company Limited (SET:KTC)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.05139999999999999</v>
+      </c>
+      <c r="E12">
+        <v>0.0611</v>
+      </c>
+      <c r="F12">
+        <v>0.0658</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>226</v>
+      </c>
+      <c r="L12">
+        <v>0.395727543337419</v>
+      </c>
+      <c r="M12">
+        <v>101.3</v>
+      </c>
+      <c r="N12">
+        <v>0.02697018104366347</v>
+      </c>
+      <c r="O12">
+        <v>0.4482300884955752</v>
+      </c>
+      <c r="P12">
+        <v>101.3</v>
+      </c>
+      <c r="Q12">
+        <v>0.02697018104366347</v>
+      </c>
+      <c r="R12">
+        <v>0.4482300884955752</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>70.8</v>
+      </c>
+      <c r="V12">
+        <v>0.01884984025559105</v>
+      </c>
+      <c r="W12">
+        <v>0.243586979952576</v>
+      </c>
+      <c r="X12">
+        <v>0.06745351390547144</v>
+      </c>
+      <c r="Y12">
+        <v>0.1761334660471046</v>
+      </c>
+      <c r="Z12">
+        <v>0.2212108300732075</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.06301421557376102</v>
+      </c>
+      <c r="AC12">
+        <v>-0.06301421557376102</v>
+      </c>
+      <c r="AD12">
+        <v>1871.5</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>1871.5</v>
+      </c>
+      <c r="AG12">
+        <v>1800.7</v>
+      </c>
+      <c r="AH12">
+        <v>0.3325633051976899</v>
+      </c>
+      <c r="AI12">
+        <v>0.6139890423542534</v>
+      </c>
+      <c r="AJ12">
+        <v>0.3240592437957781</v>
+      </c>
+      <c r="AK12">
+        <v>0.6048097269337991</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Saksiam Leasing Public Company Limited (SET:SAK)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.135</v>
+      </c>
+      <c r="E13">
+        <v>0.165</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>25.3</v>
+      </c>
+      <c r="L13">
+        <v>0.3324572930354797</v>
+      </c>
+      <c r="M13">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="N13">
+        <v>0.03288227334235453</v>
+      </c>
+      <c r="O13">
+        <v>0.3841897233201581</v>
+      </c>
+      <c r="P13">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="Q13">
+        <v>0.03288227334235453</v>
+      </c>
+      <c r="R13">
+        <v>0.3841897233201581</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>8.94</v>
+      </c>
+      <c r="V13">
+        <v>0.03024357239512855</v>
+      </c>
+      <c r="W13">
+        <v>0.1646063760572544</v>
+      </c>
+      <c r="X13">
+        <v>0.07257419651180821</v>
+      </c>
+      <c r="Y13">
+        <v>0.09203217954544621</v>
+      </c>
+      <c r="Z13">
+        <v>0.223429242513212</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.06510134718705264</v>
+      </c>
+      <c r="AC13">
+        <v>-0.06510134718705264</v>
+      </c>
+      <c r="AD13">
+        <v>269.5</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>269.5</v>
+      </c>
+      <c r="AG13">
+        <v>260.56</v>
+      </c>
+      <c r="AH13">
+        <v>0.4769067421695275</v>
+      </c>
+      <c r="AI13">
+        <v>0.5872739158858139</v>
+      </c>
+      <c r="AJ13">
+        <v>0.4684982738780206</v>
+      </c>
+      <c r="AK13">
+        <v>0.5790736954395946</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ratchthani Leasing Public Company Limited (SET:THANI)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>-0.0886</v>
+      </c>
+      <c r="E14">
+        <v>-0.154</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>25.9</v>
+      </c>
+      <c r="L14">
+        <v>0.4473229706390328</v>
+      </c>
+      <c r="M14">
+        <v>3.5</v>
+      </c>
+      <c r="N14">
+        <v>0.01205234159779614</v>
+      </c>
+      <c r="O14">
+        <v>0.1351351351351351</v>
+      </c>
+      <c r="P14">
+        <v>3.5</v>
+      </c>
+      <c r="Q14">
+        <v>0.01205234159779614</v>
+      </c>
+      <c r="R14">
+        <v>0.1351351351351351</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>45</v>
+      </c>
+      <c r="V14">
+        <v>0.1549586776859504</v>
+      </c>
+      <c r="W14">
+        <v>0.07562043795620438</v>
+      </c>
+      <c r="X14">
+        <v>0.1096007770736134</v>
+      </c>
+      <c r="Y14">
+        <v>-0.033980339117409</v>
+      </c>
+      <c r="Z14">
+        <v>0.03920639219934995</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.06542778994712643</v>
+      </c>
+      <c r="AC14">
+        <v>-0.06542778994712643</v>
+      </c>
+      <c r="AD14">
+        <v>1132.9</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>1132.9</v>
+      </c>
+      <c r="AG14">
+        <v>1087.9</v>
+      </c>
+      <c r="AH14">
+        <v>0.7959671186678845</v>
+      </c>
+      <c r="AI14">
+        <v>0.7344094386101387</v>
+      </c>
+      <c r="AJ14">
+        <v>0.7893056664006385</v>
+      </c>
+      <c r="AK14">
+        <v>0.7264289529914529</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Srisawad Corporation Public Company Limited (SET:SAWAD)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.153</v>
+      </c>
+      <c r="E15">
+        <v>0.07829999999999999</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>157.5</v>
+      </c>
+      <c r="L15">
+        <v>0.3181818181818182</v>
+      </c>
+      <c r="M15">
+        <v>0.489</v>
+      </c>
+      <c r="N15">
+        <v>0.0002661514178413977</v>
+      </c>
+      <c r="O15">
+        <v>0.003104761904761905</v>
+      </c>
+      <c r="P15">
+        <v>0.489</v>
+      </c>
+      <c r="Q15">
+        <v>0.0002661514178413977</v>
+      </c>
+      <c r="R15">
+        <v>0.003104761904761905</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>110</v>
+      </c>
+      <c r="V15">
+        <v>0.05987046209111196</v>
+      </c>
+      <c r="W15">
+        <v>0.2137042062415197</v>
+      </c>
+      <c r="X15">
+        <v>0.07620654233852957</v>
+      </c>
+      <c r="Y15">
+        <v>0.1374976639029901</v>
+      </c>
+      <c r="Z15">
+        <v>0.187642153146323</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0.06565851539811415</v>
+      </c>
+      <c r="AC15">
+        <v>-0.06565851539811415</v>
+      </c>
+      <c r="AD15">
+        <v>2213.9</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>2213.9</v>
+      </c>
+      <c r="AG15">
+        <v>2103.9</v>
+      </c>
+      <c r="AH15">
+        <v>0.5464800552922592</v>
+      </c>
+      <c r="AI15">
+        <v>0.6718152576318505</v>
+      </c>
+      <c r="AJ15">
+        <v>0.5338221861362022</v>
+      </c>
+      <c r="AK15">
+        <v>0.6604822000376719</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Lease IT Public Company Limited (SET:LIT)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="K16">
+        <v>-15</v>
+      </c>
+      <c r="M16">
+        <v>-0</v>
+      </c>
+      <c r="N16">
+        <v>-0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>-0</v>
+      </c>
+      <c r="Q16">
+        <v>-0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>2.66</v>
+      </c>
+      <c r="V16">
+        <v>0.298876404494382</v>
+      </c>
+      <c r="W16">
+        <v>-0.5357142857142857</v>
+      </c>
+      <c r="X16">
+        <v>0.07645109037432318</v>
+      </c>
+      <c r="Y16">
+        <v>-0.6121653760886089</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.06569074901301022</v>
+      </c>
+      <c r="AC16">
+        <v>-0.06569074901301022</v>
+      </c>
+      <c r="AD16">
+        <v>10.9</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>10.9</v>
+      </c>
+      <c r="AG16">
+        <v>8.24</v>
+      </c>
+      <c r="AH16">
+        <v>0.5505050505050505</v>
+      </c>
+      <c r="AI16">
+        <v>0.394927536231884</v>
+      </c>
+      <c r="AJ16">
+        <v>0.4807467911318553</v>
+      </c>
+      <c r="AK16">
+        <v>0.3303929430633521</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ngern Tid Lor Public Company Limited (SET:TIDLOR)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>126.4</v>
+      </c>
+      <c r="L17">
+        <v>0.2113358970071894</v>
+      </c>
+      <c r="M17">
+        <v>24.54</v>
+      </c>
+      <c r="N17">
+        <v>0.017006237006237</v>
+      </c>
+      <c r="O17">
+        <v>0.1941455696202531</v>
+      </c>
+      <c r="P17">
+        <v>23.4</v>
+      </c>
+      <c r="Q17">
+        <v>0.01621621621621621</v>
+      </c>
+      <c r="R17">
+        <v>0.185126582278481</v>
+      </c>
+      <c r="S17">
+        <v>1.140000000000001</v>
+      </c>
+      <c r="T17">
+        <v>0.0464547677261614</v>
+      </c>
+      <c r="U17">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="V17">
+        <v>0.06784476784476785</v>
+      </c>
+      <c r="W17">
+        <v>0.1676614935667861</v>
+      </c>
+      <c r="X17">
+        <v>0.08073784481491716</v>
+      </c>
+      <c r="Y17">
+        <v>0.08692364875186889</v>
+      </c>
+      <c r="Z17">
+        <v>0.2414068680475952</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0.06617537264766774</v>
+      </c>
+      <c r="AC17">
+        <v>-0.06617537264766774</v>
+      </c>
+      <c r="AD17">
+        <v>2266.7</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>2266.7</v>
+      </c>
+      <c r="AG17">
+        <v>2168.8</v>
+      </c>
+      <c r="AH17">
+        <v>0.6110197590101625</v>
+      </c>
+      <c r="AI17">
+        <v>0.7040315567151199</v>
+      </c>
+      <c r="AJ17">
+        <v>0.6004762168447865</v>
+      </c>
+      <c r="AK17">
+        <v>0.6947496556363519</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AEON Thana Sinsap (Thailand) Public Company Limited (SET:AEONTS)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>-0.0193</v>
+      </c>
+      <c r="E18">
+        <v>-0.0291</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>92.5</v>
+      </c>
+      <c r="L18">
+        <v>0.2577319587628866</v>
+      </c>
+      <c r="M18">
+        <v>40.9</v>
+      </c>
+      <c r="N18">
+        <v>0.04386999892738389</v>
+      </c>
+      <c r="O18">
+        <v>0.4421621621621621</v>
+      </c>
+      <c r="P18">
+        <v>40.9</v>
+      </c>
+      <c r="Q18">
+        <v>0.04386999892738389</v>
+      </c>
+      <c r="R18">
+        <v>0.4421621621621621</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>132.8</v>
+      </c>
+      <c r="V18">
+        <v>0.1424434195001609</v>
+      </c>
+      <c r="W18">
+        <v>0.1369761587442618</v>
+      </c>
+      <c r="X18">
+        <v>0.08647062676564476</v>
+      </c>
+      <c r="Y18">
+        <v>0.05050553197861704</v>
+      </c>
+      <c r="Z18">
+        <v>0.1436864440707823</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0.06665064965181507</v>
+      </c>
+      <c r="AC18">
+        <v>-0.06665064965181507</v>
+      </c>
+      <c r="AD18">
+        <v>1896</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>1896</v>
+      </c>
+      <c r="AG18">
+        <v>1763.2</v>
+      </c>
+      <c r="AH18">
+        <v>0.6703673584838948</v>
+      </c>
+      <c r="AI18">
+        <v>0.7116849968094291</v>
+      </c>
+      <c r="AJ18">
+        <v>0.6541272491189019</v>
+      </c>
+      <c r="AK18">
+        <v>0.6965590803144629</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Heng Leasing and Capital Public Company Limited (SET:HENG)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>5.34</v>
+      </c>
+      <c r="L19">
+        <v>0.1026923076923077</v>
+      </c>
+      <c r="M19">
+        <v>7.83</v>
+      </c>
+      <c r="N19">
+        <v>0.06299275945293645</v>
+      </c>
+      <c r="O19">
+        <v>1.466292134831461</v>
+      </c>
+      <c r="P19">
+        <v>7.83</v>
+      </c>
+      <c r="Q19">
+        <v>0.06299275945293645</v>
+      </c>
+      <c r="R19">
+        <v>1.466292134831461</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>3.61</v>
+      </c>
+      <c r="V19">
+        <v>0.02904263877715205</v>
+      </c>
+      <c r="W19">
+        <v>0.03716075156576201</v>
+      </c>
+      <c r="X19">
+        <v>0.08773744992316021</v>
+      </c>
+      <c r="Y19">
+        <v>-0.0505766983573982</v>
+      </c>
+      <c r="Z19">
+        <v>0.1328292633084704</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.06673674885353548</v>
+      </c>
+      <c r="AC19">
+        <v>-0.06673674885353548</v>
+      </c>
+      <c r="AD19">
+        <v>265.5</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>265.5</v>
+      </c>
+      <c r="AG19">
+        <v>261.89</v>
+      </c>
+      <c r="AH19">
+        <v>0.6811185223191381</v>
+      </c>
+      <c r="AI19">
+        <v>0.6238251879699248</v>
+      </c>
+      <c r="AJ19">
+        <v>0.6781377042388461</v>
+      </c>
+      <c r="AK19">
+        <v>0.6206071233915496</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S 11 Group Public Company Limited (SET:S11)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>-0.208</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>-1.45</v>
+      </c>
+      <c r="L20">
+        <v>-0.1239316239316239</v>
+      </c>
+      <c r="M20">
+        <v>-0</v>
+      </c>
+      <c r="N20">
+        <v>-0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>-0</v>
+      </c>
+      <c r="Q20">
+        <v>-0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>1.86</v>
+      </c>
+      <c r="V20">
+        <v>0.04603960396039605</v>
+      </c>
+      <c r="W20">
+        <v>-0.01598676957001103</v>
+      </c>
+      <c r="X20">
+        <v>0.09034554403677586</v>
+      </c>
+      <c r="Y20">
+        <v>-0.1063323136067869</v>
+      </c>
+      <c r="Z20">
+        <v>0.05994466646172764</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0.06689743589435385</v>
+      </c>
+      <c r="AC20">
+        <v>-0.06689743589435385</v>
+      </c>
+      <c r="AD20">
+        <v>94.8</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>94.8</v>
+      </c>
+      <c r="AG20">
+        <v>92.94</v>
+      </c>
+      <c r="AH20">
+        <v>0.7011834319526628</v>
+      </c>
+      <c r="AI20">
+        <v>0.4839203675344564</v>
+      </c>
+      <c r="AJ20">
+        <v>0.6970151492425378</v>
+      </c>
+      <c r="AK20">
+        <v>0.4789734075448361</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Eastern Commercial Leasing Public Company Limited (SET:ECL)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>-0.0521</v>
+      </c>
+      <c r="E21">
+        <v>-0.147</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0.001386413190408154</v>
+      </c>
+      <c r="J21">
+        <v>0.001122054743084565</v>
+      </c>
+      <c r="K21">
+        <v>1.91</v>
+      </c>
+      <c r="L21">
+        <v>0.1503937007874016</v>
+      </c>
+      <c r="M21">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="N21">
+        <v>0.02234527687296417</v>
+      </c>
+      <c r="O21">
+        <v>0.3591623036649215</v>
+      </c>
+      <c r="P21">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="Q21">
+        <v>0.02234527687296417</v>
+      </c>
+      <c r="R21">
+        <v>0.3591623036649215</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0.707</v>
+      </c>
+      <c r="V21">
+        <v>0.02302931596091205</v>
+      </c>
+      <c r="W21">
+        <v>0.0373046875</v>
+      </c>
+      <c r="X21">
+        <v>0.1013164966087898</v>
+      </c>
+      <c r="Y21">
+        <v>-0.06401180910878981</v>
+      </c>
+      <c r="Z21">
+        <v>0.09645914228787411</v>
+      </c>
+      <c r="AA21">
+        <v>0.0001082324381179781</v>
+      </c>
+      <c r="AB21">
+        <v>0.06739827128992713</v>
+      </c>
+      <c r="AC21">
+        <v>-0.06729003885180916</v>
+      </c>
+      <c r="AD21">
+        <v>99.2</v>
+      </c>
+      <c r="AE21">
+        <v>0.03196276240908221</v>
+      </c>
+      <c r="AF21">
+        <v>99.23196276240908</v>
+      </c>
+      <c r="AG21">
+        <v>98.52496276240909</v>
+      </c>
+      <c r="AH21">
+        <v>0.7637224948557316</v>
+      </c>
+      <c r="AI21">
+        <v>0.6267336110227806</v>
+      </c>
+      <c r="AJ21">
+        <v>0.7624298019226786</v>
+      </c>
+      <c r="AK21">
+        <v>0.6250593880292775</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>4133.333333333333</v>
+      </c>
+      <c r="AP21">
+        <v>4105.206781767045</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Mida Leasing Public Company Limited (SET:ML)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>-0.1</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>-1.56</v>
+      </c>
+      <c r="L22">
+        <v>-0.2206506364922206</v>
+      </c>
+      <c r="M22">
+        <v>-0</v>
+      </c>
+      <c r="N22">
+        <v>-0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>-0</v>
+      </c>
+      <c r="Q22">
+        <v>-0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0.929</v>
+      </c>
+      <c r="V22">
+        <v>0.05993548387096775</v>
+      </c>
+      <c r="W22">
+        <v>-0.02666666666666667</v>
+      </c>
+      <c r="X22">
+        <v>0.09931814381780421</v>
+      </c>
+      <c r="Y22">
+        <v>-0.1259848104844709</v>
+      </c>
+      <c r="Z22">
+        <v>0.0660377358490566</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0.06732327832859103</v>
+      </c>
+      <c r="AC22">
+        <v>-0.06732327832859103</v>
+      </c>
+      <c r="AD22">
+        <v>47.6</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>47.6</v>
+      </c>
+      <c r="AG22">
+        <v>46.671</v>
+      </c>
+      <c r="AH22">
+        <v>0.7543581616481775</v>
+      </c>
+      <c r="AI22">
+        <v>0.4242424242424243</v>
+      </c>
+      <c r="AJ22">
+        <v>0.7506876196297309</v>
+      </c>
+      <c r="AK22">
+        <v>0.4194354324127581</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SGF Capital Public Company Limited (SET:SGF)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>-0.2</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>-3.91</v>
+      </c>
+      <c r="L23">
+        <v>-1.277777777777778</v>
+      </c>
+      <c r="M23">
+        <v>-0</v>
+      </c>
+      <c r="N23">
+        <v>-0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>-0</v>
+      </c>
+      <c r="Q23">
+        <v>-0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>2.65</v>
+      </c>
+      <c r="V23">
+        <v>0.3154761904761905</v>
+      </c>
+      <c r="W23">
+        <v>-0.08095238095238096</v>
+      </c>
+      <c r="X23">
+        <v>0.1046320020692174</v>
+      </c>
+      <c r="Y23">
+        <v>-0.1855843830215984</v>
+      </c>
+      <c r="Z23">
+        <v>0.03864124258113398</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0.06751083107025303</v>
+      </c>
+      <c r="AC23">
+        <v>-0.06751083107025303</v>
+      </c>
+      <c r="AD23">
+        <v>29.4</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>29.4</v>
+      </c>
+      <c r="AG23">
+        <v>26.75</v>
+      </c>
+      <c r="AH23">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="AI23">
+        <v>0.3675</v>
+      </c>
+      <c r="AJ23">
+        <v>0.7610241820768137</v>
+      </c>
+      <c r="AK23">
+        <v>0.3458306399482871</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>G Capital Public Company Limited (SET:GCAP)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>-0.119</v>
+      </c>
+      <c r="E24">
+        <v>-0.519</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0.049</v>
+      </c>
+      <c r="L24">
+        <v>0.01526479750778816</v>
+      </c>
+      <c r="M24">
+        <v>-0</v>
+      </c>
+      <c r="N24">
+        <v>-0</v>
+      </c>
+      <c r="O24">
+        <v>-0</v>
+      </c>
+      <c r="P24">
+        <v>-0</v>
+      </c>
+      <c r="Q24">
+        <v>-0</v>
+      </c>
+      <c r="R24">
+        <v>-0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0.26</v>
+      </c>
+      <c r="V24">
+        <v>0.05936073059360731</v>
+      </c>
+      <c r="W24">
+        <v>0.003828125</v>
+      </c>
+      <c r="X24">
+        <v>0.1090716196250295</v>
+      </c>
+      <c r="Y24">
+        <v>-0.1052434946250295</v>
+      </c>
+      <c r="Z24">
+        <v>0.1008387522382433</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0.06764212938741503</v>
+      </c>
+      <c r="AC24">
+        <v>-0.06764212938741503</v>
+      </c>
+      <c r="AD24">
+        <v>16.9</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>16.9</v>
+      </c>
+      <c r="AG24">
+        <v>16.64</v>
+      </c>
+      <c r="AH24">
+        <v>0.7941729323308271</v>
+      </c>
+      <c r="AI24">
+        <v>0.5232198142414861</v>
+      </c>
+      <c r="AJ24">
+        <v>0.7916270218839201</v>
+      </c>
+      <c r="AK24">
+        <v>0.5193508114856429</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bangkok Commercial Asset Management Public Company Limited (SET:BAM)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>-0.195</v>
+      </c>
+      <c r="E25">
+        <v>-0.257</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0.0002766963036862</v>
+      </c>
+      <c r="J25">
+        <v>0.000227473990595218</v>
+      </c>
+      <c r="K25">
+        <v>47.6</v>
+      </c>
+      <c r="L25">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="M25">
+        <v>38</v>
+      </c>
+      <c r="N25">
+        <v>0.06615598885793872</v>
+      </c>
+      <c r="O25">
+        <v>0.7983193277310924</v>
+      </c>
+      <c r="P25">
+        <v>38</v>
+      </c>
+      <c r="Q25">
+        <v>0.06615598885793872</v>
+      </c>
+      <c r="R25">
+        <v>0.7983193277310924</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>18.7</v>
+      </c>
+      <c r="V25">
+        <v>0.03255571030640669</v>
+      </c>
+      <c r="W25">
+        <v>0.04031165311653117</v>
+      </c>
+      <c r="X25">
+        <v>0.12372302771508</v>
+      </c>
+      <c r="Y25">
+        <v>-0.08341137459854878</v>
+      </c>
+      <c r="Z25">
+        <v>0.02440864466784017</v>
+      </c>
+      <c r="AA25">
+        <v>5.552331807614292E-06</v>
+      </c>
+      <c r="AB25">
+        <v>0.0679648817623633</v>
+      </c>
+      <c r="AC25">
+        <v>-0.06795932943055569</v>
+      </c>
+      <c r="AD25">
+        <v>2895.6</v>
+      </c>
+      <c r="AE25">
+        <v>0.1677002337706996</v>
+      </c>
+      <c r="AF25">
+        <v>2895.76770023377</v>
+      </c>
+      <c r="AG25">
+        <v>2877.067700233771</v>
+      </c>
+      <c r="AH25">
+        <v>0.8344748583875917</v>
+      </c>
+      <c r="AI25">
+        <v>0.6818275348128732</v>
+      </c>
+      <c r="AJ25">
+        <v>0.8335780456641401</v>
+      </c>
+      <c r="AK25">
+        <v>0.6804204137863196</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>49924.13793103448</v>
+      </c>
+      <c r="AP25">
+        <v>49604.6155212719</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Next Capital Public Company Limited (SET:NCAP)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>5.61</v>
+      </c>
+      <c r="L26">
+        <v>0.198936170212766</v>
+      </c>
+      <c r="M26">
+        <v>-0</v>
+      </c>
+      <c r="N26">
+        <v>-0</v>
+      </c>
+      <c r="O26">
+        <v>-0</v>
+      </c>
+      <c r="P26">
+        <v>-0</v>
+      </c>
+      <c r="Q26">
+        <v>-0</v>
+      </c>
+      <c r="R26">
+        <v>-0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>2.02</v>
+      </c>
+      <c r="V26">
+        <v>0.03519163763066202</v>
+      </c>
+      <c r="W26">
+        <v>0.04609695973705834</v>
+      </c>
+      <c r="X26">
+        <v>0.09520248257380275</v>
+      </c>
+      <c r="Y26">
+        <v>-0.0491055228367444</v>
+      </c>
+      <c r="Z26">
+        <v>0.1097959819342782</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0.06861348678324189</v>
+      </c>
+      <c r="AC26">
+        <v>-0.06861348678324189</v>
+      </c>
+      <c r="AD26">
+        <v>157.2</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>157.2</v>
+      </c>
+      <c r="AG26">
+        <v>155.18</v>
+      </c>
+      <c r="AH26">
+        <v>0.7325256290773532</v>
+      </c>
+      <c r="AI26">
+        <v>0.5245245245245245</v>
+      </c>
+      <c r="AJ26">
+        <v>0.7299840060212626</v>
+      </c>
+      <c r="AK26">
+        <v>0.5212980381617844</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Asia Sermkij Leasing Public Company Limited (SET:ASK)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>0.0428</v>
+      </c>
+      <c r="E27">
+        <v>-0.108</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>14.7</v>
+      </c>
+      <c r="L27">
+        <v>0.2145985401459854</v>
+      </c>
+      <c r="M27">
+        <v>18.9</v>
+      </c>
+      <c r="N27">
+        <v>0.1193181818181818</v>
+      </c>
+      <c r="O27">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="P27">
+        <v>18.9</v>
+      </c>
+      <c r="Q27">
+        <v>0.1193181818181818</v>
+      </c>
+      <c r="R27">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>16.2</v>
+      </c>
+      <c r="V27">
+        <v>0.1022727272727273</v>
+      </c>
+      <c r="W27">
+        <v>0.05097087378640777</v>
+      </c>
+      <c r="X27">
+        <v>0.2120136985626467</v>
+      </c>
+      <c r="Y27">
+        <v>-0.161042824776239</v>
+      </c>
+      <c r="Z27">
+        <v>0.03376380126182965</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0.06868238268784148</v>
+      </c>
+      <c r="AC27">
+        <v>-0.06868238268784148</v>
+      </c>
+      <c r="AD27">
+        <v>1927.7</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>1927.7</v>
+      </c>
+      <c r="AG27">
+        <v>1911.5</v>
+      </c>
+      <c r="AH27">
+        <v>0.9240688365850152</v>
+      </c>
+      <c r="AI27">
+        <v>0.8577467295541514</v>
+      </c>
+      <c r="AJ27">
+        <v>0.9234745639885984</v>
+      </c>
+      <c r="AK27">
+        <v>0.8567138759411976</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Micro Leasing Public Company Limited (SET:MICRO)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>0.138</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>-3.03</v>
+      </c>
+      <c r="L28">
+        <v>-0.2047297297297297</v>
+      </c>
+      <c r="M28">
+        <v>-0</v>
+      </c>
+      <c r="N28">
+        <v>-0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>-0</v>
+      </c>
+      <c r="Q28">
+        <v>-0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>25.9</v>
+      </c>
+      <c r="V28">
+        <v>0.9700374531835205</v>
+      </c>
+      <c r="W28">
+        <v>-0.05860735009671179</v>
+      </c>
+      <c r="X28">
+        <v>0.1011760713346172</v>
+      </c>
+      <c r="Y28">
+        <v>-0.159783421431329</v>
+      </c>
+      <c r="Z28">
+        <v>0.1148176881303336</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0.06891936446306302</v>
+      </c>
+      <c r="AC28">
+        <v>-0.06891936446306302</v>
+      </c>
+      <c r="AD28">
+        <v>86</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>86</v>
+      </c>
+      <c r="AG28">
+        <v>60.1</v>
+      </c>
+      <c r="AH28">
+        <v>0.7630878438331854</v>
+      </c>
+      <c r="AI28">
+        <v>0.5760214333556597</v>
+      </c>
+      <c r="AJ28">
+        <v>0.6923963133640554</v>
+      </c>
+      <c r="AK28">
+        <v>0.4870340356564019</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>Muangthai Capital Public Company Limited (SET:MTC)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D29">
         <v>0.132</v>
       </c>
-      <c r="E3">
+      <c r="E29">
         <v>0.0668</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
         <v>175.5</v>
       </c>
-      <c r="L3">
+      <c r="L29">
         <v>0.3022214568624074</v>
       </c>
-      <c r="M3">
+      <c r="M29">
         <v>13.8</v>
       </c>
-      <c r="N3">
+      <c r="N29">
         <v>0.004654614139233675</v>
       </c>
-      <c r="O3">
+      <c r="O29">
         <v>0.07863247863247863</v>
       </c>
-      <c r="P3">
+      <c r="P29">
         <v>13.8</v>
       </c>
-      <c r="Q3">
+      <c r="Q29">
         <v>0.004654614139233675</v>
       </c>
-      <c r="R3">
+      <c r="R29">
         <v>0.07863247863247863</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
         <v>248.6</v>
       </c>
-      <c r="V3">
+      <c r="V29">
         <v>0.08385051268213707</v>
       </c>
-      <c r="W3">
+      <c r="W29">
         <v>0.2094022193055721</v>
       </c>
-      <c r="X3">
-        <v>0.07843697142345817</v>
-      </c>
-      <c r="Y3">
-        <v>0.1309652478821139</v>
-      </c>
-      <c r="Z3">
+      <c r="X29">
+        <v>0.07842814111974952</v>
+      </c>
+      <c r="Y29">
+        <v>0.1309740781858226</v>
+      </c>
+      <c r="Z29">
         <v>0.1511767156097053</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.07183430967375638</v>
-      </c>
-      <c r="AC3">
-        <v>-0.07183430967375638</v>
-      </c>
-      <c r="AD3">
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0.07183060622007269</v>
+      </c>
+      <c r="AC29">
+        <v>-0.07183060622007269</v>
+      </c>
+      <c r="AD29">
         <v>4104.3</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
         <v>4104.3</v>
       </c>
-      <c r="AG3">
+      <c r="AG29">
         <v>3855.7</v>
       </c>
-      <c r="AH3">
+      <c r="AH29">
         <v>0.580597247174322</v>
       </c>
-      <c r="AI3">
+      <c r="AI29">
         <v>0.7881819753039003</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ29">
         <v>0.5653104611098894</v>
       </c>
-      <c r="AK3">
+      <c r="AK29">
         <v>0.7775626676346622</v>
       </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Srisawad Capital 1969 Public Company Limited (SET:SCAP)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>0.146</v>
+      </c>
+      <c r="E30">
+        <v>0.06280000000000001</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>19.3</v>
+      </c>
+      <c r="L30">
+        <v>0.1230082855321861</v>
+      </c>
+      <c r="M30">
+        <v>0.463</v>
+      </c>
+      <c r="N30">
+        <v>0.001629134412385644</v>
+      </c>
+      <c r="O30">
+        <v>0.02398963730569948</v>
+      </c>
+      <c r="P30">
+        <v>0.463</v>
+      </c>
+      <c r="Q30">
+        <v>0.001629134412385644</v>
+      </c>
+      <c r="R30">
+        <v>0.02398963730569948</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>34.6</v>
+      </c>
+      <c r="V30">
+        <v>0.1217452498240676</v>
+      </c>
+      <c r="W30">
+        <v>0.07313376278893521</v>
+      </c>
+      <c r="X30">
+        <v>0.09295232759642191</v>
+      </c>
+      <c r="Y30">
+        <v>-0.0198185648074867</v>
+      </c>
+      <c r="Z30">
+        <v>0.178620218579235</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0.07209983651932467</v>
+      </c>
+      <c r="AC30">
+        <v>-0.07209983651932467</v>
+      </c>
+      <c r="AD30">
+        <v>726.7</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>726.7</v>
+      </c>
+      <c r="AG30">
+        <v>692.1</v>
+      </c>
+      <c r="AH30">
+        <v>0.7188643782767831</v>
+      </c>
+      <c r="AI30">
+        <v>0.6940783190066858</v>
+      </c>
+      <c r="AJ30">
+        <v>0.7089009525760525</v>
+      </c>
+      <c r="AK30">
+        <v>0.6836230738838404</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amanah Leasing Public Company Limited (SET:AMANAH)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>0.0675</v>
+      </c>
+      <c r="E31">
+        <v>-0.342</v>
+      </c>
+      <c r="G31">
+        <v>0.1277591973244147</v>
+      </c>
+      <c r="H31">
+        <v>0.1277591973244147</v>
+      </c>
+      <c r="I31">
+        <v>-0.06086956521739131</v>
+      </c>
+      <c r="J31">
+        <v>-0.06000616712920136</v>
+      </c>
+      <c r="K31">
+        <v>0.834</v>
+      </c>
+      <c r="L31">
+        <v>0.02789297658862876</v>
+      </c>
+      <c r="M31">
+        <v>0.509</v>
+      </c>
+      <c r="N31">
+        <v>0.01488304093567251</v>
+      </c>
+      <c r="O31">
+        <v>0.6103117505995205</v>
+      </c>
+      <c r="P31">
+        <v>0.509</v>
+      </c>
+      <c r="Q31">
+        <v>0.01488304093567251</v>
+      </c>
+      <c r="R31">
+        <v>0.6103117505995205</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>5.17</v>
+      </c>
+      <c r="V31">
+        <v>0.1511695906432748</v>
+      </c>
+      <c r="W31">
+        <v>0.01705521472392638</v>
+      </c>
+      <c r="X31">
+        <v>0.08884206491798391</v>
+      </c>
+      <c r="Y31">
+        <v>-0.07178685019405753</v>
+      </c>
+      <c r="Z31">
+        <v>0.2466182777961069</v>
+      </c>
+      <c r="AA31">
+        <v>-0.014798617594549</v>
+      </c>
+      <c r="AB31">
+        <v>0.06680736669660246</v>
+      </c>
+      <c r="AC31">
+        <v>-0.08160598429115146</v>
+      </c>
+      <c r="AD31">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AG31">
+        <v>70.92999999999999</v>
+      </c>
+      <c r="AH31">
+        <v>0.6899365367180417</v>
+      </c>
+      <c r="AI31">
+        <v>0.577828397873956</v>
+      </c>
+      <c r="AJ31">
+        <v>0.6746884809283743</v>
+      </c>
+      <c r="AK31">
+        <v>0.5605785189283173</v>
+      </c>
+      <c r="AL31">
+        <v>3.87</v>
+      </c>
+      <c r="AM31">
+        <v>3.87</v>
+      </c>
+      <c r="AN31">
+        <v>-46.12121212121212</v>
+      </c>
+      <c r="AO31">
+        <v>-0.4702842377260982</v>
+      </c>
+      <c r="AP31">
+        <v>-42.98787878787878</v>
+      </c>
+      <c r="AQ31">
+        <v>-0.4702842377260982</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sabuy Technology Public Company Limited (SET:SABUY)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="F32">
+        <v>0.406</v>
+      </c>
+      <c r="G32">
+        <v>0.02078598484848485</v>
+      </c>
+      <c r="H32">
+        <v>0.02078598484848485</v>
+      </c>
+      <c r="I32">
+        <v>-0.1876425893047664</v>
+      </c>
+      <c r="J32">
+        <v>-0.1876425893047664</v>
+      </c>
+      <c r="K32">
+        <v>-195.3</v>
+      </c>
+      <c r="L32">
+        <v>-0.9247159090909092</v>
+      </c>
+      <c r="M32">
+        <v>7.673</v>
+      </c>
+      <c r="N32">
+        <v>0.2974031007751938</v>
+      </c>
+      <c r="O32">
+        <v>-0.03928827444956477</v>
+      </c>
+      <c r="P32">
+        <v>0.283</v>
+      </c>
+      <c r="Q32">
+        <v>0.01096899224806201</v>
+      </c>
+      <c r="R32">
+        <v>-0.00144905273937532</v>
+      </c>
+      <c r="S32">
+        <v>7.39</v>
+      </c>
+      <c r="T32">
+        <v>0.9631174247360875</v>
+      </c>
+      <c r="U32">
+        <v>4.66</v>
+      </c>
+      <c r="V32">
+        <v>0.1806201550387597</v>
+      </c>
+      <c r="W32">
+        <v>-0.7958435207823961</v>
+      </c>
+      <c r="X32">
+        <v>0.1535509314728504</v>
+      </c>
+      <c r="Y32">
+        <v>-0.9493944522552464</v>
+      </c>
+      <c r="Z32">
+        <v>0.6049832499415366</v>
+      </c>
+      <c r="AA32">
+        <v>-0.1135206235050426</v>
+      </c>
+      <c r="AB32">
+        <v>0.07454951872960618</v>
+      </c>
+      <c r="AC32">
+        <v>-0.1880701422346488</v>
+      </c>
+      <c r="AD32">
+        <v>190.6</v>
+      </c>
+      <c r="AE32">
+        <v>1.600574305833369</v>
+      </c>
+      <c r="AF32">
+        <v>192.2005743058334</v>
+      </c>
+      <c r="AG32">
+        <v>187.5405743058334</v>
+      </c>
+      <c r="AH32">
+        <v>0.8816516879271834</v>
+      </c>
+      <c r="AI32">
+        <v>0.7375293581673856</v>
+      </c>
+      <c r="AJ32">
+        <v>0.8790666047283883</v>
+      </c>
+      <c r="AK32">
+        <v>0.7327504629325939</v>
+      </c>
+      <c r="AL32">
+        <v>16</v>
+      </c>
+      <c r="AM32">
+        <v>16</v>
+      </c>
+      <c r="AN32">
+        <v>-8.779364348226624</v>
+      </c>
+      <c r="AO32">
+        <v>-2.55</v>
+      </c>
+      <c r="AP32">
+        <v>-8.638441930254876</v>
+      </c>
+      <c r="AQ32">
+        <v>-2.55</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Oriental Payment Group Holdings Limited (SEHK:8613)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>-0.158</v>
+      </c>
+      <c r="G33">
+        <v>-0.655831739961759</v>
+      </c>
+      <c r="H33">
+        <v>-0.655831739961759</v>
+      </c>
+      <c r="I33">
+        <v>-0.7552581261950286</v>
+      </c>
+      <c r="J33">
+        <v>-0.7552581261950286</v>
+      </c>
+      <c r="K33">
+        <v>-4.51</v>
+      </c>
+      <c r="L33">
+        <v>-0.8623326959847035</v>
+      </c>
+      <c r="M33">
+        <v>-0</v>
+      </c>
+      <c r="N33">
+        <v>-0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>-0</v>
+      </c>
+      <c r="Q33">
+        <v>-0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0.407</v>
+      </c>
+      <c r="V33">
+        <v>0.01108991825613079</v>
+      </c>
+      <c r="W33">
+        <v>-0.882583170254403</v>
+      </c>
+      <c r="X33">
+        <v>0.06256117242373545</v>
+      </c>
+      <c r="Y33">
+        <v>-0.9451443426781385</v>
+      </c>
+      <c r="Z33">
+        <v>0.7378668171557562</v>
+      </c>
+      <c r="AA33">
+        <v>-0.5572799097065462</v>
+      </c>
+      <c r="AB33">
+        <v>0.06221892201876759</v>
+      </c>
+      <c r="AC33">
+        <v>-0.6194988317253137</v>
+      </c>
+      <c r="AD33">
+        <v>3.79</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>3.79</v>
+      </c>
+      <c r="AG33">
+        <v>3.383</v>
+      </c>
+      <c r="AH33">
+        <v>0.09360335885403803</v>
+      </c>
+      <c r="AI33">
+        <v>0.7927211880359758</v>
+      </c>
+      <c r="AJ33">
+        <v>0.08439987026919142</v>
+      </c>
+      <c r="AK33">
+        <v>0.7734339277549155</v>
+      </c>
+      <c r="AL33">
+        <v>0.376</v>
+      </c>
+      <c r="AM33">
+        <v>0.342</v>
+      </c>
+      <c r="AN33">
+        <v>-1.534412955465587</v>
+      </c>
+      <c r="AO33">
+        <v>-10.50531914893617</v>
+      </c>
+      <c r="AP33">
+        <v>-1.369635627530364</v>
+      </c>
+      <c r="AQ33">
+        <v>-11.54970760233918</v>
       </c>
     </row>
   </sheetData>
